--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,33 +450,1083 @@
       <c r="H3" t="n">
         <v>2022</v>
       </c>
+      <c r="I3" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.05987</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.07005</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.55753</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.63815</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.24652</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.68666</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.23272</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.34605</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.99537</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.9861</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.97426</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.85284</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.35015</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.16005</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.0574</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.50139</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>5.49858</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>5.7128</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B8" t="n">
         <v>2.88621</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C8" t="n">
         <v>2.9547</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D8" t="n">
         <v>2.9604</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E8" t="n">
         <v>3.01889</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F8" t="n">
         <v>2.1474</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G8" t="n">
         <v>2.76457</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H8" t="n">
         <v>2.96775</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2020.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2272.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2485.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2546.2</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>491.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.955</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.195</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>South Asia (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9.523</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14.355</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16.029</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>262.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>271.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>284.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>73.902</v>
+      </c>
+      <c r="H21" t="n">
+        <v>62.351</v>
+      </c>
+      <c r="I21" t="n">
+        <v>195.241</v>
+      </c>
+      <c r="J21" t="n">
+        <v>234.123</v>
+      </c>
+      <c r="K21" t="n">
+        <v>252.546</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3508.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3889.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4084.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4142</v>
+      </c>
+      <c r="G22" t="n">
+        <v>797.258</v>
+      </c>
+      <c r="H22" t="n">
+        <v>873.521</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3045.921</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3800.781</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4250.701</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3488.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3888.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3964.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3962.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>579.165</v>
+      </c>
+      <c r="H23" t="n">
+        <v>313.499</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1202.564</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2329.21</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2700.05</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>26568.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>27635.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>28681.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>29489.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10594.872</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10047.669</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23043.584</v>
+      </c>
+      <c r="J24" t="n">
+        <v>27129.43</v>
+      </c>
+      <c r="K24" t="n">
+        <v>28794.97</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>673.1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>660.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>636</v>
+      </c>
+      <c r="F25" t="n">
+        <v>604.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>95.996</v>
+      </c>
+      <c r="H25" t="n">
+        <v>165.966</v>
+      </c>
+      <c r="I25" t="n">
+        <v>404.707</v>
+      </c>
+      <c r="J25" t="n">
+        <v>483.885</v>
+      </c>
+      <c r="K25" t="n">
+        <v>489.689</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>South Asia (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>289.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>307.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>55.831</v>
+      </c>
+      <c r="H26" t="n">
+        <v>42.545</v>
+      </c>
+      <c r="I26" t="n">
+        <v>160.263</v>
+      </c>
+      <c r="J26" t="n">
+        <v>232.398</v>
+      </c>
+      <c r="K26" t="n">
+        <v>278.701</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1243</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1314.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1235.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1340</v>
+      </c>
+      <c r="G27" t="n">
+        <v>262.945</v>
+      </c>
+      <c r="H27" t="n">
+        <v>250.284</v>
+      </c>
+      <c r="I27" t="n">
+        <v>830.221</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1025.13128294283</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1297.90576947888</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4573.9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5866</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6370.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7092.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1320.48</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1867.265</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6359.413</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8470.624000010759</v>
+      </c>
+      <c r="K28" t="n">
+        <v>9428.970904708071</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1904.7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2299</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2560.7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2977</v>
+      </c>
+      <c r="G29" t="n">
+        <v>562.403</v>
+      </c>
+      <c r="H29" t="n">
+        <v>230.302</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1086.684</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2360.18863897558</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2817.03795662791</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>67047.39999999999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>71695.89999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>71903.89999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>71377.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16676.276</v>
+      </c>
+      <c r="H30" t="n">
+        <v>28505.919</v>
+      </c>
+      <c r="I30" t="n">
+        <v>62765.346</v>
+      </c>
+      <c r="J30" t="n">
+        <v>72386.9099346476</v>
+      </c>
+      <c r="K30" t="n">
+        <v>79114.75530078731</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>424.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76.34399999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>281.162</v>
+      </c>
+      <c r="I31" t="n">
+        <v>416.759</v>
+      </c>
+      <c r="J31" t="n">
+        <v>617.95432944935</v>
+      </c>
+      <c r="K31" t="n">
+        <v>765.914310277042</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>South Asia (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>159.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>227</v>
+      </c>
+      <c r="E32" t="n">
+        <v>321</v>
+      </c>
+      <c r="F32" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.655</v>
+      </c>
+      <c r="H32" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="I32" t="n">
+        <v>200.859</v>
+      </c>
+      <c r="J32" t="n">
+        <v>308.24178665693</v>
+      </c>
+      <c r="K32" t="n">
+        <v>334.712612593961</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>574.301</v>
+      </c>
+      <c r="D33" t="n">
+        <v>585.447</v>
+      </c>
+      <c r="E33" t="n">
+        <v>597.803</v>
+      </c>
+      <c r="F33" t="n">
+        <v>566.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>107.201</v>
+      </c>
+      <c r="H33" t="n">
+        <v>153.671</v>
+      </c>
+      <c r="I33" t="n">
+        <v>366.029</v>
+      </c>
+      <c r="J33" t="n">
+        <v>529.515</v>
+      </c>
+      <c r="K33" t="n">
+        <v>586.16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>46459.207</v>
+      </c>
+      <c r="D34" t="n">
+        <v>46675.98</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48966.068</v>
+      </c>
+      <c r="F34" t="n">
+        <v>48061.7</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13952.619</v>
+      </c>
+      <c r="H34" t="n">
+        <v>18293.477</v>
+      </c>
+      <c r="I34" t="n">
+        <v>33573.32</v>
+      </c>
+      <c r="J34" t="n">
+        <v>42840.828</v>
+      </c>
+      <c r="K34" t="n">
+        <v>46039.515</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>11764.684</v>
+      </c>
+      <c r="D35" t="n">
+        <v>12260.961</v>
+      </c>
+      <c r="E35" t="n">
+        <v>11952.945</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12183.9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2027.749</v>
+      </c>
+      <c r="H35" t="n">
+        <v>816.227</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3455.282</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6726.311</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7951.807</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>15505.744</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15633.303</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16082.513</v>
+      </c>
+      <c r="F36" t="n">
+        <v>16381.9</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2612.223</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2259.032</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11567.835</v>
+      </c>
+      <c r="J36" t="n">
+        <v>13771.831</v>
+      </c>
+      <c r="K36" t="n">
+        <v>14854.886</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>681.191</v>
+      </c>
+      <c r="D37" t="n">
+        <v>550.013</v>
+      </c>
+      <c r="E37" t="n">
+        <v>576.227</v>
+      </c>
+      <c r="F37" t="n">
+        <v>577.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>127.276</v>
+      </c>
+      <c r="H37" t="n">
+        <v>227.801</v>
+      </c>
+      <c r="I37" t="n">
+        <v>366.673</v>
+      </c>
+      <c r="J37" t="n">
+        <v>463.179</v>
+      </c>
+      <c r="K37" t="n">
+        <v>459.545</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>South Asia (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1422.361</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1481.042</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1570.362</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1670.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>384.746</v>
+      </c>
+      <c r="H38" t="n">
+        <v>528.2569999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1440.26</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2016.472</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2496.501</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,301 +450,336 @@
       <c r="H3" t="n">
         <v>2022</v>
       </c>
-      <c r="I3" t="n">
-        <v>2023</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.05987</v>
+        <v>3.99537</v>
       </c>
       <c r="C4" t="n">
-        <v>2.07005</v>
+        <v>3.9861</v>
       </c>
       <c r="D4" t="n">
-        <v>2.55753</v>
+        <v>3.97426</v>
       </c>
       <c r="E4" t="n">
-        <v>2.63815</v>
+        <v>3.85284</v>
       </c>
       <c r="F4" t="n">
-        <v>1.24652</v>
+        <v>2.35015</v>
       </c>
       <c r="G4" t="n">
-        <v>1.68666</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.23272</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.34605</v>
-      </c>
+        <v>2.16005</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.99537</v>
+        <v>6.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9861</v>
+        <v>6.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3.97426</v>
+        <v>6.7</v>
       </c>
       <c r="E5" t="n">
-        <v>3.85284</v>
+        <v>6.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2.35015</v>
+        <v>5.0574</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16005</v>
+        <v>5.50139</v>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6.5</v>
-      </c>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.7</v>
-      </c>
+        <v>5.49858</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.0574</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.50139</v>
-      </c>
+        <v>5.7128</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.88621</v>
+      </c>
       <c r="C7" t="n">
-        <v>5.49858</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>2.9547</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.9604</v>
+      </c>
       <c r="E7" t="n">
-        <v>5.7128</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.88621</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.9547</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.9604</v>
-      </c>
-      <c r="E8" t="n">
         <v>3.01889</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F7" t="n">
         <v>2.1474</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G7" t="n">
         <v>2.76457</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H7" t="n">
         <v>2.96775</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
-        </is>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_arrivals_by_purpose_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>series</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>5703.7</v>
       </c>
       <c r="D14" t="n">
-        <v>2017</v>
+        <v>5706.7</v>
       </c>
       <c r="E14" t="n">
-        <v>2018</v>
+        <v>5636.8</v>
       </c>
       <c r="F14" t="n">
-        <v>2019</v>
+        <v>6112.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2020</v>
+        <v>1565.465</v>
       </c>
       <c r="H14" t="n">
-        <v>2021</v>
+        <v>2270.304</v>
       </c>
       <c r="I14" t="n">
-        <v>2022</v>
+        <v>4952.511</v>
       </c>
       <c r="J14" t="n">
-        <v>2023</v>
+        <v>4973.06749958168</v>
       </c>
       <c r="K14" t="n">
-        <v>2024</v>
+        <v>5253.19541783694</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.8</v>
+        <v>69611.3</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7</v>
+        <v>76161.7</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5</v>
+        <v>77171.60000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>77396.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>17367.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>28910.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>66706.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>80195.98247311771</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88506.1014367087</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2020.9</v>
+        <v>14649</v>
       </c>
       <c r="D16" t="n">
-        <v>2272.5</v>
+        <v>14537</v>
       </c>
       <c r="E16" t="n">
-        <v>2485.8</v>
+        <v>14377.6</v>
       </c>
       <c r="F16" t="n">
-        <v>2546.2</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+        <v>14875.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6766</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8326</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10259</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11321</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11247</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54.4</v>
+        <v>70275</v>
       </c>
       <c r="D17" t="n">
-        <v>58.4</v>
+        <v>75394</v>
       </c>
       <c r="E17" t="n">
-        <v>61.4</v>
+        <v>78850.89999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+        <v>80523.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18423</v>
+      </c>
+      <c r="H17" t="n">
+        <v>18562</v>
+      </c>
+      <c r="I17" t="n">
+        <v>39552</v>
+      </c>
+      <c r="J17" t="n">
+        <v>45929</v>
+      </c>
+      <c r="K17" t="n">
+        <v>46478</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Europe (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>439.9</v>
+        <v>6863.27243246694</v>
       </c>
       <c r="D18" t="n">
-        <v>491.4</v>
+        <v>6963.91479812882</v>
       </c>
       <c r="E18" t="n">
-        <v>544.3</v>
+        <v>6979.49317509289</v>
       </c>
       <c r="F18" t="n">
-        <v>586.5</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+        <v>6988</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1625.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1128.5</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -752,274 +787,80 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.9</v>
+        <v>31266.1315675331</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1</v>
+        <v>31941.6092018712</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2</v>
+        <v>32903.8678249071</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>33405</v>
       </c>
       <c r="G19" t="n">
-        <v>0.674</v>
+        <v>5968.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.236</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.471</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.955</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.195</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>South Asia (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.083</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.056</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9.523</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14.355</v>
-      </c>
-      <c r="K20" t="n">
-        <v>16.029</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Africa (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>262.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>271.2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>272.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>284.2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>73.902</v>
-      </c>
-      <c r="H21" t="n">
-        <v>62.351</v>
-      </c>
-      <c r="I21" t="n">
-        <v>195.241</v>
-      </c>
-      <c r="J21" t="n">
-        <v>234.123</v>
-      </c>
-      <c r="K21" t="n">
-        <v>252.546</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Americas (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3508.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3889.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4084.7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4142</v>
-      </c>
-      <c r="G22" t="n">
-        <v>797.258</v>
-      </c>
-      <c r="H22" t="n">
-        <v>873.521</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3045.921</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3800.781</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4250.701</v>
-      </c>
+        <v>8046.4</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>3488.9</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3888.7</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3964.8</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3962.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>579.165</v>
-      </c>
-      <c r="H23" t="n">
-        <v>313.499</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1202.564</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2329.21</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2700.05</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Europe (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>26568.4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>27635.3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>28681.2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>29489.2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10594.872</v>
-      </c>
-      <c r="H24" t="n">
-        <v>10047.669</v>
-      </c>
-      <c r="I24" t="n">
-        <v>23043.584</v>
-      </c>
-      <c r="J24" t="n">
-        <v>27129.43</v>
-      </c>
-      <c r="K24" t="n">
-        <v>28794.97</v>
+          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>series</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>673.1</v>
+        <v>2016</v>
       </c>
       <c r="D25" t="n">
-        <v>660.8</v>
+        <v>2017</v>
       </c>
       <c r="E25" t="n">
-        <v>636</v>
+        <v>2018</v>
       </c>
       <c r="F25" t="n">
-        <v>604.3</v>
+        <v>2019</v>
       </c>
       <c r="G25" t="n">
-        <v>95.996</v>
+        <v>2020</v>
       </c>
       <c r="H25" t="n">
-        <v>165.966</v>
+        <v>2021</v>
       </c>
       <c r="I25" t="n">
-        <v>404.707</v>
+        <v>2022</v>
       </c>
       <c r="J25" t="n">
-        <v>483.885</v>
+        <v>2023</v>
       </c>
       <c r="K25" t="n">
-        <v>489.689</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="26">
@@ -1030,230 +871,230 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>South Asia (UNWTO total)</t>
+          <t>Africa (UNWTO total)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>231.2</v>
+        <v>262.6</v>
       </c>
       <c r="D26" t="n">
-        <v>268.7</v>
+        <v>271.2</v>
       </c>
       <c r="E26" t="n">
-        <v>289.7</v>
+        <v>272.5</v>
       </c>
       <c r="F26" t="n">
-        <v>307.1</v>
+        <v>284.2</v>
       </c>
       <c r="G26" t="n">
-        <v>55.831</v>
+        <v>73.902</v>
       </c>
       <c r="H26" t="n">
-        <v>42.545</v>
+        <v>62.351</v>
       </c>
       <c r="I26" t="n">
-        <v>160.263</v>
+        <v>195.241</v>
       </c>
       <c r="J26" t="n">
-        <v>232.398</v>
+        <v>234.123</v>
       </c>
       <c r="K26" t="n">
-        <v>278.701</v>
+        <v>252.546</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>Americas (UNWTO total)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1243</v>
+        <v>3508.5</v>
       </c>
       <c r="D27" t="n">
-        <v>1314.3</v>
+        <v>3889.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1235.9</v>
+        <v>4084.7</v>
       </c>
       <c r="F27" t="n">
-        <v>1340</v>
+        <v>4142</v>
       </c>
       <c r="G27" t="n">
-        <v>262.945</v>
+        <v>797.258</v>
       </c>
       <c r="H27" t="n">
-        <v>250.284</v>
+        <v>873.521</v>
       </c>
       <c r="I27" t="n">
-        <v>830.221</v>
+        <v>3045.921</v>
       </c>
       <c r="J27" t="n">
-        <v>1025.13128294283</v>
+        <v>3800.781</v>
       </c>
       <c r="K27" t="n">
-        <v>1297.90576947888</v>
+        <v>4250.701</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>East Asia and the Pacific (UNWTO total)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4573.9</v>
+        <v>3488.9</v>
       </c>
       <c r="D28" t="n">
-        <v>5866</v>
+        <v>3888.7</v>
       </c>
       <c r="E28" t="n">
-        <v>6370.5</v>
+        <v>3964.8</v>
       </c>
       <c r="F28" t="n">
-        <v>7092.1</v>
+        <v>3962.6</v>
       </c>
       <c r="G28" t="n">
-        <v>1320.48</v>
+        <v>579.165</v>
       </c>
       <c r="H28" t="n">
-        <v>1867.265</v>
+        <v>313.499</v>
       </c>
       <c r="I28" t="n">
-        <v>6359.413</v>
+        <v>1202.564</v>
       </c>
       <c r="J28" t="n">
-        <v>8470.624000010759</v>
+        <v>2329.21</v>
       </c>
       <c r="K28" t="n">
-        <v>9428.970904708071</v>
+        <v>2700.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>Europe (UNWTO total)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1904.7</v>
+        <v>26568.4</v>
       </c>
       <c r="D29" t="n">
-        <v>2299</v>
+        <v>27635.3</v>
       </c>
       <c r="E29" t="n">
-        <v>2560.7</v>
+        <v>28681.2</v>
       </c>
       <c r="F29" t="n">
-        <v>2977</v>
+        <v>29489.2</v>
       </c>
       <c r="G29" t="n">
-        <v>562.403</v>
+        <v>10594.872</v>
       </c>
       <c r="H29" t="n">
-        <v>230.302</v>
+        <v>10047.669</v>
       </c>
       <c r="I29" t="n">
-        <v>1086.684</v>
+        <v>23043.584</v>
       </c>
       <c r="J29" t="n">
-        <v>2360.18863897558</v>
+        <v>27129.43</v>
       </c>
       <c r="K29" t="n">
-        <v>2817.03795662791</v>
+        <v>28794.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Europe (UNWTO total)</t>
+          <t>Middle East (UNWTO total)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>67047.39999999999</v>
+        <v>673.1</v>
       </c>
       <c r="D30" t="n">
-        <v>71695.89999999999</v>
+        <v>660.8</v>
       </c>
       <c r="E30" t="n">
-        <v>71903.89999999999</v>
+        <v>636</v>
       </c>
       <c r="F30" t="n">
-        <v>71377.8</v>
+        <v>604.3</v>
       </c>
       <c r="G30" t="n">
-        <v>16676.276</v>
+        <v>95.996</v>
       </c>
       <c r="H30" t="n">
-        <v>28505.919</v>
+        <v>165.966</v>
       </c>
       <c r="I30" t="n">
-        <v>62765.346</v>
+        <v>404.707</v>
       </c>
       <c r="J30" t="n">
-        <v>72386.9099346476</v>
+        <v>483.885</v>
       </c>
       <c r="K30" t="n">
-        <v>79114.75530078731</v>
+        <v>489.689</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>South Asia (UNWTO total)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>386.7</v>
+        <v>231.2</v>
       </c>
       <c r="D31" t="n">
-        <v>466.4</v>
+        <v>268.7</v>
       </c>
       <c r="E31" t="n">
-        <v>416.3</v>
+        <v>289.7</v>
       </c>
       <c r="F31" t="n">
-        <v>424.7</v>
+        <v>307.1</v>
       </c>
       <c r="G31" t="n">
-        <v>76.34399999999999</v>
+        <v>55.831</v>
       </c>
       <c r="H31" t="n">
-        <v>281.162</v>
+        <v>42.545</v>
       </c>
       <c r="I31" t="n">
-        <v>416.759</v>
+        <v>160.263</v>
       </c>
       <c r="J31" t="n">
-        <v>617.95432944935</v>
+        <v>232.398</v>
       </c>
       <c r="K31" t="n">
-        <v>765.914310277042</v>
+        <v>278.701</v>
       </c>
     </row>
     <row r="32">
@@ -1264,230 +1105,230 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>South Asia (UNWTO total)</t>
+          <t>Africa (UNWTO total)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>159.3</v>
+        <v>1243</v>
       </c>
       <c r="D32" t="n">
-        <v>227</v>
+        <v>1314.3</v>
       </c>
       <c r="E32" t="n">
-        <v>321</v>
+        <v>1235.9</v>
       </c>
       <c r="F32" t="n">
-        <v>297.5</v>
+        <v>1340</v>
       </c>
       <c r="G32" t="n">
-        <v>34.655</v>
+        <v>262.945</v>
       </c>
       <c r="H32" t="n">
-        <v>45.87</v>
+        <v>250.284</v>
       </c>
       <c r="I32" t="n">
-        <v>200.859</v>
+        <v>830.221</v>
       </c>
       <c r="J32" t="n">
-        <v>308.24178665693</v>
+        <v>1025.13128294283</v>
       </c>
       <c r="K32" t="n">
-        <v>334.712612593961</v>
+        <v>1297.90576947888</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>Americas (UNWTO total)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>574.301</v>
+        <v>4573.9</v>
       </c>
       <c r="D33" t="n">
-        <v>585.447</v>
+        <v>5866</v>
       </c>
       <c r="E33" t="n">
-        <v>597.803</v>
+        <v>6370.5</v>
       </c>
       <c r="F33" t="n">
-        <v>566.6</v>
+        <v>7092.1</v>
       </c>
       <c r="G33" t="n">
-        <v>107.201</v>
+        <v>1320.48</v>
       </c>
       <c r="H33" t="n">
-        <v>153.671</v>
+        <v>1867.265</v>
       </c>
       <c r="I33" t="n">
-        <v>366.029</v>
+        <v>6359.413</v>
       </c>
       <c r="J33" t="n">
-        <v>529.515</v>
+        <v>8470.624000010759</v>
       </c>
       <c r="K33" t="n">
-        <v>586.16</v>
+        <v>9428.970904708071</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>East Asia and the Pacific (UNWTO total)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>46459.207</v>
+        <v>1904.7</v>
       </c>
       <c r="D34" t="n">
-        <v>46675.98</v>
+        <v>2299</v>
       </c>
       <c r="E34" t="n">
-        <v>48966.068</v>
+        <v>2560.7</v>
       </c>
       <c r="F34" t="n">
-        <v>48061.7</v>
+        <v>2977</v>
       </c>
       <c r="G34" t="n">
-        <v>13952.619</v>
+        <v>562.403</v>
       </c>
       <c r="H34" t="n">
-        <v>18293.477</v>
+        <v>230.302</v>
       </c>
       <c r="I34" t="n">
-        <v>33573.32</v>
+        <v>1086.684</v>
       </c>
       <c r="J34" t="n">
-        <v>42840.828</v>
+        <v>2360.18863897558</v>
       </c>
       <c r="K34" t="n">
-        <v>46039.515</v>
+        <v>2817.03795662791</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>Europe (UNWTO total)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11764.684</v>
+        <v>67047.39999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>12260.961</v>
+        <v>71695.89999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>11952.945</v>
+        <v>71903.89999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>12183.9</v>
+        <v>71377.8</v>
       </c>
       <c r="G35" t="n">
-        <v>2027.749</v>
+        <v>16676.276</v>
       </c>
       <c r="H35" t="n">
-        <v>816.227</v>
+        <v>28505.919</v>
       </c>
       <c r="I35" t="n">
-        <v>3455.282</v>
+        <v>62765.346</v>
       </c>
       <c r="J35" t="n">
-        <v>6726.311</v>
+        <v>72386.9099346476</v>
       </c>
       <c r="K35" t="n">
-        <v>7951.807</v>
+        <v>79114.75530078731</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Europe (UNWTO total)</t>
+          <t>Middle East (UNWTO total)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15505.744</v>
+        <v>386.7</v>
       </c>
       <c r="D36" t="n">
-        <v>15633.303</v>
+        <v>466.4</v>
       </c>
       <c r="E36" t="n">
-        <v>16082.513</v>
+        <v>416.3</v>
       </c>
       <c r="F36" t="n">
-        <v>16381.9</v>
+        <v>424.7</v>
       </c>
       <c r="G36" t="n">
-        <v>2612.223</v>
+        <v>76.34399999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>2259.032</v>
+        <v>281.162</v>
       </c>
       <c r="I36" t="n">
-        <v>11567.835</v>
+        <v>416.759</v>
       </c>
       <c r="J36" t="n">
-        <v>13771.831</v>
+        <v>617.95432944935</v>
       </c>
       <c r="K36" t="n">
-        <v>14854.886</v>
+        <v>765.914310277042</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>South Asia (UNWTO total)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>681.191</v>
+        <v>159.3</v>
       </c>
       <c r="D37" t="n">
-        <v>550.013</v>
+        <v>227</v>
       </c>
       <c r="E37" t="n">
-        <v>576.227</v>
+        <v>321</v>
       </c>
       <c r="F37" t="n">
-        <v>577.1</v>
+        <v>297.5</v>
       </c>
       <c r="G37" t="n">
-        <v>127.276</v>
+        <v>34.655</v>
       </c>
       <c r="H37" t="n">
-        <v>227.801</v>
+        <v>45.87</v>
       </c>
       <c r="I37" t="n">
-        <v>366.673</v>
+        <v>200.859</v>
       </c>
       <c r="J37" t="n">
-        <v>463.179</v>
+        <v>308.24178665693</v>
       </c>
       <c r="K37" t="n">
-        <v>459.545</v>
+        <v>334.712612593961</v>
       </c>
     </row>
     <row r="38">
@@ -1498,36 +1339,647 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>574.301</v>
+      </c>
+      <c r="D38" t="n">
+        <v>585.447</v>
+      </c>
+      <c r="E38" t="n">
+        <v>597.803</v>
+      </c>
+      <c r="F38" t="n">
+        <v>566.6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>107.201</v>
+      </c>
+      <c r="H38" t="n">
+        <v>153.671</v>
+      </c>
+      <c r="I38" t="n">
+        <v>366.029</v>
+      </c>
+      <c r="J38" t="n">
+        <v>529.515</v>
+      </c>
+      <c r="K38" t="n">
+        <v>586.16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>46459.207</v>
+      </c>
+      <c r="D39" t="n">
+        <v>46675.98</v>
+      </c>
+      <c r="E39" t="n">
+        <v>48966.068</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48061.7</v>
+      </c>
+      <c r="G39" t="n">
+        <v>13952.619</v>
+      </c>
+      <c r="H39" t="n">
+        <v>18293.477</v>
+      </c>
+      <c r="I39" t="n">
+        <v>33573.32</v>
+      </c>
+      <c r="J39" t="n">
+        <v>42840.828</v>
+      </c>
+      <c r="K39" t="n">
+        <v>46039.515</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>11764.684</v>
+      </c>
+      <c r="D40" t="n">
+        <v>12260.961</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11952.945</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12183.9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2027.749</v>
+      </c>
+      <c r="H40" t="n">
+        <v>816.227</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3455.282</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6726.311</v>
+      </c>
+      <c r="K40" t="n">
+        <v>7951.807</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>15505.744</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15633.303</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16082.513</v>
+      </c>
+      <c r="F41" t="n">
+        <v>16381.9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2612.223</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2259.032</v>
+      </c>
+      <c r="I41" t="n">
+        <v>11567.835</v>
+      </c>
+      <c r="J41" t="n">
+        <v>13771.831</v>
+      </c>
+      <c r="K41" t="n">
+        <v>14854.886</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>681.191</v>
+      </c>
+      <c r="D42" t="n">
+        <v>550.013</v>
+      </c>
+      <c r="E42" t="n">
+        <v>576.227</v>
+      </c>
+      <c r="F42" t="n">
+        <v>577.1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>127.276</v>
+      </c>
+      <c r="H42" t="n">
+        <v>227.801</v>
+      </c>
+      <c r="I42" t="n">
+        <v>366.673</v>
+      </c>
+      <c r="J42" t="n">
+        <v>463.179</v>
+      </c>
+      <c r="K42" t="n">
+        <v>459.545</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>South Asia (UNWTO total)</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C43" t="n">
         <v>1422.361</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D43" t="n">
         <v>1481.042</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E43" t="n">
         <v>1570.362</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F43" t="n">
         <v>1670.5</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G43" t="n">
         <v>384.746</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H43" t="n">
         <v>528.2569999999999</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I43" t="n">
         <v>1440.26</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J43" t="n">
         <v>2016.472</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K43" t="n">
         <v>2496.501</v>
       </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_arrivals_by_transport_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>88747</v>
+      </c>
+      <c r="D50" t="n">
+        <v>94671</v>
+      </c>
+      <c r="E50" t="n">
+        <v>99763</v>
+      </c>
+      <c r="F50" t="n">
+        <v>102244</v>
+      </c>
+      <c r="G50" t="n">
+        <v>26432</v>
+      </c>
+      <c r="H50" t="n">
+        <v>34307</v>
+      </c>
+      <c r="I50" t="n">
+        <v>73226</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6420</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6635</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6422</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6684</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2412</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3110</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6028</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>60343.7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>66639.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>67545.7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>68691.89999999999</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13657.664</v>
+      </c>
+      <c r="H52" t="n">
+        <v>24431.89</v>
+      </c>
+      <c r="I52" t="n">
+        <v>59307.849</v>
+      </c>
+      <c r="J52" t="n">
+        <v>69564.23140752919</v>
+      </c>
+      <c r="K52" t="n">
+        <v>77119.7871470598</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>13335.9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>13263.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>13250.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>13096.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5052.128</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6521.955</v>
+      </c>
+      <c r="I53" t="n">
+        <v>11199.208</v>
+      </c>
+      <c r="J53" t="n">
+        <v>13745.4613453271</v>
+      </c>
+      <c r="K53" t="n">
+        <v>14535.4190698515</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1635.4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1965.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2012.1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1720.8</v>
+      </c>
+      <c r="G54" t="n">
+        <v>223.311</v>
+      </c>
+      <c r="H54" t="n">
+        <v>226.957</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1152.225</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1859.35721985221</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2104.09063755124</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>30483.8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>34116.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>37229.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>39396.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9277</v>
+      </c>
+      <c r="H55" t="n">
+        <v>10600</v>
+      </c>
+      <c r="I55" t="n">
+        <v>29042</v>
+      </c>
+      <c r="J55" t="n">
+        <v>35814</v>
+      </c>
+      <c r="K55" t="n">
+        <v>38587</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1701.5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1633.7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1701</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1727.9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>348</v>
+      </c>
+      <c r="H56" t="n">
+        <v>472</v>
+      </c>
+      <c r="I56" t="n">
+        <v>703</v>
+      </c>
+      <c r="J56" t="n">
+        <v>885</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>46940.691</v>
+      </c>
+      <c r="D57" t="n">
+        <v>48734.483</v>
+      </c>
+      <c r="E57" t="n">
+        <v>50695.476</v>
+      </c>
+      <c r="F57" t="n">
+        <v>50253.1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>10932.649</v>
+      </c>
+      <c r="H57" t="n">
+        <v>13735.582</v>
+      </c>
+      <c r="I57" t="n">
+        <v>31938.417</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>28913.34</v>
+      </c>
+      <c r="D58" t="n">
+        <v>27920.526</v>
+      </c>
+      <c r="E58" t="n">
+        <v>28489.235</v>
+      </c>
+      <c r="F58" t="n">
+        <v>28651.9</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8221.689</v>
+      </c>
+      <c r="H58" t="n">
+        <v>8290.293</v>
+      </c>
+      <c r="I58" t="n">
+        <v>18383.956</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>553.457</v>
+      </c>
+      <c r="D59" t="n">
+        <v>531.737</v>
+      </c>
+      <c r="E59" t="n">
+        <v>561.207</v>
+      </c>
+      <c r="F59" t="n">
+        <v>536.7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>57.676</v>
+      </c>
+      <c r="H59" t="n">
+        <v>74.578</v>
+      </c>
+      <c r="I59" t="n">
+        <v>547.312</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,32 +450,40 @@
       <c r="H3" t="n">
         <v>2022</v>
       </c>
+      <c r="I3" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.99537</v>
+        <v>1.99315</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9861</v>
+        <v>1.99379</v>
       </c>
       <c r="D4" t="n">
-        <v>3.97426</v>
+        <v>2.00237</v>
       </c>
       <c r="E4" t="n">
-        <v>3.85284</v>
+        <v>2.01469</v>
       </c>
       <c r="F4" t="n">
-        <v>2.35015</v>
+        <v>1.00336</v>
       </c>
       <c r="G4" t="n">
-        <v>2.16005</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>0.98237</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.41368</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.577</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -502,6 +510,7 @@
         <v>5.50139</v>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -520,196 +529,174 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8.4518</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.487259999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.539569999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.61168</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.76612</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.62444</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.462899999999999</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>2.88621</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>2.9547</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>2.9604</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>3.01889</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>2.1474</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>2.76457</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>2.96775</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>UN_Tourism_inbound_arrivals_by_purpose_12_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>geo</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2017</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2019</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2020</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2024</v>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_accommodation_12_2025</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
+          <t>series</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5703.7</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="n">
-        <v>5706.7</v>
+        <v>2017</v>
       </c>
       <c r="E14" t="n">
-        <v>5636.8</v>
+        <v>2018</v>
       </c>
       <c r="F14" t="n">
-        <v>6112.7</v>
+        <v>2019</v>
       </c>
       <c r="G14" t="n">
-        <v>1565.465</v>
+        <v>2020</v>
       </c>
       <c r="H14" t="n">
-        <v>2270.304</v>
+        <v>2021</v>
       </c>
       <c r="I14" t="n">
-        <v>4952.511</v>
+        <v>2022</v>
       </c>
       <c r="J14" t="n">
-        <v>4973.06749958168</v>
+        <v>2023</v>
       </c>
       <c r="K14" t="n">
-        <v>5253.19541783694</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>69611.3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>76161.7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>77171.60000000001</v>
-      </c>
-      <c r="F15" t="n">
-        <v>77396.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>17367.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>28910.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>66706.8</v>
-      </c>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>80195.98247311771</v>
+        <v>7087</v>
       </c>
       <c r="K15" t="n">
-        <v>88506.1014367087</v>
+        <v>6612</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14649</v>
+        <v>50297</v>
       </c>
       <c r="D16" t="n">
-        <v>14537</v>
+        <v>53334</v>
       </c>
       <c r="E16" t="n">
-        <v>14377.6</v>
+        <v>54146</v>
       </c>
       <c r="F16" t="n">
-        <v>14875.2</v>
+        <v>55982</v>
       </c>
       <c r="G16" t="n">
-        <v>6766</v>
+        <v>10894</v>
       </c>
       <c r="H16" t="n">
-        <v>8326</v>
+        <v>20451</v>
       </c>
       <c r="I16" t="n">
-        <v>10259</v>
+        <v>49568</v>
       </c>
       <c r="J16" t="n">
-        <v>11321</v>
+        <v>68632.25</v>
       </c>
       <c r="K16" t="n">
-        <v>11247</v>
+        <v>73766.842</v>
       </c>
     </row>
     <row r="17">
@@ -720,69 +707,75 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>70275</v>
+        <v>43405</v>
       </c>
       <c r="D17" t="n">
-        <v>75394</v>
+        <v>45365</v>
       </c>
       <c r="E17" t="n">
-        <v>78850.89999999999</v>
+        <v>46825</v>
       </c>
       <c r="F17" t="n">
-        <v>80523.5</v>
+        <v>47377</v>
       </c>
       <c r="G17" t="n">
-        <v>18423</v>
+        <v>14387.445</v>
       </c>
       <c r="H17" t="n">
-        <v>18562</v>
+        <v>22915.817</v>
       </c>
       <c r="I17" t="n">
-        <v>39552</v>
+        <v>49193.898</v>
       </c>
       <c r="J17" t="n">
-        <v>45929</v>
+        <v>61506.242</v>
       </c>
       <c r="K17" t="n">
-        <v>46478</v>
+        <v>67311.56600000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6863.27243246694</v>
+        <v>18875</v>
       </c>
       <c r="D18" t="n">
-        <v>6963.91479812882</v>
+        <v>21394</v>
       </c>
       <c r="E18" t="n">
-        <v>6979.49317509289</v>
+        <v>21764</v>
       </c>
       <c r="F18" t="n">
-        <v>6988</v>
+        <v>22614</v>
       </c>
       <c r="G18" t="n">
-        <v>1625.1</v>
+        <v>9556.136</v>
       </c>
       <c r="H18" t="n">
-        <v>1128.5</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>15267.289</v>
+      </c>
+      <c r="I18" t="n">
+        <v>21306.849</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23167.132</v>
+      </c>
+      <c r="K18" t="n">
+        <v>23243.383</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -792,26 +785,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31266.1315675331</v>
+        <v>29588.417504</v>
       </c>
       <c r="D19" t="n">
-        <v>31941.6092018712</v>
+        <v>29802</v>
       </c>
       <c r="E19" t="n">
-        <v>32903.8678249071</v>
+        <v>30391</v>
       </c>
       <c r="F19" t="n">
-        <v>33405</v>
+        <v>30699</v>
       </c>
       <c r="G19" t="n">
-        <v>5968.8</v>
+        <v>5339</v>
       </c>
       <c r="H19" t="n">
-        <v>8046.4</v>
+        <v>4404</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -820,7 +813,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
+          <t>UN_Tourism_inbound_arrivals_by_purpose_12_2025</t>
         </is>
       </c>
     </row>
@@ -866,820 +859,810 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>262.6</v>
+        <v>16210.1</v>
       </c>
       <c r="D26" t="n">
-        <v>271.2</v>
+        <v>16793.1</v>
       </c>
       <c r="E26" t="n">
-        <v>272.5</v>
+        <v>17439</v>
       </c>
       <c r="F26" t="n">
-        <v>284.2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>73.902</v>
-      </c>
-      <c r="H26" t="n">
-        <v>62.351</v>
-      </c>
-      <c r="I26" t="n">
-        <v>195.241</v>
-      </c>
+        <v>18260.8</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>234.123</v>
+        <v>16429</v>
       </c>
       <c r="K26" t="n">
-        <v>252.546</v>
+        <v>17963</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3508.5</v>
+        <v>5703.7</v>
       </c>
       <c r="D27" t="n">
-        <v>3889.5</v>
+        <v>5706.7</v>
       </c>
       <c r="E27" t="n">
-        <v>4084.7</v>
+        <v>5636.8</v>
       </c>
       <c r="F27" t="n">
-        <v>4142</v>
+        <v>6112.7</v>
       </c>
       <c r="G27" t="n">
-        <v>797.258</v>
+        <v>1565.465</v>
       </c>
       <c r="H27" t="n">
-        <v>873.521</v>
+        <v>2270.304</v>
       </c>
       <c r="I27" t="n">
-        <v>3045.921</v>
+        <v>4952.511</v>
       </c>
       <c r="J27" t="n">
-        <v>3800.781</v>
+        <v>4973.06749958168</v>
       </c>
       <c r="K27" t="n">
-        <v>4250.701</v>
+        <v>5253.19541783694</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3488.9</v>
+        <v>69611.3</v>
       </c>
       <c r="D28" t="n">
-        <v>3888.7</v>
+        <v>76161.7</v>
       </c>
       <c r="E28" t="n">
-        <v>3964.8</v>
+        <v>77171.60000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>3962.6</v>
+        <v>77396.5</v>
       </c>
       <c r="G28" t="n">
-        <v>579.165</v>
+        <v>17367.6</v>
       </c>
       <c r="H28" t="n">
-        <v>313.499</v>
+        <v>28910.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1202.564</v>
+        <v>66706.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2329.21</v>
+        <v>80195.98247311771</v>
       </c>
       <c r="K28" t="n">
-        <v>2700.05</v>
+        <v>88506.1014367087</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Europe (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26568.4</v>
+        <v>14649</v>
       </c>
       <c r="D29" t="n">
-        <v>27635.3</v>
+        <v>14537</v>
       </c>
       <c r="E29" t="n">
-        <v>28681.2</v>
+        <v>14377.6</v>
       </c>
       <c r="F29" t="n">
-        <v>29489.2</v>
+        <v>14875.2</v>
       </c>
       <c r="G29" t="n">
-        <v>10594.872</v>
+        <v>6766</v>
       </c>
       <c r="H29" t="n">
-        <v>10047.669</v>
+        <v>8326</v>
       </c>
       <c r="I29" t="n">
-        <v>23043.584</v>
+        <v>10259</v>
       </c>
       <c r="J29" t="n">
-        <v>27129.43</v>
+        <v>11321</v>
       </c>
       <c r="K29" t="n">
-        <v>28794.97</v>
+        <v>11247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>673.1</v>
+        <v>70275</v>
       </c>
       <c r="D30" t="n">
-        <v>660.8</v>
+        <v>75394</v>
       </c>
       <c r="E30" t="n">
-        <v>636</v>
+        <v>78850.89999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>604.3</v>
+        <v>80523.5</v>
       </c>
       <c r="G30" t="n">
-        <v>95.996</v>
+        <v>18423</v>
       </c>
       <c r="H30" t="n">
-        <v>165.966</v>
+        <v>18562</v>
       </c>
       <c r="I30" t="n">
-        <v>404.707</v>
+        <v>39552</v>
       </c>
       <c r="J30" t="n">
-        <v>483.885</v>
+        <v>45929</v>
       </c>
       <c r="K30" t="n">
-        <v>489.689</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>South Asia (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>231.2</v>
+        <v>1628</v>
       </c>
       <c r="D31" t="n">
-        <v>268.7</v>
+        <v>1935.7</v>
       </c>
       <c r="E31" t="n">
-        <v>289.7</v>
+        <v>2002.4</v>
       </c>
       <c r="F31" t="n">
-        <v>307.1</v>
+        <v>1890.7</v>
       </c>
       <c r="G31" t="n">
-        <v>55.831</v>
+        <v>498.255</v>
       </c>
       <c r="H31" t="n">
-        <v>42.545</v>
+        <v>573.603</v>
       </c>
       <c r="I31" t="n">
-        <v>160.263</v>
+        <v>1142.118</v>
       </c>
       <c r="J31" t="n">
-        <v>232.398</v>
+        <v>1326</v>
       </c>
       <c r="K31" t="n">
-        <v>278.701</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1243</v>
+        <v>33451</v>
       </c>
       <c r="D32" t="n">
-        <v>1314.3</v>
+        <v>37355.3</v>
       </c>
       <c r="E32" t="n">
-        <v>1235.9</v>
+        <v>39310.3</v>
       </c>
       <c r="F32" t="n">
-        <v>1340</v>
+        <v>43133.7</v>
       </c>
       <c r="G32" t="n">
-        <v>262.945</v>
+        <v>23785.3</v>
       </c>
       <c r="H32" t="n">
-        <v>250.284</v>
+        <v>31286.8</v>
       </c>
       <c r="I32" t="n">
-        <v>830.221</v>
+        <v>37183.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1025.13128294283</v>
+        <v>41926</v>
       </c>
       <c r="K32" t="n">
-        <v>1297.90576947888</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4573.9</v>
+        <v>6863.27243246694</v>
       </c>
       <c r="D33" t="n">
-        <v>5866</v>
+        <v>6963.91479812882</v>
       </c>
       <c r="E33" t="n">
-        <v>6370.5</v>
+        <v>6979.49317509289</v>
       </c>
       <c r="F33" t="n">
-        <v>7092.1</v>
+        <v>6988</v>
       </c>
       <c r="G33" t="n">
-        <v>1320.48</v>
+        <v>1625.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1867.265</v>
-      </c>
-      <c r="I33" t="n">
-        <v>6359.413</v>
-      </c>
-      <c r="J33" t="n">
-        <v>8470.624000010759</v>
-      </c>
-      <c r="K33" t="n">
-        <v>9428.970904708071</v>
-      </c>
+        <v>1128.5</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1904.7</v>
+        <v>31266.1315675331</v>
       </c>
       <c r="D34" t="n">
-        <v>2299</v>
+        <v>31941.6092018712</v>
       </c>
       <c r="E34" t="n">
-        <v>2560.7</v>
+        <v>32903.8678249071</v>
       </c>
       <c r="F34" t="n">
-        <v>2977</v>
+        <v>33405</v>
       </c>
       <c r="G34" t="n">
-        <v>562.403</v>
+        <v>5968.8</v>
       </c>
       <c r="H34" t="n">
-        <v>230.302</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1086.684</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2360.18863897558</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2817.03795662791</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Europe (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>67047.39999999999</v>
-      </c>
-      <c r="D35" t="n">
-        <v>71695.89999999999</v>
-      </c>
-      <c r="E35" t="n">
-        <v>71903.89999999999</v>
-      </c>
-      <c r="F35" t="n">
-        <v>71377.8</v>
-      </c>
-      <c r="G35" t="n">
-        <v>16676.276</v>
-      </c>
-      <c r="H35" t="n">
-        <v>28505.919</v>
-      </c>
-      <c r="I35" t="n">
-        <v>62765.346</v>
-      </c>
-      <c r="J35" t="n">
-        <v>72386.9099346476</v>
-      </c>
-      <c r="K35" t="n">
-        <v>79114.75530078731</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Middle East (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>386.7</v>
-      </c>
-      <c r="D36" t="n">
-        <v>466.4</v>
-      </c>
-      <c r="E36" t="n">
-        <v>416.3</v>
-      </c>
-      <c r="F36" t="n">
-        <v>424.7</v>
-      </c>
-      <c r="G36" t="n">
-        <v>76.34399999999999</v>
-      </c>
-      <c r="H36" t="n">
-        <v>281.162</v>
-      </c>
-      <c r="I36" t="n">
-        <v>416.759</v>
-      </c>
-      <c r="J36" t="n">
-        <v>617.95432944935</v>
-      </c>
-      <c r="K36" t="n">
-        <v>765.914310277042</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>South Asia (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>159.3</v>
-      </c>
-      <c r="D37" t="n">
-        <v>227</v>
-      </c>
-      <c r="E37" t="n">
-        <v>321</v>
-      </c>
-      <c r="F37" t="n">
-        <v>297.5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>34.655</v>
-      </c>
-      <c r="H37" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I37" t="n">
-        <v>200.859</v>
-      </c>
-      <c r="J37" t="n">
-        <v>308.24178665693</v>
-      </c>
-      <c r="K37" t="n">
-        <v>334.712612593961</v>
-      </c>
+        <v>8046.4</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Africa (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>574.301</v>
-      </c>
-      <c r="D38" t="n">
-        <v>585.447</v>
-      </c>
-      <c r="E38" t="n">
-        <v>597.803</v>
-      </c>
-      <c r="F38" t="n">
-        <v>566.6</v>
-      </c>
-      <c r="G38" t="n">
-        <v>107.201</v>
-      </c>
-      <c r="H38" t="n">
-        <v>153.671</v>
-      </c>
-      <c r="I38" t="n">
-        <v>366.029</v>
-      </c>
-      <c r="J38" t="n">
-        <v>529.515</v>
-      </c>
-      <c r="K38" t="n">
-        <v>586.16</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Americas (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>46459.207</v>
-      </c>
-      <c r="D39" t="n">
-        <v>46675.98</v>
-      </c>
-      <c r="E39" t="n">
-        <v>48966.068</v>
-      </c>
-      <c r="F39" t="n">
-        <v>48061.7</v>
-      </c>
-      <c r="G39" t="n">
-        <v>13952.619</v>
-      </c>
-      <c r="H39" t="n">
-        <v>18293.477</v>
-      </c>
-      <c r="I39" t="n">
-        <v>33573.32</v>
-      </c>
-      <c r="J39" t="n">
-        <v>42840.828</v>
-      </c>
-      <c r="K39" t="n">
-        <v>46039.515</v>
+          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>series</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11764.684</v>
+        <v>2016</v>
       </c>
       <c r="D40" t="n">
-        <v>12260.961</v>
+        <v>2017</v>
       </c>
       <c r="E40" t="n">
-        <v>11952.945</v>
+        <v>2018</v>
       </c>
       <c r="F40" t="n">
-        <v>12183.9</v>
+        <v>2019</v>
       </c>
       <c r="G40" t="n">
-        <v>2027.749</v>
+        <v>2020</v>
       </c>
       <c r="H40" t="n">
-        <v>816.227</v>
+        <v>2021</v>
       </c>
       <c r="I40" t="n">
-        <v>3455.282</v>
+        <v>2022</v>
       </c>
       <c r="J40" t="n">
-        <v>6726.311</v>
+        <v>2023</v>
       </c>
       <c r="K40" t="n">
-        <v>7951.807</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Europe (UNWTO total)</t>
+          <t>Africa (UNWTO total)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>15505.744</v>
+        <v>124.1</v>
       </c>
       <c r="D41" t="n">
-        <v>15633.303</v>
+        <v>132.5</v>
       </c>
       <c r="E41" t="n">
-        <v>16082.513</v>
+        <v>143.4</v>
       </c>
       <c r="F41" t="n">
-        <v>16381.9</v>
+        <v>165.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2612.223</v>
+        <v>30</v>
       </c>
       <c r="H41" t="n">
-        <v>2259.032</v>
+        <v>39</v>
       </c>
       <c r="I41" t="n">
-        <v>11567.835</v>
+        <v>112</v>
       </c>
       <c r="J41" t="n">
-        <v>13771.831</v>
+        <v>216</v>
       </c>
       <c r="K41" t="n">
-        <v>14854.886</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>Americas (UNWTO total)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>681.191</v>
+        <v>14587.7</v>
       </c>
       <c r="D42" t="n">
-        <v>550.013</v>
+        <v>15150</v>
       </c>
       <c r="E42" t="n">
-        <v>576.227</v>
+        <v>15405.4</v>
       </c>
       <c r="F42" t="n">
-        <v>577.1</v>
+        <v>16085</v>
       </c>
       <c r="G42" t="n">
-        <v>127.276</v>
+        <v>2130</v>
       </c>
       <c r="H42" t="n">
-        <v>227.801</v>
+        <v>2280</v>
       </c>
       <c r="I42" t="n">
-        <v>366.673</v>
+        <v>9776</v>
       </c>
       <c r="J42" t="n">
-        <v>463.179</v>
+        <v>13859</v>
       </c>
       <c r="K42" t="n">
-        <v>459.545</v>
+        <v>15051</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2182.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2149.3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2176.2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>299</v>
+      </c>
+      <c r="H43" t="n">
+        <v>129</v>
+      </c>
+      <c r="I43" t="n">
+        <v>567</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1154</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2875.8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2974.9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2943.9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3150.3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>392</v>
+      </c>
+      <c r="H44" t="n">
+        <v>460</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1998</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2503</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>121</v>
+      </c>
+      <c r="G45" t="n">
+        <v>26</v>
+      </c>
+      <c r="H45" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" t="n">
+        <v>76</v>
+      </c>
+      <c r="J45" t="n">
+        <v>111</v>
+      </c>
+      <c r="K45" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>South Asia (UNWTO total)</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>1422.361</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1481.042</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1570.362</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1670.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>384.746</v>
-      </c>
-      <c r="H43" t="n">
-        <v>528.2569999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1440.26</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2016.472</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2496.501</v>
+      <c r="C46" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>446.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>84</v>
+      </c>
+      <c r="H46" t="n">
+        <v>114</v>
+      </c>
+      <c r="I46" t="n">
+        <v>295</v>
+      </c>
+      <c r="J46" t="n">
+        <v>502</v>
+      </c>
+      <c r="K46" t="n">
+        <v>523</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UN_Tourism_inbound_arrivals_by_transport_12_2025</t>
-        </is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1243</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1314.3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1235.9</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1340</v>
+      </c>
+      <c r="G47" t="n">
+        <v>262.945</v>
+      </c>
+      <c r="H47" t="n">
+        <v>250.284</v>
+      </c>
+      <c r="I47" t="n">
+        <v>830.221</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1025.13128294283</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1297.90576947888</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4573.9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5866</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6370.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7092.1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1320.48</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1867.265</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6359.413</v>
+      </c>
+      <c r="J48" t="n">
+        <v>8470.624000010759</v>
+      </c>
+      <c r="K48" t="n">
+        <v>9428.970904708071</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>series</t>
+          <t>East Asia and the Pacific (UNWTO total)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2016</v>
+        <v>1904.7</v>
       </c>
       <c r="D49" t="n">
-        <v>2017</v>
+        <v>2299</v>
       </c>
       <c r="E49" t="n">
-        <v>2018</v>
+        <v>2560.7</v>
       </c>
       <c r="F49" t="n">
-        <v>2019</v>
+        <v>2977</v>
       </c>
       <c r="G49" t="n">
-        <v>2020</v>
+        <v>562.403</v>
       </c>
       <c r="H49" t="n">
-        <v>2021</v>
+        <v>230.302</v>
       </c>
       <c r="I49" t="n">
-        <v>2022</v>
+        <v>1086.684</v>
       </c>
       <c r="J49" t="n">
-        <v>2023</v>
+        <v>2360.18863897558</v>
       </c>
       <c r="K49" t="n">
-        <v>2024</v>
+        <v>2817.03795662791</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>Europe (UNWTO total)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>88747</v>
+        <v>67047.39999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>94671</v>
+        <v>71695.89999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>99763</v>
+        <v>71903.89999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>102244</v>
+        <v>71377.8</v>
       </c>
       <c r="G50" t="n">
-        <v>26432</v>
+        <v>16676.276</v>
       </c>
       <c r="H50" t="n">
-        <v>34307</v>
+        <v>28505.919</v>
       </c>
       <c r="I50" t="n">
-        <v>73226</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+        <v>62765.346</v>
+      </c>
+      <c r="J50" t="n">
+        <v>72386.9099346476</v>
+      </c>
+      <c r="K50" t="n">
+        <v>79114.75530078731</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+          <t>Middle East (UNWTO total)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6420</v>
+        <v>386.7</v>
       </c>
       <c r="D51" t="n">
-        <v>6635</v>
+        <v>466.4</v>
       </c>
       <c r="E51" t="n">
-        <v>6422</v>
+        <v>416.3</v>
       </c>
       <c r="F51" t="n">
-        <v>6684</v>
+        <v>424.7</v>
       </c>
       <c r="G51" t="n">
-        <v>2412</v>
+        <v>76.34399999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>3110</v>
+        <v>281.162</v>
       </c>
       <c r="I51" t="n">
-        <v>6028</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+        <v>416.759</v>
+      </c>
+      <c r="J51" t="n">
+        <v>617.95432944935</v>
+      </c>
+      <c r="K51" t="n">
+        <v>765.914310277042</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1689,262 +1672,270 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>South Asia (UNWTO total)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>60343.7</v>
+        <v>159.3</v>
       </c>
       <c r="D52" t="n">
-        <v>66639.5</v>
+        <v>227</v>
       </c>
       <c r="E52" t="n">
-        <v>67545.7</v>
+        <v>321</v>
       </c>
       <c r="F52" t="n">
-        <v>68691.89999999999</v>
+        <v>297.5</v>
       </c>
       <c r="G52" t="n">
-        <v>13657.664</v>
+        <v>34.655</v>
       </c>
       <c r="H52" t="n">
-        <v>24431.89</v>
+        <v>45.87</v>
       </c>
       <c r="I52" t="n">
-        <v>59307.849</v>
+        <v>200.859</v>
       </c>
       <c r="J52" t="n">
-        <v>69564.23140752919</v>
+        <v>308.24178665693</v>
       </c>
       <c r="K52" t="n">
-        <v>77119.7871470598</v>
+        <v>334.712612593961</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+          <t>Africa (UNWTO total)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13335.9</v>
+        <v>25.6</v>
       </c>
       <c r="D53" t="n">
-        <v>13263.4</v>
+        <v>27.6</v>
       </c>
       <c r="E53" t="n">
-        <v>13250.6</v>
+        <v>32.7</v>
       </c>
       <c r="F53" t="n">
-        <v>13096.5</v>
+        <v>33.6</v>
       </c>
       <c r="G53" t="n">
-        <v>5052.128</v>
+        <v>8.821999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>6521.955</v>
+        <v>14.051</v>
       </c>
       <c r="I53" t="n">
-        <v>11199.208</v>
+        <v>25.231</v>
       </c>
       <c r="J53" t="n">
-        <v>13745.4613453271</v>
+        <v>25.175</v>
       </c>
       <c r="K53" t="n">
-        <v>14535.4190698515</v>
+        <v>24.723</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+          <t>Americas (UNWTO total)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1635.4</v>
+        <v>31490.2</v>
       </c>
       <c r="D54" t="n">
-        <v>1965.7</v>
+        <v>35340.2</v>
       </c>
       <c r="E54" t="n">
-        <v>2012.1</v>
+        <v>38247.9</v>
       </c>
       <c r="F54" t="n">
-        <v>1720.8</v>
+        <v>41938.6</v>
       </c>
       <c r="G54" t="n">
-        <v>223.311</v>
+        <v>6980.967</v>
       </c>
       <c r="H54" t="n">
-        <v>226.957</v>
+        <v>12505.975</v>
       </c>
       <c r="I54" t="n">
-        <v>1152.225</v>
+        <v>17575.432</v>
       </c>
       <c r="J54" t="n">
-        <v>1859.35721985221</v>
+        <v>17057.584</v>
       </c>
       <c r="K54" t="n">
-        <v>2104.09063755124</v>
+        <v>18253.981</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>East Asia and the Pacific (UNWTO total)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>30483.8</v>
+        <v>370.1</v>
       </c>
       <c r="D55" t="n">
-        <v>34116.5</v>
+        <v>411.6</v>
       </c>
       <c r="E55" t="n">
-        <v>37229.5</v>
+        <v>437.4</v>
       </c>
       <c r="F55" t="n">
-        <v>39396.2</v>
+        <v>437.2</v>
       </c>
       <c r="G55" t="n">
-        <v>9277</v>
+        <v>102.894</v>
       </c>
       <c r="H55" t="n">
-        <v>10600</v>
+        <v>54.699</v>
       </c>
       <c r="I55" t="n">
-        <v>29042</v>
+        <v>142.697</v>
       </c>
       <c r="J55" t="n">
-        <v>35814</v>
+        <v>257.555</v>
       </c>
       <c r="K55" t="n">
-        <v>38587</v>
+        <v>312.311</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+          <t>Europe (UNWTO total)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1701.5</v>
+        <v>1832.9</v>
       </c>
       <c r="D56" t="n">
-        <v>1633.7</v>
+        <v>1961.7</v>
       </c>
       <c r="E56" t="n">
-        <v>1701</v>
+        <v>2056.6</v>
       </c>
       <c r="F56" t="n">
-        <v>1727.9</v>
+        <v>2105.1</v>
       </c>
       <c r="G56" t="n">
-        <v>348</v>
+        <v>559.011</v>
       </c>
       <c r="H56" t="n">
-        <v>472</v>
+        <v>963.153</v>
       </c>
       <c r="I56" t="n">
-        <v>703</v>
+        <v>2103.138</v>
       </c>
       <c r="J56" t="n">
-        <v>885</v>
+        <v>1938.865</v>
       </c>
       <c r="K56" t="n">
-        <v>1275</v>
+        <v>1788.665</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>Middle East (UNWTO total)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>46940.691</v>
+        <v>45.8</v>
       </c>
       <c r="D57" t="n">
-        <v>48734.483</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>50695.476</v>
+        <v>61</v>
       </c>
       <c r="F57" t="n">
-        <v>50253.1</v>
+        <v>53.8</v>
       </c>
       <c r="G57" t="n">
-        <v>10932.649</v>
+        <v>27.265</v>
       </c>
       <c r="H57" t="n">
-        <v>13735.582</v>
+        <v>77.745</v>
       </c>
       <c r="I57" t="n">
-        <v>31938.417</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+        <v>94.98</v>
+      </c>
+      <c r="J57" t="n">
+        <v>81.999</v>
+      </c>
+      <c r="K57" t="n">
+        <v>70.41</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+          <t>South Asia (UNWTO total)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>28913.34</v>
+        <v>23.9</v>
       </c>
       <c r="D58" t="n">
-        <v>27920.526</v>
+        <v>26.3</v>
       </c>
       <c r="E58" t="n">
-        <v>28489.235</v>
+        <v>32.4</v>
       </c>
       <c r="F58" t="n">
-        <v>28651.9</v>
+        <v>33</v>
       </c>
       <c r="G58" t="n">
-        <v>8221.689</v>
+        <v>7.483</v>
       </c>
       <c r="H58" t="n">
-        <v>8290.293</v>
+        <v>44.228</v>
       </c>
       <c r="I58" t="n">
-        <v>18383.956</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+        <v>40.493</v>
+      </c>
+      <c r="J58" t="n">
+        <v>45.088</v>
+      </c>
+      <c r="K58" t="n">
+        <v>40.784</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1954,32 +1945,997 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>574.301</v>
+      </c>
+      <c r="D59" t="n">
+        <v>585.447</v>
+      </c>
+      <c r="E59" t="n">
+        <v>597.803</v>
+      </c>
+      <c r="F59" t="n">
+        <v>566.6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>107.201</v>
+      </c>
+      <c r="H59" t="n">
+        <v>153.671</v>
+      </c>
+      <c r="I59" t="n">
+        <v>366.029</v>
+      </c>
+      <c r="J59" t="n">
+        <v>529.515</v>
+      </c>
+      <c r="K59" t="n">
+        <v>586.16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>46459.207</v>
+      </c>
+      <c r="D60" t="n">
+        <v>46675.98</v>
+      </c>
+      <c r="E60" t="n">
+        <v>48966.068</v>
+      </c>
+      <c r="F60" t="n">
+        <v>48061.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>13952.619</v>
+      </c>
+      <c r="H60" t="n">
+        <v>18293.477</v>
+      </c>
+      <c r="I60" t="n">
+        <v>33573.32</v>
+      </c>
+      <c r="J60" t="n">
+        <v>42840.828</v>
+      </c>
+      <c r="K60" t="n">
+        <v>46039.515</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>11764.684</v>
+      </c>
+      <c r="D61" t="n">
+        <v>12260.961</v>
+      </c>
+      <c r="E61" t="n">
+        <v>11952.945</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12183.9</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2027.749</v>
+      </c>
+      <c r="H61" t="n">
+        <v>816.227</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3455.282</v>
+      </c>
+      <c r="J61" t="n">
+        <v>6726.311</v>
+      </c>
+      <c r="K61" t="n">
+        <v>7951.807</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>15505.744</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15633.303</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16082.513</v>
+      </c>
+      <c r="F62" t="n">
+        <v>16381.9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2612.223</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2259.032</v>
+      </c>
+      <c r="I62" t="n">
+        <v>11567.835</v>
+      </c>
+      <c r="J62" t="n">
+        <v>13771.831</v>
+      </c>
+      <c r="K62" t="n">
+        <v>14854.886</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>681.191</v>
+      </c>
+      <c r="D63" t="n">
+        <v>550.013</v>
+      </c>
+      <c r="E63" t="n">
+        <v>576.227</v>
+      </c>
+      <c r="F63" t="n">
+        <v>577.1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>127.276</v>
+      </c>
+      <c r="H63" t="n">
+        <v>227.801</v>
+      </c>
+      <c r="I63" t="n">
+        <v>366.673</v>
+      </c>
+      <c r="J63" t="n">
+        <v>463.179</v>
+      </c>
+      <c r="K63" t="n">
+        <v>459.545</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>South Asia (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1422.361</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1481.042</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1570.362</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1670.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>384.746</v>
+      </c>
+      <c r="H64" t="n">
+        <v>528.2569999999999</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1440.26</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2016.472</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2496.501</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_arrivals_by_transport_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9802.4</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10576.8</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10372.1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10999</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1664</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1595</v>
+      </c>
+      <c r="I71" t="n">
+        <v>6669</v>
+      </c>
+      <c r="J71" t="n">
+        <v>9364</v>
+      </c>
+      <c r="K71" t="n">
+        <v>10269</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9373.4</v>
+      </c>
+      <c r="D72" t="n">
+        <v>9458.5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>9802.299999999999</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10032.9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1294</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1461</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5767</v>
+      </c>
+      <c r="J72" t="n">
+        <v>8449</v>
+      </c>
+      <c r="K72" t="n">
+        <v>9142</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C73" t="n">
+        <v>795.5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>847.9</v>
+      </c>
+      <c r="E73" t="n">
+        <v>959.5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1113.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>6</v>
+      </c>
+      <c r="I73" t="n">
+        <v>388</v>
+      </c>
+      <c r="J73" t="n">
+        <v>531</v>
+      </c>
+      <c r="K73" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>60343.7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>66639.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>67545.7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>68691.89999999999</v>
+      </c>
+      <c r="G74" t="n">
+        <v>13657.664</v>
+      </c>
+      <c r="H74" t="n">
+        <v>24431.89</v>
+      </c>
+      <c r="I74" t="n">
+        <v>59307.849</v>
+      </c>
+      <c r="J74" t="n">
+        <v>69564.23140752919</v>
+      </c>
+      <c r="K74" t="n">
+        <v>77119.7871470598</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13335.9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>13263.4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13250.6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13096.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5052.128</v>
+      </c>
+      <c r="H75" t="n">
+        <v>6521.955</v>
+      </c>
+      <c r="I75" t="n">
+        <v>11199.208</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13745.4613453271</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14535.4190698515</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1635.4</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1965.7</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2012.1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1720.8</v>
+      </c>
+      <c r="G76" t="n">
+        <v>223.311</v>
+      </c>
+      <c r="H76" t="n">
+        <v>226.957</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1152.225</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1859.35721985221</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2104.09063755124</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>30483.8</v>
+      </c>
+      <c r="D77" t="n">
+        <v>34116.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>37229.5</v>
+      </c>
+      <c r="F77" t="n">
+        <v>39396.2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>9277</v>
+      </c>
+      <c r="H77" t="n">
+        <v>10600</v>
+      </c>
+      <c r="I77" t="n">
+        <v>29042</v>
+      </c>
+      <c r="J77" t="n">
+        <v>35814</v>
+      </c>
+      <c r="K77" t="n">
+        <v>38587</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1701.5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1633.7</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1701</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1727.9</v>
+      </c>
+      <c r="G78" t="n">
+        <v>348</v>
+      </c>
+      <c r="H78" t="n">
+        <v>472</v>
+      </c>
+      <c r="I78" t="n">
+        <v>703</v>
+      </c>
+      <c r="J78" t="n">
+        <v>885</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>16878</v>
+      </c>
+      <c r="D79" t="n">
+        <v>18548</v>
+      </c>
+      <c r="E79" t="n">
+        <v>19368</v>
+      </c>
+      <c r="F79" t="n">
+        <v>19634.9</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8337.627</v>
+      </c>
+      <c r="H79" t="n">
+        <v>14602.112</v>
+      </c>
+      <c r="I79" t="n">
+        <v>21329.168</v>
+      </c>
+      <c r="J79" t="n">
+        <v>22821.343</v>
+      </c>
+      <c r="K79" t="n">
+        <v>23165.256</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>18201</v>
+      </c>
+      <c r="D80" t="n">
+        <v>20743</v>
+      </c>
+      <c r="E80" t="n">
+        <v>21944.7</v>
+      </c>
+      <c r="F80" t="n">
+        <v>25389.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>15945.909</v>
+      </c>
+      <c r="H80" t="n">
+        <v>17258.28</v>
+      </c>
+      <c r="I80" t="n">
+        <v>16996.382</v>
+      </c>
+      <c r="J80" t="n">
+        <v>19128.085</v>
+      </c>
+      <c r="K80" t="n">
+        <v>21873.498</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>46940.691</v>
+      </c>
+      <c r="D81" t="n">
+        <v>48734.483</v>
+      </c>
+      <c r="E81" t="n">
+        <v>50695.476</v>
+      </c>
+      <c r="F81" t="n">
+        <v>50253.1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>10932.649</v>
+      </c>
+      <c r="H81" t="n">
+        <v>13735.582</v>
+      </c>
+      <c r="I81" t="n">
+        <v>31938.417</v>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>28913.34</v>
+      </c>
+      <c r="D82" t="n">
+        <v>27920.526</v>
+      </c>
+      <c r="E82" t="n">
+        <v>28489.235</v>
+      </c>
+      <c r="F82" t="n">
+        <v>28651.9</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8221.689</v>
+      </c>
+      <c r="H82" t="n">
+        <v>8290.293</v>
+      </c>
+      <c r="I82" t="n">
+        <v>18383.956</v>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
         <v>553.457</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D83" t="n">
         <v>531.737</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E83" t="n">
         <v>561.207</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F83" t="n">
         <v>536.7</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G83" t="n">
         <v>57.676</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H83" t="n">
         <v>74.578</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I83" t="n">
         <v>547.312</v>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_expenditure_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="n">
+        <v>13899.963252617</v>
+      </c>
+      <c r="H90" t="n">
+        <v>15360.7697581997</v>
+      </c>
+      <c r="I90" t="n">
+        <v>31816.9121593968</v>
+      </c>
+      <c r="J90" t="n">
+        <v>45409.9218533883</v>
+      </c>
+      <c r="K90" t="n">
+        <v>49886.0324452887</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>18380.4147013811</v>
+      </c>
+      <c r="H91" t="n">
+        <v>34176.1559870135</v>
+      </c>
+      <c r="I91" t="n">
+        <v>72083.3294863503</v>
+      </c>
+      <c r="J91" t="n">
+        <v>92144.2801105462</v>
+      </c>
+      <c r="K91" t="n">
+        <v>106656.535197297</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>42423</v>
+      </c>
+      <c r="D92" t="n">
+        <v>46719</v>
+      </c>
+      <c r="E92" t="n">
+        <v>51602</v>
+      </c>
+      <c r="F92" t="n">
+        <v>51910</v>
+      </c>
+      <c r="G92" t="n">
+        <v>20316.7578071358</v>
+      </c>
+      <c r="H92" t="n">
+        <v>25354.9279185429</v>
+      </c>
+      <c r="I92" t="n">
+        <v>47100.4319500271</v>
+      </c>
+      <c r="J92" t="n">
+        <v>57919.6252057293</v>
+      </c>
+      <c r="K92" t="n">
+        <v>61433.937023306</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>23270</v>
+      </c>
+      <c r="D93" t="n">
+        <v>24619</v>
+      </c>
+      <c r="E93" t="n">
+        <v>26044</v>
+      </c>
+      <c r="F93" t="n">
+        <v>27126</v>
+      </c>
+      <c r="G93" t="n">
+        <v>12142.599224</v>
+      </c>
+      <c r="H93" t="n">
+        <v>22138.069892</v>
+      </c>
+      <c r="I93" t="n">
+        <v>31257.108743</v>
+      </c>
+      <c r="J93" t="n">
+        <v>33495.50487</v>
+      </c>
+      <c r="K93" t="n">
+        <v>36239.253442</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>228549</v>
+      </c>
+      <c r="D94" t="n">
+        <v>233758</v>
+      </c>
+      <c r="E94" t="n">
+        <v>241984</v>
+      </c>
+      <c r="F94" t="n">
+        <v>239065</v>
+      </c>
+      <c r="G94" t="n">
+        <v>84297</v>
+      </c>
+      <c r="H94" t="n">
+        <v>84506</v>
+      </c>
+      <c r="I94" t="n">
+        <v>172284</v>
+      </c>
+      <c r="J94" t="n">
+        <v>226167</v>
+      </c>
+      <c r="K94" t="n">
+        <v>251649</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,1075 +515,678 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8.4518</v>
+      </c>
       <c r="C6" t="n">
-        <v>5.49858</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>8.487259999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.539569999999999</v>
+      </c>
       <c r="E6" t="n">
-        <v>5.7128</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+        <v>8.61168</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.76612</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.62444</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.462899999999999</v>
+      </c>
       <c r="I6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>8.4518</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8.487259999999999</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8.539569999999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8.61168</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6.76612</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.62444</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8.462899999999999</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.88621</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.9547</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.9604</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.01889</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.1474</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.76457</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.96775</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UN_Tourism_accommodation_hotels_12_2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UN_Tourism_inbound_accommodation_12_2025</t>
-        </is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2.16295899222728</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.11612934692484</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>geo</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.32</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>3.28</v>
       </c>
       <c r="D14" t="n">
-        <v>2017</v>
+        <v>3.23</v>
       </c>
       <c r="E14" t="n">
-        <v>2018</v>
+        <v>3.15</v>
       </c>
       <c r="F14" t="n">
-        <v>2019</v>
+        <v>2.66625227673538</v>
       </c>
       <c r="G14" t="n">
-        <v>2020</v>
+        <v>2.84577761675779</v>
       </c>
       <c r="H14" t="n">
-        <v>2021</v>
+        <v>3.11392663439669</v>
       </c>
       <c r="I14" t="n">
-        <v>2022</v>
+        <v>3.24824041907784</v>
       </c>
       <c r="J14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2024</v>
+        <v>3.27010231370084</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.9170692431562</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.73054830287206</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.45294635004398</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.2908350305499</v>
+      </c>
       <c r="J15" t="n">
-        <v>7087</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6612</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>50297</v>
-      </c>
-      <c r="D16" t="n">
-        <v>53334</v>
-      </c>
-      <c r="E16" t="n">
-        <v>54146</v>
-      </c>
-      <c r="F16" t="n">
-        <v>55982</v>
-      </c>
-      <c r="G16" t="n">
-        <v>10894</v>
-      </c>
-      <c r="H16" t="n">
-        <v>20451</v>
-      </c>
-      <c r="I16" t="n">
-        <v>49568</v>
-      </c>
-      <c r="J16" t="n">
-        <v>68632.25</v>
-      </c>
-      <c r="K16" t="n">
-        <v>73766.842</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>43405</v>
-      </c>
-      <c r="D17" t="n">
-        <v>45365</v>
-      </c>
-      <c r="E17" t="n">
-        <v>46825</v>
-      </c>
-      <c r="F17" t="n">
-        <v>47377</v>
-      </c>
-      <c r="G17" t="n">
-        <v>14387.445</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22915.817</v>
-      </c>
-      <c r="I17" t="n">
-        <v>49193.898</v>
-      </c>
-      <c r="J17" t="n">
-        <v>61506.242</v>
-      </c>
-      <c r="K17" t="n">
-        <v>67311.56600000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>18875</v>
-      </c>
-      <c r="D18" t="n">
-        <v>21394</v>
-      </c>
-      <c r="E18" t="n">
-        <v>21764</v>
-      </c>
-      <c r="F18" t="n">
-        <v>22614</v>
-      </c>
-      <c r="G18" t="n">
-        <v>9556.136</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15267.289</v>
-      </c>
-      <c r="I18" t="n">
-        <v>21306.849</v>
-      </c>
-      <c r="J18" t="n">
-        <v>23167.132</v>
-      </c>
-      <c r="K18" t="n">
-        <v>23243.383</v>
+        <v>2.25914634146341</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>29588.417504</v>
-      </c>
-      <c r="D19" t="n">
-        <v>29802</v>
-      </c>
-      <c r="E19" t="n">
-        <v>30391</v>
-      </c>
-      <c r="F19" t="n">
-        <v>30699</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5339</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4404</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>UN_Tourism_domestic_accommodation_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>114239</v>
+      </c>
+      <c r="C22" t="n">
+        <v>115822</v>
+      </c>
+      <c r="D22" t="n">
+        <v>116500</v>
+      </c>
+      <c r="E22" t="n">
+        <v>119609</v>
+      </c>
+      <c r="F22" t="n">
+        <v>51151</v>
+      </c>
+      <c r="G22" t="n">
+        <v>90700</v>
+      </c>
+      <c r="H22" t="n">
+        <v>120038</v>
+      </c>
+      <c r="I22" t="n">
+        <v>157251.063</v>
+      </c>
+      <c r="J22" t="n">
+        <v>156540.899</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UN_Tourism_inbound_arrivals_by_purpose_12_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>geo</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2017</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2019</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2020</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2021</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>16210.1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>16793.1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>17439</v>
-      </c>
-      <c r="F26" t="n">
-        <v>18260.8</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>16429</v>
-      </c>
-      <c r="K26" t="n">
-        <v>17963</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>5703.7</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5706.7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5636.8</v>
-      </c>
-      <c r="F27" t="n">
-        <v>6112.7</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1565.465</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2270.304</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4952.511</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4973.06749958168</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5253.19541783694</v>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>99854</v>
+      </c>
+      <c r="C23" t="n">
+        <v>102260</v>
+      </c>
+      <c r="D23" t="n">
+        <v>108279</v>
+      </c>
+      <c r="E23" t="n">
+        <v>112731</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50524.471</v>
+      </c>
+      <c r="G23" t="n">
+        <v>81337.709</v>
+      </c>
+      <c r="H23" t="n">
+        <v>111063.759</v>
+      </c>
+      <c r="I23" t="n">
+        <v>121512.987</v>
+      </c>
+      <c r="J23" t="n">
+        <v>116238.947</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2632</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2864</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3002</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3190</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2590</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3197</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2731</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2487</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2527</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>69611.3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>76161.7</v>
-      </c>
-      <c r="E28" t="n">
-        <v>77171.60000000001</v>
-      </c>
-      <c r="F28" t="n">
-        <v>77396.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>17367.6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>28910.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>66706.8</v>
-      </c>
-      <c r="J28" t="n">
-        <v>80195.98247311771</v>
-      </c>
-      <c r="K28" t="n">
-        <v>88506.1014367087</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>14649</v>
-      </c>
-      <c r="D29" t="n">
-        <v>14537</v>
-      </c>
-      <c r="E29" t="n">
-        <v>14377.6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>14875.2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6766</v>
-      </c>
-      <c r="H29" t="n">
-        <v>8326</v>
-      </c>
-      <c r="I29" t="n">
-        <v>10259</v>
-      </c>
-      <c r="J29" t="n">
-        <v>11321</v>
-      </c>
-      <c r="K29" t="n">
-        <v>11247</v>
+          <t>UN_Tourism_domestic_trips_12_2025</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
-        </is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2016</v>
       </c>
       <c r="C30" t="n">
-        <v>70275</v>
+        <v>2017</v>
       </c>
       <c r="D30" t="n">
-        <v>75394</v>
+        <v>2018</v>
       </c>
       <c r="E30" t="n">
-        <v>78850.89999999999</v>
+        <v>2019</v>
       </c>
       <c r="F30" t="n">
-        <v>80523.5</v>
+        <v>2020</v>
       </c>
       <c r="G30" t="n">
-        <v>18423</v>
+        <v>2021</v>
       </c>
       <c r="H30" t="n">
-        <v>18562</v>
+        <v>2022</v>
       </c>
       <c r="I30" t="n">
-        <v>39552</v>
+        <v>2023</v>
       </c>
       <c r="J30" t="n">
-        <v>45929</v>
-      </c>
-      <c r="K30" t="n">
-        <v>46478</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
-        </is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>319315</v>
       </c>
       <c r="C31" t="n">
-        <v>1628</v>
+        <v>325808.2</v>
       </c>
       <c r="D31" t="n">
-        <v>1935.7</v>
+        <v>278060</v>
       </c>
       <c r="E31" t="n">
-        <v>2002.4</v>
+        <v>275418</v>
       </c>
       <c r="F31" t="n">
-        <v>1890.7</v>
+        <v>188372</v>
       </c>
       <c r="G31" t="n">
-        <v>498.255</v>
+        <v>244142</v>
       </c>
       <c r="H31" t="n">
-        <v>573.603</v>
+        <v>313708</v>
       </c>
       <c r="I31" t="n">
-        <v>1142.118</v>
+        <v>339757</v>
       </c>
       <c r="J31" t="n">
-        <v>1326</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1410</v>
+        <v>335689</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
-        </is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>397134</v>
       </c>
       <c r="C32" t="n">
-        <v>33451</v>
+        <v>448305</v>
       </c>
       <c r="D32" t="n">
-        <v>37355.3</v>
+        <v>446479</v>
       </c>
       <c r="E32" t="n">
-        <v>39310.3</v>
+        <v>423572</v>
       </c>
       <c r="F32" t="n">
-        <v>43133.7</v>
+        <v>250469</v>
       </c>
       <c r="G32" t="n">
-        <v>23785.3</v>
+        <v>341053</v>
       </c>
       <c r="H32" t="n">
-        <v>31286.8</v>
+        <v>353920</v>
       </c>
       <c r="I32" t="n">
-        <v>37183.4</v>
+        <v>370764</v>
       </c>
       <c r="J32" t="n">
-        <v>41926</v>
-      </c>
-      <c r="K32" t="n">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>6863.27243246694</v>
-      </c>
-      <c r="D33" t="n">
-        <v>6963.91479812882</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6979.49317509289</v>
-      </c>
-      <c r="F33" t="n">
-        <v>6988</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1625.1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1128.5</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>31266.1315675331</v>
-      </c>
-      <c r="D34" t="n">
-        <v>31941.6092018712</v>
-      </c>
-      <c r="E34" t="n">
-        <v>32903.8678249071</v>
-      </c>
-      <c r="F34" t="n">
-        <v>33405</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5968.8</v>
-      </c>
-      <c r="H34" t="n">
-        <v>8046.4</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+        <v>352441</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_accommodation_12_2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
-        </is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>7087</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6612</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>series</t>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2016</v>
+        <v>50297</v>
       </c>
       <c r="D40" t="n">
-        <v>2017</v>
+        <v>53334</v>
       </c>
       <c r="E40" t="n">
-        <v>2018</v>
+        <v>54146</v>
       </c>
       <c r="F40" t="n">
-        <v>2019</v>
+        <v>55982</v>
       </c>
       <c r="G40" t="n">
-        <v>2020</v>
+        <v>10894</v>
       </c>
       <c r="H40" t="n">
-        <v>2021</v>
+        <v>20451</v>
       </c>
       <c r="I40" t="n">
-        <v>2022</v>
+        <v>49568</v>
       </c>
       <c r="J40" t="n">
-        <v>2023</v>
+        <v>68632.25</v>
       </c>
       <c r="K40" t="n">
-        <v>2024</v>
+        <v>73766.842</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>124.1</v>
+        <v>18875</v>
       </c>
       <c r="D41" t="n">
-        <v>132.5</v>
+        <v>21394</v>
       </c>
       <c r="E41" t="n">
-        <v>143.4</v>
+        <v>21764</v>
       </c>
       <c r="F41" t="n">
-        <v>165.5</v>
+        <v>22614</v>
       </c>
       <c r="G41" t="n">
-        <v>30</v>
+        <v>9556.136</v>
       </c>
       <c r="H41" t="n">
-        <v>39</v>
+        <v>15267.289</v>
       </c>
       <c r="I41" t="n">
-        <v>112</v>
+        <v>21306.849</v>
       </c>
       <c r="J41" t="n">
-        <v>216</v>
+        <v>23167.132</v>
       </c>
       <c r="K41" t="n">
-        <v>235</v>
+        <v>23243.383</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - guests</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>14587.7</v>
+        <v>1147</v>
       </c>
       <c r="D42" t="n">
-        <v>15150</v>
+        <v>1336</v>
       </c>
       <c r="E42" t="n">
-        <v>15405.4</v>
+        <v>1514</v>
       </c>
       <c r="F42" t="n">
-        <v>16085</v>
+        <v>1626</v>
       </c>
       <c r="G42" t="n">
-        <v>2130</v>
+        <v>392</v>
       </c>
       <c r="H42" t="n">
-        <v>2280</v>
+        <v>776</v>
       </c>
       <c r="I42" t="n">
-        <v>9776</v>
+        <v>1214</v>
       </c>
       <c r="J42" t="n">
-        <v>13859</v>
+        <v>1434</v>
       </c>
       <c r="K42" t="n">
-        <v>15051</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1994</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2182.5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2149.3</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2176.2</v>
-      </c>
-      <c r="G43" t="n">
-        <v>299</v>
-      </c>
-      <c r="H43" t="n">
-        <v>129</v>
-      </c>
-      <c r="I43" t="n">
-        <v>567</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1154</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Europe (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2875.8</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2974.9</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2943.9</v>
-      </c>
-      <c r="F44" t="n">
-        <v>3150.3</v>
-      </c>
-      <c r="G44" t="n">
-        <v>392</v>
-      </c>
-      <c r="H44" t="n">
-        <v>460</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1998</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2503</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2624</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Middle East (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="D45" t="n">
-        <v>116.1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>110.1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>121</v>
-      </c>
-      <c r="G45" t="n">
-        <v>26</v>
-      </c>
-      <c r="H45" t="n">
-        <v>40</v>
-      </c>
-      <c r="I45" t="n">
-        <v>76</v>
-      </c>
-      <c r="J45" t="n">
-        <v>111</v>
-      </c>
-      <c r="K45" t="n">
-        <v>121</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>South Asia (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>274.2</v>
-      </c>
-      <c r="D46" t="n">
-        <v>327.1</v>
-      </c>
-      <c r="E46" t="n">
-        <v>380.6</v>
-      </c>
-      <c r="F46" t="n">
-        <v>446.8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>84</v>
-      </c>
-      <c r="H46" t="n">
-        <v>114</v>
-      </c>
-      <c r="I46" t="n">
-        <v>295</v>
-      </c>
-      <c r="J46" t="n">
-        <v>502</v>
-      </c>
-      <c r="K46" t="n">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Africa (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1243</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1314.3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1235.9</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G47" t="n">
-        <v>262.945</v>
-      </c>
-      <c r="H47" t="n">
-        <v>250.284</v>
-      </c>
-      <c r="I47" t="n">
-        <v>830.221</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1025.13128294283</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1297.90576947888</v>
+          <t>UN_Tourism_inbound_arrivals_by_purpose_12_2025</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>series</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4573.9</v>
+        <v>2016</v>
       </c>
       <c r="D48" t="n">
-        <v>5866</v>
+        <v>2017</v>
       </c>
       <c r="E48" t="n">
-        <v>6370.5</v>
+        <v>2018</v>
       </c>
       <c r="F48" t="n">
-        <v>7092.1</v>
+        <v>2019</v>
       </c>
       <c r="G48" t="n">
-        <v>1320.48</v>
+        <v>2020</v>
       </c>
       <c r="H48" t="n">
-        <v>1867.265</v>
+        <v>2021</v>
       </c>
       <c r="I48" t="n">
-        <v>6359.413</v>
+        <v>2022</v>
       </c>
       <c r="J48" t="n">
-        <v>8470.624000010759</v>
+        <v>2023</v>
       </c>
       <c r="K48" t="n">
-        <v>9428.970904708071</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1904.7</v>
+        <v>16210.1</v>
       </c>
       <c r="D49" t="n">
-        <v>2299</v>
+        <v>16793.1</v>
       </c>
       <c r="E49" t="n">
-        <v>2560.7</v>
+        <v>17439</v>
       </c>
       <c r="F49" t="n">
-        <v>2977</v>
-      </c>
-      <c r="G49" t="n">
-        <v>562.403</v>
-      </c>
-      <c r="H49" t="n">
-        <v>230.302</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1086.684</v>
-      </c>
+        <v>18260.8</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>2360.18863897558</v>
+        <v>16429</v>
       </c>
       <c r="K49" t="n">
-        <v>2817.03795662791</v>
+        <v>17963</v>
       </c>
     </row>
     <row r="50">
@@ -1594,35 +1197,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Europe (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67047.39999999999</v>
+        <v>5703.7</v>
       </c>
       <c r="D50" t="n">
-        <v>71695.89999999999</v>
+        <v>5706.7</v>
       </c>
       <c r="E50" t="n">
-        <v>71903.89999999999</v>
+        <v>5636.8</v>
       </c>
       <c r="F50" t="n">
-        <v>71377.8</v>
+        <v>6112.7</v>
       </c>
       <c r="G50" t="n">
-        <v>16676.276</v>
+        <v>1565.465</v>
       </c>
       <c r="H50" t="n">
-        <v>28505.919</v>
+        <v>2270.304</v>
       </c>
       <c r="I50" t="n">
-        <v>62765.346</v>
+        <v>4952.511</v>
       </c>
       <c r="J50" t="n">
-        <v>72386.9099346476</v>
+        <v>4973.06749958168</v>
       </c>
       <c r="K50" t="n">
-        <v>79114.75530078731</v>
+        <v>5253.19541783694</v>
       </c>
     </row>
     <row r="51">
@@ -1633,74 +1236,74 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>386.7</v>
+        <v>69611.3</v>
       </c>
       <c r="D51" t="n">
-        <v>466.4</v>
+        <v>76161.7</v>
       </c>
       <c r="E51" t="n">
-        <v>416.3</v>
+        <v>77171.60000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>424.7</v>
+        <v>77396.5</v>
       </c>
       <c r="G51" t="n">
-        <v>76.34399999999999</v>
+        <v>17367.6</v>
       </c>
       <c r="H51" t="n">
-        <v>281.162</v>
+        <v>28910.5</v>
       </c>
       <c r="I51" t="n">
-        <v>416.759</v>
+        <v>66706.8</v>
       </c>
       <c r="J51" t="n">
-        <v>617.95432944935</v>
+        <v>80195.98247311771</v>
       </c>
       <c r="K51" t="n">
-        <v>765.914310277042</v>
+        <v>88506.1014367087</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>South Asia (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>159.3</v>
+        <v>1628</v>
       </c>
       <c r="D52" t="n">
-        <v>227</v>
+        <v>1935.7</v>
       </c>
       <c r="E52" t="n">
-        <v>321</v>
+        <v>2002.4</v>
       </c>
       <c r="F52" t="n">
-        <v>297.5</v>
+        <v>1890.7</v>
       </c>
       <c r="G52" t="n">
-        <v>34.655</v>
+        <v>498.255</v>
       </c>
       <c r="H52" t="n">
-        <v>45.87</v>
+        <v>573.603</v>
       </c>
       <c r="I52" t="n">
-        <v>200.859</v>
+        <v>1142.118</v>
       </c>
       <c r="J52" t="n">
-        <v>308.24178665693</v>
+        <v>1326</v>
       </c>
       <c r="K52" t="n">
-        <v>334.712612593961</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="53">
@@ -1711,1011 +1314,1019 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>25.6</v>
+        <v>33451</v>
       </c>
       <c r="D53" t="n">
-        <v>27.6</v>
+        <v>37355.3</v>
       </c>
       <c r="E53" t="n">
-        <v>32.7</v>
+        <v>39310.3</v>
       </c>
       <c r="F53" t="n">
-        <v>33.6</v>
+        <v>43133.7</v>
       </c>
       <c r="G53" t="n">
-        <v>8.821999999999999</v>
+        <v>23785.3</v>
       </c>
       <c r="H53" t="n">
-        <v>14.051</v>
+        <v>31286.8</v>
       </c>
       <c r="I53" t="n">
-        <v>25.231</v>
+        <v>37183.4</v>
       </c>
       <c r="J53" t="n">
-        <v>25.175</v>
+        <v>41926</v>
       </c>
       <c r="K53" t="n">
-        <v>24.723</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Americas (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>31490.2</v>
-      </c>
-      <c r="D54" t="n">
-        <v>35340.2</v>
-      </c>
-      <c r="E54" t="n">
-        <v>38247.9</v>
-      </c>
-      <c r="F54" t="n">
-        <v>41938.6</v>
-      </c>
-      <c r="G54" t="n">
-        <v>6980.967</v>
-      </c>
-      <c r="H54" t="n">
-        <v>12505.975</v>
-      </c>
-      <c r="I54" t="n">
-        <v>17575.432</v>
-      </c>
-      <c r="J54" t="n">
-        <v>17057.584</v>
-      </c>
-      <c r="K54" t="n">
-        <v>18253.981</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>370.1</v>
-      </c>
-      <c r="D55" t="n">
-        <v>411.6</v>
-      </c>
-      <c r="E55" t="n">
-        <v>437.4</v>
-      </c>
-      <c r="F55" t="n">
-        <v>437.2</v>
-      </c>
-      <c r="G55" t="n">
-        <v>102.894</v>
-      </c>
-      <c r="H55" t="n">
-        <v>54.699</v>
-      </c>
-      <c r="I55" t="n">
-        <v>142.697</v>
-      </c>
-      <c r="J55" t="n">
-        <v>257.555</v>
-      </c>
-      <c r="K55" t="n">
-        <v>312.311</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Europe (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1832.9</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1961.7</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2056.6</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2105.1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>559.011</v>
-      </c>
-      <c r="H56" t="n">
-        <v>963.153</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2103.138</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1938.865</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1788.665</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Middle East (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="D57" t="n">
-        <v>50</v>
-      </c>
-      <c r="E57" t="n">
-        <v>61</v>
-      </c>
-      <c r="F57" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="G57" t="n">
-        <v>27.265</v>
-      </c>
-      <c r="H57" t="n">
-        <v>77.745</v>
-      </c>
-      <c r="I57" t="n">
-        <v>94.98</v>
-      </c>
-      <c r="J57" t="n">
-        <v>81.999</v>
-      </c>
-      <c r="K57" t="n">
-        <v>70.41</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>South Asia (UNWTO total)</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D58" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F58" t="n">
-        <v>33</v>
-      </c>
-      <c r="G58" t="n">
-        <v>7.483</v>
-      </c>
-      <c r="H58" t="n">
-        <v>44.228</v>
-      </c>
-      <c r="I58" t="n">
-        <v>40.493</v>
-      </c>
-      <c r="J58" t="n">
-        <v>45.088</v>
-      </c>
-      <c r="K58" t="n">
-        <v>40.784</v>
+          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Africa (UNWTO total)</t>
+          <t>series</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>574.301</v>
+        <v>2016</v>
       </c>
       <c r="D59" t="n">
-        <v>585.447</v>
+        <v>2017</v>
       </c>
       <c r="E59" t="n">
-        <v>597.803</v>
+        <v>2018</v>
       </c>
       <c r="F59" t="n">
-        <v>566.6</v>
+        <v>2019</v>
       </c>
       <c r="G59" t="n">
-        <v>107.201</v>
+        <v>2020</v>
       </c>
       <c r="H59" t="n">
-        <v>153.671</v>
+        <v>2021</v>
       </c>
       <c r="I59" t="n">
-        <v>366.029</v>
+        <v>2022</v>
       </c>
       <c r="J59" t="n">
-        <v>529.515</v>
+        <v>2023</v>
       </c>
       <c r="K59" t="n">
-        <v>586.16</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Americas (UNWTO total)</t>
+          <t>Africa (UNWTO total)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>46459.207</v>
+        <v>124.1</v>
       </c>
       <c r="D60" t="n">
-        <v>46675.98</v>
+        <v>132.5</v>
       </c>
       <c r="E60" t="n">
-        <v>48966.068</v>
+        <v>143.4</v>
       </c>
       <c r="F60" t="n">
-        <v>48061.7</v>
+        <v>165.5</v>
       </c>
       <c r="G60" t="n">
-        <v>13952.619</v>
+        <v>30</v>
       </c>
       <c r="H60" t="n">
-        <v>18293.477</v>
+        <v>39</v>
       </c>
       <c r="I60" t="n">
-        <v>33573.32</v>
+        <v>112</v>
       </c>
       <c r="J60" t="n">
-        <v>42840.828</v>
+        <v>216</v>
       </c>
       <c r="K60" t="n">
-        <v>46039.515</v>
+        <v>235</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>East Asia and the Pacific (UNWTO total)</t>
+          <t>Americas (UNWTO total)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11764.684</v>
+        <v>14587.7</v>
       </c>
       <c r="D61" t="n">
-        <v>12260.961</v>
+        <v>15150</v>
       </c>
       <c r="E61" t="n">
-        <v>11952.945</v>
+        <v>15405.4</v>
       </c>
       <c r="F61" t="n">
-        <v>12183.9</v>
+        <v>16085</v>
       </c>
       <c r="G61" t="n">
-        <v>2027.749</v>
+        <v>2130</v>
       </c>
       <c r="H61" t="n">
-        <v>816.227</v>
+        <v>2280</v>
       </c>
       <c r="I61" t="n">
-        <v>3455.282</v>
+        <v>9776</v>
       </c>
       <c r="J61" t="n">
-        <v>6726.311</v>
+        <v>13859</v>
       </c>
       <c r="K61" t="n">
-        <v>7951.807</v>
+        <v>15051</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Europe (UNWTO total)</t>
+          <t>East Asia and the Pacific (UNWTO total)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>15505.744</v>
+        <v>1994</v>
       </c>
       <c r="D62" t="n">
-        <v>15633.303</v>
+        <v>2182.5</v>
       </c>
       <c r="E62" t="n">
-        <v>16082.513</v>
+        <v>2149.3</v>
       </c>
       <c r="F62" t="n">
-        <v>16381.9</v>
+        <v>2176.2</v>
       </c>
       <c r="G62" t="n">
-        <v>2612.223</v>
+        <v>299</v>
       </c>
       <c r="H62" t="n">
-        <v>2259.032</v>
+        <v>129</v>
       </c>
       <c r="I62" t="n">
-        <v>11567.835</v>
+        <v>567</v>
       </c>
       <c r="J62" t="n">
-        <v>13771.831</v>
+        <v>1154</v>
       </c>
       <c r="K62" t="n">
-        <v>14854.886</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Middle East (UNWTO total)</t>
+          <t>Europe (UNWTO total)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>681.191</v>
+        <v>2875.8</v>
       </c>
       <c r="D63" t="n">
-        <v>550.013</v>
+        <v>2974.9</v>
       </c>
       <c r="E63" t="n">
-        <v>576.227</v>
+        <v>2943.9</v>
       </c>
       <c r="F63" t="n">
-        <v>577.1</v>
+        <v>3150.3</v>
       </c>
       <c r="G63" t="n">
-        <v>127.276</v>
+        <v>392</v>
       </c>
       <c r="H63" t="n">
-        <v>227.801</v>
+        <v>460</v>
       </c>
       <c r="I63" t="n">
-        <v>366.673</v>
+        <v>1998</v>
       </c>
       <c r="J63" t="n">
-        <v>463.179</v>
+        <v>2503</v>
       </c>
       <c r="K63" t="n">
-        <v>459.545</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>121</v>
+      </c>
+      <c r="G64" t="n">
+        <v>26</v>
+      </c>
+      <c r="H64" t="n">
+        <v>40</v>
+      </c>
+      <c r="I64" t="n">
+        <v>76</v>
+      </c>
+      <c r="J64" t="n">
+        <v>111</v>
+      </c>
+      <c r="K64" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>South Asia (UNWTO total)</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>1422.361</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1481.042</v>
-      </c>
-      <c r="E64" t="n">
-        <v>1570.362</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1670.5</v>
-      </c>
-      <c r="G64" t="n">
-        <v>384.746</v>
-      </c>
-      <c r="H64" t="n">
-        <v>528.2569999999999</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1440.26</v>
-      </c>
-      <c r="J64" t="n">
-        <v>2016.472</v>
-      </c>
-      <c r="K64" t="n">
-        <v>2496.501</v>
+      <c r="C65" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>446.8</v>
+      </c>
+      <c r="G65" t="n">
+        <v>84</v>
+      </c>
+      <c r="H65" t="n">
+        <v>114</v>
+      </c>
+      <c r="I65" t="n">
+        <v>295</v>
+      </c>
+      <c r="J65" t="n">
+        <v>502</v>
+      </c>
+      <c r="K65" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1243</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1314.3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1235.9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1340</v>
+      </c>
+      <c r="G66" t="n">
+        <v>262.945</v>
+      </c>
+      <c r="H66" t="n">
+        <v>250.284</v>
+      </c>
+      <c r="I66" t="n">
+        <v>830.221</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1025.13128294283</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1297.90576947888</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4573.9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5866</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6370.5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7092.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1320.48</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1867.265</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6359.413</v>
+      </c>
+      <c r="J67" t="n">
+        <v>8470.624000010759</v>
+      </c>
+      <c r="K67" t="n">
+        <v>9428.970904708071</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UN_Tourism_inbound_arrivals_by_transport_12_2025</t>
-        </is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1904.7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2299</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2560.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2977</v>
+      </c>
+      <c r="G68" t="n">
+        <v>562.403</v>
+      </c>
+      <c r="H68" t="n">
+        <v>230.302</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1086.684</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2360.18863897558</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2817.03795662791</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>67047.39999999999</v>
+      </c>
+      <c r="D69" t="n">
+        <v>71695.89999999999</v>
+      </c>
+      <c r="E69" t="n">
+        <v>71903.89999999999</v>
+      </c>
+      <c r="F69" t="n">
+        <v>71377.8</v>
+      </c>
+      <c r="G69" t="n">
+        <v>16676.276</v>
+      </c>
+      <c r="H69" t="n">
+        <v>28505.919</v>
+      </c>
+      <c r="I69" t="n">
+        <v>62765.346</v>
+      </c>
+      <c r="J69" t="n">
+        <v>72386.9099346476</v>
+      </c>
+      <c r="K69" t="n">
+        <v>79114.75530078731</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>series</t>
+          <t>Middle East (UNWTO total)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2016</v>
+        <v>386.7</v>
       </c>
       <c r="D70" t="n">
-        <v>2017</v>
+        <v>466.4</v>
       </c>
       <c r="E70" t="n">
-        <v>2018</v>
+        <v>416.3</v>
       </c>
       <c r="F70" t="n">
-        <v>2019</v>
+        <v>424.7</v>
       </c>
       <c r="G70" t="n">
-        <v>2020</v>
+        <v>76.34399999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>2021</v>
+        <v>281.162</v>
       </c>
       <c r="I70" t="n">
-        <v>2022</v>
+        <v>416.759</v>
       </c>
       <c r="J70" t="n">
-        <v>2023</v>
+        <v>617.95432944935</v>
       </c>
       <c r="K70" t="n">
-        <v>2024</v>
+        <v>765.914310277042</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>South Asia (UNWTO total)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9802.4</v>
+        <v>159.3</v>
       </c>
       <c r="D71" t="n">
-        <v>10576.8</v>
+        <v>227</v>
       </c>
       <c r="E71" t="n">
-        <v>10372.1</v>
+        <v>321</v>
       </c>
       <c r="F71" t="n">
-        <v>10999</v>
+        <v>297.5</v>
       </c>
       <c r="G71" t="n">
-        <v>1664</v>
+        <v>34.655</v>
       </c>
       <c r="H71" t="n">
-        <v>1595</v>
+        <v>45.87</v>
       </c>
       <c r="I71" t="n">
-        <v>6669</v>
+        <v>200.859</v>
       </c>
       <c r="J71" t="n">
-        <v>9364</v>
+        <v>308.24178665693</v>
       </c>
       <c r="K71" t="n">
-        <v>10269</v>
+        <v>334.712612593961</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+          <t>Africa (UNWTO total)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9373.4</v>
+        <v>25.6</v>
       </c>
       <c r="D72" t="n">
-        <v>9458.5</v>
+        <v>27.6</v>
       </c>
       <c r="E72" t="n">
-        <v>9802.299999999999</v>
+        <v>32.7</v>
       </c>
       <c r="F72" t="n">
-        <v>10032.9</v>
+        <v>33.6</v>
       </c>
       <c r="G72" t="n">
-        <v>1294</v>
+        <v>8.821999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>1461</v>
+        <v>14.051</v>
       </c>
       <c r="I72" t="n">
-        <v>5767</v>
+        <v>25.231</v>
       </c>
       <c r="J72" t="n">
-        <v>8449</v>
+        <v>25.175</v>
       </c>
       <c r="K72" t="n">
-        <v>9142</v>
+        <v>24.723</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+          <t>Americas (UNWTO total)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>795.5</v>
+        <v>31490.2</v>
       </c>
       <c r="D73" t="n">
-        <v>847.9</v>
+        <v>35340.2</v>
       </c>
       <c r="E73" t="n">
-        <v>959.5</v>
+        <v>38247.9</v>
       </c>
       <c r="F73" t="n">
-        <v>1113.5</v>
+        <v>41938.6</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>6980.967</v>
       </c>
       <c r="H73" t="n">
-        <v>6</v>
+        <v>12505.975</v>
       </c>
       <c r="I73" t="n">
-        <v>388</v>
+        <v>17575.432</v>
       </c>
       <c r="J73" t="n">
-        <v>531</v>
+        <v>17057.584</v>
       </c>
       <c r="K73" t="n">
-        <v>502</v>
+        <v>18253.981</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>East Asia and the Pacific (UNWTO total)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>60343.7</v>
+        <v>370.1</v>
       </c>
       <c r="D74" t="n">
-        <v>66639.5</v>
+        <v>411.6</v>
       </c>
       <c r="E74" t="n">
-        <v>67545.7</v>
+        <v>437.4</v>
       </c>
       <c r="F74" t="n">
-        <v>68691.89999999999</v>
+        <v>437.2</v>
       </c>
       <c r="G74" t="n">
-        <v>13657.664</v>
+        <v>102.894</v>
       </c>
       <c r="H74" t="n">
-        <v>24431.89</v>
+        <v>54.699</v>
       </c>
       <c r="I74" t="n">
-        <v>59307.849</v>
+        <v>142.697</v>
       </c>
       <c r="J74" t="n">
-        <v>69564.23140752919</v>
+        <v>257.555</v>
       </c>
       <c r="K74" t="n">
-        <v>77119.7871470598</v>
+        <v>312.311</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+          <t>Europe (UNWTO total)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13335.9</v>
+        <v>1832.9</v>
       </c>
       <c r="D75" t="n">
-        <v>13263.4</v>
+        <v>1961.7</v>
       </c>
       <c r="E75" t="n">
-        <v>13250.6</v>
+        <v>2056.6</v>
       </c>
       <c r="F75" t="n">
-        <v>13096.5</v>
+        <v>2105.1</v>
       </c>
       <c r="G75" t="n">
-        <v>5052.128</v>
+        <v>559.011</v>
       </c>
       <c r="H75" t="n">
-        <v>6521.955</v>
+        <v>963.153</v>
       </c>
       <c r="I75" t="n">
-        <v>11199.208</v>
+        <v>2103.138</v>
       </c>
       <c r="J75" t="n">
-        <v>13745.4613453271</v>
+        <v>1938.865</v>
       </c>
       <c r="K75" t="n">
-        <v>14535.4190698515</v>
+        <v>1788.665</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+          <t>Middle East (UNWTO total)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1635.4</v>
+        <v>45.8</v>
       </c>
       <c r="D76" t="n">
-        <v>1965.7</v>
+        <v>50</v>
       </c>
       <c r="E76" t="n">
-        <v>2012.1</v>
+        <v>61</v>
       </c>
       <c r="F76" t="n">
-        <v>1720.8</v>
+        <v>53.8</v>
       </c>
       <c r="G76" t="n">
-        <v>223.311</v>
+        <v>27.265</v>
       </c>
       <c r="H76" t="n">
-        <v>226.957</v>
+        <v>77.745</v>
       </c>
       <c r="I76" t="n">
-        <v>1152.225</v>
+        <v>94.98</v>
       </c>
       <c r="J76" t="n">
-        <v>1859.35721985221</v>
+        <v>81.999</v>
       </c>
       <c r="K76" t="n">
-        <v>2104.09063755124</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>South Asia (UNWTO total)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30483.8</v>
+        <v>23.9</v>
       </c>
       <c r="D77" t="n">
-        <v>34116.5</v>
+        <v>26.3</v>
       </c>
       <c r="E77" t="n">
-        <v>37229.5</v>
+        <v>32.4</v>
       </c>
       <c r="F77" t="n">
-        <v>39396.2</v>
+        <v>33</v>
       </c>
       <c r="G77" t="n">
-        <v>9277</v>
+        <v>7.483</v>
       </c>
       <c r="H77" t="n">
-        <v>10600</v>
+        <v>44.228</v>
       </c>
       <c r="I77" t="n">
-        <v>29042</v>
+        <v>40.493</v>
       </c>
       <c r="J77" t="n">
-        <v>35814</v>
+        <v>45.088</v>
       </c>
       <c r="K77" t="n">
-        <v>38587</v>
+        <v>40.784</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+          <t>Africa (UNWTO total)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1701.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>1633.7</v>
+        <v>10.9</v>
       </c>
       <c r="E78" t="n">
-        <v>1701</v>
+        <v>12.7</v>
       </c>
       <c r="F78" t="n">
-        <v>1727.9</v>
+        <v>12.9</v>
       </c>
       <c r="G78" t="n">
-        <v>348</v>
+        <v>4</v>
       </c>
       <c r="H78" t="n">
-        <v>472</v>
+        <v>9.4</v>
       </c>
       <c r="I78" t="n">
-        <v>703</v>
+        <v>59</v>
       </c>
       <c r="J78" t="n">
-        <v>885</v>
+        <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>1275</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>Americas (UNWTO total)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>16878</v>
+        <v>41.4</v>
       </c>
       <c r="D79" t="n">
-        <v>18548</v>
+        <v>50.3</v>
       </c>
       <c r="E79" t="n">
-        <v>19368</v>
+        <v>58.6</v>
       </c>
       <c r="F79" t="n">
-        <v>19634.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>8337.627</v>
+        <v>14.5</v>
       </c>
       <c r="H79" t="n">
-        <v>14602.112</v>
+        <v>31.2</v>
       </c>
       <c r="I79" t="n">
-        <v>21329.168</v>
+        <v>63.2</v>
       </c>
       <c r="J79" t="n">
-        <v>22821.343</v>
+        <v>77</v>
       </c>
       <c r="K79" t="n">
-        <v>23165.256</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+          <t>East Asia and the Pacific (UNWTO total)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>18201</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>20743</v>
+        <v>111.4</v>
       </c>
       <c r="E80" t="n">
-        <v>21944.7</v>
+        <v>158.8</v>
       </c>
       <c r="F80" t="n">
-        <v>25389.5</v>
+        <v>198.4</v>
       </c>
       <c r="G80" t="n">
-        <v>15945.909</v>
+        <v>29.4</v>
       </c>
       <c r="H80" t="n">
-        <v>17258.28</v>
+        <v>45.1</v>
       </c>
       <c r="I80" t="n">
-        <v>16996.382</v>
+        <v>72.2</v>
       </c>
       <c r="J80" t="n">
-        <v>19128.085</v>
+        <v>126</v>
       </c>
       <c r="K80" t="n">
-        <v>21873.498</v>
+        <v>195</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+          <t>Europe (UNWTO total)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>46940.691</v>
+        <v>1158.4</v>
       </c>
       <c r="D81" t="n">
-        <v>48734.483</v>
+        <v>1319.5</v>
       </c>
       <c r="E81" t="n">
-        <v>50695.476</v>
+        <v>1439.6</v>
       </c>
       <c r="F81" t="n">
-        <v>50253.1</v>
+        <v>1555.7</v>
       </c>
       <c r="G81" t="n">
-        <v>10932.649</v>
+        <v>393.2</v>
       </c>
       <c r="H81" t="n">
-        <v>13735.582</v>
+        <v>755.1</v>
       </c>
       <c r="I81" t="n">
-        <v>31938.417</v>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+        <v>1529</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1895</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2070</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+          <t>Middle East (UNWTO total)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>28913.34</v>
+        <v>5.8</v>
       </c>
       <c r="D82" t="n">
-        <v>27920.526</v>
+        <v>5.2</v>
       </c>
       <c r="E82" t="n">
-        <v>28489.235</v>
+        <v>5.8</v>
       </c>
       <c r="F82" t="n">
-        <v>28651.9</v>
+        <v>4.8</v>
       </c>
       <c r="G82" t="n">
-        <v>8221.689</v>
+        <v>2.4</v>
       </c>
       <c r="H82" t="n">
-        <v>8290.293</v>
+        <v>5.6</v>
       </c>
       <c r="I82" t="n">
-        <v>18383.956</v>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="J82" t="n">
+        <v>15</v>
+      </c>
+      <c r="K82" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>553.457</v>
-      </c>
-      <c r="D83" t="n">
-        <v>531.737</v>
-      </c>
+          <t>South Asia (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>561.207</v>
+        <v>35.1</v>
       </c>
       <c r="F83" t="n">
-        <v>536.7</v>
+        <v>10.4</v>
       </c>
       <c r="G83" t="n">
-        <v>57.676</v>
+        <v>2.2</v>
       </c>
       <c r="H83" t="n">
-        <v>74.578</v>
+        <v>24.9</v>
       </c>
       <c r="I83" t="n">
-        <v>547.312</v>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+        <v>45.5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>13</v>
+      </c>
+      <c r="K83" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UN_Tourism_inbound_expenditure_12_2025</t>
+          <t>UN_Tourism_inbound_arrivals_by_transport_12_2025</t>
         </is>
       </c>
     </row>
@@ -2766,176 +2377,493 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>inbound - expenditure - balance of payments - total - visitors</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>9802.4</v>
+      </c>
+      <c r="D90" t="n">
+        <v>10576.8</v>
+      </c>
+      <c r="E90" t="n">
+        <v>10372.1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>10999</v>
+      </c>
       <c r="G90" t="n">
-        <v>13899.963252617</v>
+        <v>1664</v>
       </c>
       <c r="H90" t="n">
-        <v>15360.7697581997</v>
+        <v>1595</v>
       </c>
       <c r="I90" t="n">
-        <v>31816.9121593968</v>
+        <v>6669</v>
       </c>
       <c r="J90" t="n">
-        <v>45409.9218533883</v>
+        <v>9364</v>
       </c>
       <c r="K90" t="n">
-        <v>49886.0324452887</v>
+        <v>10269</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>inbound - expenditure - balance of payments - total - visitors</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>9373.4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>9458.5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>9802.299999999999</v>
+      </c>
+      <c r="F91" t="n">
+        <v>10032.9</v>
+      </c>
       <c r="G91" t="n">
-        <v>18380.4147013811</v>
+        <v>1294</v>
       </c>
       <c r="H91" t="n">
-        <v>34176.1559870135</v>
+        <v>1461</v>
       </c>
       <c r="I91" t="n">
-        <v>72083.3294863503</v>
+        <v>5767</v>
       </c>
       <c r="J91" t="n">
-        <v>92144.2801105462</v>
+        <v>8449</v>
       </c>
       <c r="K91" t="n">
-        <v>106656.535197297</v>
+        <v>9142</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>inbound - expenditure - balance of payments - total - visitors</t>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>42423</v>
+        <v>795.5</v>
       </c>
       <c r="D92" t="n">
-        <v>46719</v>
+        <v>847.9</v>
       </c>
       <c r="E92" t="n">
-        <v>51602</v>
+        <v>959.5</v>
       </c>
       <c r="F92" t="n">
-        <v>51910</v>
+        <v>1113.5</v>
       </c>
       <c r="G92" t="n">
-        <v>20316.7578071358</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>25354.9279185429</v>
+        <v>6</v>
       </c>
       <c r="I92" t="n">
-        <v>47100.4319500271</v>
+        <v>388</v>
       </c>
       <c r="J92" t="n">
-        <v>57919.6252057293</v>
+        <v>531</v>
       </c>
       <c r="K92" t="n">
-        <v>61433.937023306</v>
+        <v>502</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>inbound - expenditure - balance of payments - total - visitors</t>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>23270</v>
+        <v>60343.7</v>
       </c>
       <c r="D93" t="n">
-        <v>24619</v>
+        <v>66639.5</v>
       </c>
       <c r="E93" t="n">
-        <v>26044</v>
+        <v>67545.7</v>
       </c>
       <c r="F93" t="n">
-        <v>27126</v>
+        <v>68691.89999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>12142.599224</v>
+        <v>13657.664</v>
       </c>
       <c r="H93" t="n">
-        <v>22138.069892</v>
+        <v>24431.89</v>
       </c>
       <c r="I93" t="n">
-        <v>31257.108743</v>
+        <v>59307.849</v>
       </c>
       <c r="J93" t="n">
-        <v>33495.50487</v>
+        <v>69564.23140752919</v>
       </c>
       <c r="K93" t="n">
-        <v>36239.253442</v>
+        <v>77119.7871470598</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>13335.9</v>
+      </c>
+      <c r="D94" t="n">
+        <v>13263.4</v>
+      </c>
+      <c r="E94" t="n">
+        <v>13250.6</v>
+      </c>
+      <c r="F94" t="n">
+        <v>13096.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5052.128</v>
+      </c>
+      <c r="H94" t="n">
+        <v>6521.955</v>
+      </c>
+      <c r="I94" t="n">
+        <v>11199.208</v>
+      </c>
+      <c r="J94" t="n">
+        <v>13745.4613453271</v>
+      </c>
+      <c r="K94" t="n">
+        <v>14535.4190698515</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1635.4</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1965.7</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2012.1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1720.8</v>
+      </c>
+      <c r="G95" t="n">
+        <v>223.311</v>
+      </c>
+      <c r="H95" t="n">
+        <v>226.957</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1152.225</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1859.35721985221</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2104.09063755124</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>16878</v>
+      </c>
+      <c r="D96" t="n">
+        <v>18548</v>
+      </c>
+      <c r="E96" t="n">
+        <v>19368</v>
+      </c>
+      <c r="F96" t="n">
+        <v>19634.9</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8337.627</v>
+      </c>
+      <c r="H96" t="n">
+        <v>14602.112</v>
+      </c>
+      <c r="I96" t="n">
+        <v>21329.168</v>
+      </c>
+      <c r="J96" t="n">
+        <v>22821.343</v>
+      </c>
+      <c r="K96" t="n">
+        <v>23165.256</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>18201</v>
+      </c>
+      <c r="D97" t="n">
+        <v>20743</v>
+      </c>
+      <c r="E97" t="n">
+        <v>21944.7</v>
+      </c>
+      <c r="F97" t="n">
+        <v>25389.5</v>
+      </c>
+      <c r="G97" t="n">
+        <v>15945.909</v>
+      </c>
+      <c r="H97" t="n">
+        <v>17258.28</v>
+      </c>
+      <c r="I97" t="n">
+        <v>16996.382</v>
+      </c>
+      <c r="J97" t="n">
+        <v>19128.085</v>
+      </c>
+      <c r="K97" t="n">
+        <v>21873.498</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_expenditure_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>inbound - expenditure - balance of payments - total - visitors</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>228549</v>
-      </c>
-      <c r="D94" t="n">
-        <v>233758</v>
-      </c>
-      <c r="E94" t="n">
-        <v>241984</v>
-      </c>
-      <c r="F94" t="n">
-        <v>239065</v>
-      </c>
-      <c r="G94" t="n">
-        <v>84297</v>
-      </c>
-      <c r="H94" t="n">
-        <v>84506</v>
-      </c>
-      <c r="I94" t="n">
-        <v>172284</v>
-      </c>
-      <c r="J94" t="n">
-        <v>226167</v>
-      </c>
-      <c r="K94" t="n">
-        <v>251649</v>
-      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>13899.963252617</v>
+      </c>
+      <c r="H104" t="n">
+        <v>15360.7697581997</v>
+      </c>
+      <c r="I104" t="n">
+        <v>31816.9121593968</v>
+      </c>
+      <c r="J104" t="n">
+        <v>45409.9218533883</v>
+      </c>
+      <c r="K104" t="n">
+        <v>49886.0324452887</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="n">
+        <v>18380.4147013811</v>
+      </c>
+      <c r="H105" t="n">
+        <v>34176.1559870135</v>
+      </c>
+      <c r="I105" t="n">
+        <v>72083.3294863503</v>
+      </c>
+      <c r="J105" t="n">
+        <v>92144.2801105462</v>
+      </c>
+      <c r="K105" t="n">
+        <v>106656.535197297</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>23270</v>
+      </c>
+      <c r="D106" t="n">
+        <v>24619</v>
+      </c>
+      <c r="E106" t="n">
+        <v>26044</v>
+      </c>
+      <c r="F106" t="n">
+        <v>27126</v>
+      </c>
+      <c r="G106" t="n">
+        <v>12142.599224</v>
+      </c>
+      <c r="H106" t="n">
+        <v>22138.069892</v>
+      </c>
+      <c r="I106" t="n">
+        <v>31257.108743</v>
+      </c>
+      <c r="J106" t="n">
+        <v>33495.50487</v>
+      </c>
+      <c r="K106" t="n">
+        <v>36239.253442</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1461</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1706</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1941</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1429.81183073355</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2179.15719069842</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3061.06392017447</v>
+      </c>
+      <c r="J107" t="n">
+        <v>3466.23263064219</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>household_size_and_composition_2022</t>
+          <t>NatChange</t>
         </is>
       </c>
     </row>
@@ -435,13 +435,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="D3" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="E3" t="n">
-        <v>2016</v>
+        <v>2018</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="4">
@@ -452,31 +476,87 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DYB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>112.597</v>
+      </c>
+      <c r="D4" t="n">
+        <v>95.57299999999999</v>
+      </c>
       <c r="E4" t="n">
-        <v>2.45</v>
+        <v>84.536</v>
+      </c>
+      <c r="F4" t="n">
+        <v>83.411</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50.252</v>
+      </c>
+      <c r="H4" t="n">
+        <v>58.601</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.941</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44.921</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39.289</v>
+      </c>
+      <c r="L4" t="n">
+        <v>34.496</v>
+      </c>
+      <c r="M4" t="n">
+        <v>29.912</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DYB</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+        <v>425.132</v>
+      </c>
+      <c r="D5" t="n">
+        <v>426.546</v>
+      </c>
+      <c r="E5" t="n">
+        <v>433.628</v>
+      </c>
+      <c r="F5" t="n">
+        <v>441.061</v>
+      </c>
+      <c r="G5" t="n">
+        <v>378.997</v>
+      </c>
+      <c r="H5" t="n">
+        <v>311.156</v>
+      </c>
+      <c r="I5" t="n">
+        <v>406.142</v>
+      </c>
+      <c r="J5" t="n">
+        <v>422.576</v>
+      </c>
+      <c r="K5" t="n">
+        <v>411.685</v>
+      </c>
+      <c r="L5" t="n">
+        <v>396.091</v>
+      </c>
+      <c r="M5" t="n">
+        <v>380.132</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -486,48 +566,1606 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+        <v>-2.588</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-33.375</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-56.776</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-60.87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-152.023</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-116.872</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-141.849</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-110.642</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-122.249</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-127.192</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-133.07</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DYB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-151.57</v>
+      </c>
       <c r="D7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>-203.724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-200.742</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-224.302</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-342.345</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-267.103</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-341.929</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-278.821</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-279.791</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-284.114</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-289.782</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1220.077</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1076.533</v>
+      </c>
+      <c r="E8" t="n">
+        <v>997.449</v>
+      </c>
+      <c r="F8" t="n">
+        <v>930.222</v>
+      </c>
+      <c r="G8" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>188.321</v>
+      </c>
+      <c r="I8" t="n">
+        <v>563.077</v>
+      </c>
+      <c r="J8" t="n">
+        <v>681.818</v>
+      </c>
+      <c r="K8" t="n">
+        <v>607.88</v>
+      </c>
+      <c r="L8" t="n">
+        <v>573.802</v>
+      </c>
+      <c r="M8" t="n">
+        <v>537.058</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NetMigrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>329.455</v>
+      </c>
+      <c r="D15" t="n">
+        <v>372.685</v>
+      </c>
+      <c r="E15" t="n">
+        <v>420.224</v>
+      </c>
+      <c r="F15" t="n">
+        <v>387.685</v>
+      </c>
+      <c r="G15" t="n">
+        <v>256.592</v>
+      </c>
+      <c r="H15" t="n">
+        <v>198.867</v>
+      </c>
+      <c r="I15" t="n">
+        <v>459.988</v>
+      </c>
+      <c r="J15" t="n">
+        <v>433.842</v>
+      </c>
+      <c r="K15" t="n">
+        <v>368.599</v>
+      </c>
+      <c r="L15" t="n">
+        <v>326.204</v>
+      </c>
+      <c r="M15" t="n">
+        <v>291.403</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>104.373</v>
+      </c>
+      <c r="D16" t="n">
+        <v>431.072</v>
+      </c>
+      <c r="E16" t="n">
+        <v>495.524</v>
+      </c>
+      <c r="F16" t="n">
+        <v>396.826</v>
+      </c>
+      <c r="G16" t="n">
+        <v>227.13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>199.07</v>
+      </c>
+      <c r="I16" t="n">
+        <v>183.18</v>
+      </c>
+      <c r="J16" t="n">
+        <v>154.521</v>
+      </c>
+      <c r="K16" t="n">
+        <v>141.643</v>
+      </c>
+      <c r="L16" t="n">
+        <v>129.139</v>
+      </c>
+      <c r="M16" t="n">
+        <v>115.815</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>106.474</v>
+      </c>
+      <c r="D17" t="n">
+        <v>201.135</v>
+      </c>
+      <c r="E17" t="n">
+        <v>337.467</v>
+      </c>
+      <c r="F17" t="n">
+        <v>464.783</v>
+      </c>
+      <c r="G17" t="n">
+        <v>236.854</v>
+      </c>
+      <c r="H17" t="n">
+        <v>144.385</v>
+      </c>
+      <c r="I17" t="n">
+        <v>299.779</v>
+      </c>
+      <c r="J17" t="n">
+        <v>119.099</v>
+      </c>
+      <c r="K17" t="n">
+        <v>111.674</v>
+      </c>
+      <c r="L17" t="n">
+        <v>96.63</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.30500000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>84.568</v>
+      </c>
+      <c r="D18" t="n">
+        <v>95.14700000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>83.68600000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>46.634</v>
+      </c>
+      <c r="G18" t="n">
+        <v>85.28100000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>157.327</v>
+      </c>
+      <c r="I18" t="n">
+        <v>231.228</v>
+      </c>
+      <c r="J18" t="n">
+        <v>150.189</v>
+      </c>
+      <c r="K18" t="n">
+        <v>95.246</v>
+      </c>
+      <c r="L18" t="n">
+        <v>75.44799999999999</v>
+      </c>
+      <c r="M18" t="n">
+        <v>58.272</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1889.129</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1864.738</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1764.961</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1774.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>329.769</v>
+      </c>
+      <c r="H19" t="n">
+        <v>674.787</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1319.009</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1322.668</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1286.132</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1230.663</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1177.848</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TPopulation1Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2027</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2028</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2030</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2031</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2032</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2033</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2034</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2035</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>36132.317</v>
+      </c>
+      <c r="D26" t="n">
+        <v>36574.369</v>
+      </c>
+      <c r="E26" t="n">
+        <v>37042.624</v>
+      </c>
+      <c r="F26" t="n">
+        <v>37547.386</v>
+      </c>
+      <c r="G26" t="n">
+        <v>38018.483</v>
+      </c>
+      <c r="H26" t="n">
+        <v>38325.321</v>
+      </c>
+      <c r="I26" t="n">
+        <v>38582.793</v>
+      </c>
+      <c r="J26" t="n">
+        <v>39059.725</v>
+      </c>
+      <c r="K26" t="n">
+        <v>39538.484</v>
+      </c>
+      <c r="L26" t="n">
+        <v>39946.376</v>
+      </c>
+      <c r="M26" t="n">
+        <v>40307.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>40628.385</v>
+      </c>
+      <c r="O26" t="n">
+        <v>40936.083</v>
+      </c>
+      <c r="P26" t="n">
+        <v>41234.923</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>41517.67</v>
+      </c>
+      <c r="R26" t="n">
+        <v>41793.508</v>
+      </c>
+      <c r="S26" t="n">
+        <v>42063.722</v>
+      </c>
+      <c r="T26" t="n">
+        <v>42319.814</v>
+      </c>
+      <c r="U26" t="n">
+        <v>42556.246</v>
+      </c>
+      <c r="V26" t="n">
+        <v>42796.698</v>
+      </c>
+      <c r="W26" t="n">
+        <v>43013.836</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>47172.76</v>
+      </c>
+      <c r="D27" t="n">
+        <v>47702.264</v>
+      </c>
+      <c r="E27" t="n">
+        <v>48559.892</v>
+      </c>
+      <c r="F27" t="n">
+        <v>49489.039</v>
+      </c>
+      <c r="G27" t="n">
+        <v>50326.931</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50933.064</v>
+      </c>
+      <c r="I27" t="n">
+        <v>51443.283</v>
+      </c>
+      <c r="J27" t="n">
+        <v>52032.604</v>
+      </c>
+      <c r="K27" t="n">
+        <v>52609.701</v>
+      </c>
+      <c r="L27" t="n">
+        <v>53163.026</v>
+      </c>
+      <c r="M27" t="n">
+        <v>53688.245</v>
+      </c>
+      <c r="N27" t="n">
+        <v>54184.207</v>
+      </c>
+      <c r="O27" t="n">
+        <v>54660.324</v>
+      </c>
+      <c r="P27" t="n">
+        <v>55109.908</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>55535.344</v>
+      </c>
+      <c r="R27" t="n">
+        <v>55937.606</v>
+      </c>
+      <c r="S27" t="n">
+        <v>56314.321</v>
+      </c>
+      <c r="T27" t="n">
+        <v>56666.676</v>
+      </c>
+      <c r="U27" t="n">
+        <v>56997.845</v>
+      </c>
+      <c r="V27" t="n">
+        <v>57305.379</v>
+      </c>
+      <c r="W27" t="n">
+        <v>57586.127</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>46680.827</v>
+      </c>
+      <c r="D28" t="n">
+        <v>46784.715</v>
+      </c>
+      <c r="E28" t="n">
+        <v>46952.476</v>
+      </c>
+      <c r="F28" t="n">
+        <v>47233.166</v>
+      </c>
+      <c r="G28" t="n">
+        <v>47637.072</v>
+      </c>
+      <c r="H28" t="n">
+        <v>47721.906</v>
+      </c>
+      <c r="I28" t="n">
+        <v>47749.421</v>
+      </c>
+      <c r="J28" t="n">
+        <v>47907.344</v>
+      </c>
+      <c r="K28" t="n">
+        <v>47915.815</v>
+      </c>
+      <c r="L28" t="n">
+        <v>47905.238</v>
+      </c>
+      <c r="M28" t="n">
+        <v>47874.678</v>
+      </c>
+      <c r="N28" t="n">
+        <v>47826.907</v>
+      </c>
+      <c r="O28" t="n">
+        <v>47777.635</v>
+      </c>
+      <c r="P28" t="n">
+        <v>47719.497</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>47652.032</v>
+      </c>
+      <c r="R28" t="n">
+        <v>47569.007</v>
+      </c>
+      <c r="S28" t="n">
+        <v>47477.971</v>
+      </c>
+      <c r="T28" t="n">
+        <v>47389.074</v>
+      </c>
+      <c r="U28" t="n">
+        <v>47299.037</v>
+      </c>
+      <c r="V28" t="n">
+        <v>47205.242</v>
+      </c>
+      <c r="W28" t="n">
+        <v>47103.15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>60511.606</v>
+      </c>
+      <c r="D29" t="n">
+        <v>60444.609</v>
+      </c>
+      <c r="E29" t="n">
+        <v>60336.027</v>
+      </c>
+      <c r="F29" t="n">
+        <v>60218.97</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60041.302</v>
+      </c>
+      <c r="H29" t="n">
+        <v>59784.236</v>
+      </c>
+      <c r="I29" t="n">
+        <v>59674.464</v>
+      </c>
+      <c r="J29" t="n">
+        <v>59563.765</v>
+      </c>
+      <c r="K29" t="n">
+        <v>59435.141</v>
+      </c>
+      <c r="L29" t="n">
+        <v>59250.593</v>
+      </c>
+      <c r="M29" t="n">
+        <v>59041.927</v>
+      </c>
+      <c r="N29" t="n">
+        <v>58810.406</v>
+      </c>
+      <c r="O29" t="n">
+        <v>58567.152</v>
+      </c>
+      <c r="P29" t="n">
+        <v>58324.514</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>58077.538</v>
+      </c>
+      <c r="R29" t="n">
+        <v>57814.606</v>
+      </c>
+      <c r="S29" t="n">
+        <v>57545.634</v>
+      </c>
+      <c r="T29" t="n">
+        <v>57287.368</v>
+      </c>
+      <c r="U29" t="n">
+        <v>57025.527</v>
+      </c>
+      <c r="V29" t="n">
+        <v>56756.306</v>
+      </c>
+      <c r="W29" t="n">
+        <v>56483.705</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>327624.824</v>
+      </c>
+      <c r="D30" t="n">
+        <v>330734.029</v>
+      </c>
+      <c r="E30" t="n">
+        <v>333675.29</v>
+      </c>
+      <c r="F30" t="n">
+        <v>336437.705</v>
+      </c>
+      <c r="G30" t="n">
+        <v>339142.428</v>
+      </c>
+      <c r="H30" t="n">
+        <v>339729.889</v>
+      </c>
+      <c r="I30" t="n">
+        <v>340592.993</v>
+      </c>
+      <c r="J30" t="n">
+        <v>342475.098</v>
+      </c>
+      <c r="K30" t="n">
+        <v>344479.572</v>
+      </c>
+      <c r="L30" t="n">
+        <v>346373.57</v>
+      </c>
+      <c r="M30" t="n">
+        <v>348178.045</v>
+      </c>
+      <c r="N30" t="n">
+        <v>349892.943</v>
+      </c>
+      <c r="O30" t="n">
+        <v>351563.767</v>
+      </c>
+      <c r="P30" t="n">
+        <v>353244.404</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>354856.131</v>
+      </c>
+      <c r="R30" t="n">
+        <v>356443.631</v>
+      </c>
+      <c r="S30" t="n">
+        <v>358001.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>359538.148</v>
+      </c>
+      <c r="U30" t="n">
+        <v>361049.869</v>
+      </c>
+      <c r="V30" t="n">
+        <v>362553.753</v>
+      </c>
+      <c r="W30" t="n">
+        <v>364015.679</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TPopulationFemale1July</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>18320.689</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18544.907</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18780.076</v>
+      </c>
+      <c r="F37" t="n">
+        <v>19016.711</v>
+      </c>
+      <c r="G37" t="n">
+        <v>19207.453</v>
+      </c>
+      <c r="H37" t="n">
+        <v>19348.679</v>
+      </c>
+      <c r="I37" t="n">
+        <v>19538.904</v>
+      </c>
+      <c r="J37" t="n">
+        <v>19783.529</v>
+      </c>
+      <c r="K37" t="n">
+        <v>20007.47</v>
+      </c>
+      <c r="L37" t="n">
+        <v>20202.487</v>
+      </c>
+      <c r="M37" t="n">
+        <v>20375.297</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>23988.805</v>
+      </c>
+      <c r="D38" t="n">
+        <v>24342.009</v>
+      </c>
+      <c r="E38" t="n">
+        <v>24795.336</v>
+      </c>
+      <c r="F38" t="n">
+        <v>25243.941</v>
+      </c>
+      <c r="G38" t="n">
+        <v>25616.897</v>
+      </c>
+      <c r="H38" t="n">
+        <v>25914.904</v>
+      </c>
+      <c r="I38" t="n">
+        <v>26204.251</v>
+      </c>
+      <c r="J38" t="n">
+        <v>26502.596</v>
+      </c>
+      <c r="K38" t="n">
+        <v>26791.092</v>
+      </c>
+      <c r="L38" t="n">
+        <v>27067.163</v>
+      </c>
+      <c r="M38" t="n">
+        <v>27328.84</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>23745.407</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23831.398</v>
+      </c>
+      <c r="E39" t="n">
+        <v>23956.747</v>
+      </c>
+      <c r="F39" t="n">
+        <v>24135.524</v>
+      </c>
+      <c r="G39" t="n">
+        <v>24262.247</v>
+      </c>
+      <c r="H39" t="n">
+        <v>24292.717</v>
+      </c>
+      <c r="I39" t="n">
+        <v>24342.743</v>
+      </c>
+      <c r="J39" t="n">
+        <v>24387.156</v>
+      </c>
+      <c r="K39" t="n">
+        <v>24388.607</v>
+      </c>
+      <c r="L39" t="n">
+        <v>24382.98</v>
+      </c>
+      <c r="M39" t="n">
+        <v>24368.467</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>31086.497</v>
+      </c>
+      <c r="D40" t="n">
+        <v>30996.639</v>
+      </c>
+      <c r="E40" t="n">
+        <v>30898.339</v>
+      </c>
+      <c r="F40" t="n">
+        <v>30803.652</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30683.163</v>
+      </c>
+      <c r="H40" t="n">
+        <v>30575.93</v>
+      </c>
+      <c r="I40" t="n">
+        <v>30509.575</v>
+      </c>
+      <c r="J40" t="n">
+        <v>30437</v>
+      </c>
+      <c r="K40" t="n">
+        <v>30339.073</v>
+      </c>
+      <c r="L40" t="n">
+        <v>30218.791</v>
+      </c>
+      <c r="M40" t="n">
+        <v>30087.37</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>164043.184</v>
+      </c>
+      <c r="D41" t="n">
+        <v>165406.601</v>
+      </c>
+      <c r="E41" t="n">
+        <v>166697.774</v>
+      </c>
+      <c r="F41" t="n">
+        <v>167942.756</v>
+      </c>
+      <c r="G41" t="n">
+        <v>168726.055</v>
+      </c>
+      <c r="H41" t="n">
+        <v>169124.634</v>
+      </c>
+      <c r="I41" t="n">
+        <v>169861.303</v>
+      </c>
+      <c r="J41" t="n">
+        <v>170888.626</v>
+      </c>
+      <c r="K41" t="n">
+        <v>171875.044</v>
+      </c>
+      <c r="L41" t="n">
+        <v>172778.982</v>
+      </c>
+      <c r="M41" t="n">
+        <v>173636.381</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TPopulationMale1July</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>18032.655</v>
+      </c>
+      <c r="D48" t="n">
+        <v>18263.59</v>
+      </c>
+      <c r="E48" t="n">
+        <v>18514.929</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18766.224</v>
+      </c>
+      <c r="G48" t="n">
+        <v>18964.448</v>
+      </c>
+      <c r="H48" t="n">
+        <v>19105.377</v>
+      </c>
+      <c r="I48" t="n">
+        <v>19282.356</v>
+      </c>
+      <c r="J48" t="n">
+        <v>19515.575</v>
+      </c>
+      <c r="K48" t="n">
+        <v>19734.96</v>
+      </c>
+      <c r="L48" t="n">
+        <v>19924.235</v>
+      </c>
+      <c r="M48" t="n">
+        <v>20092.43</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>23448.707</v>
+      </c>
+      <c r="D49" t="n">
+        <v>23789.069</v>
+      </c>
+      <c r="E49" t="n">
+        <v>24229.13</v>
+      </c>
+      <c r="F49" t="n">
+        <v>24664.044</v>
+      </c>
+      <c r="G49" t="n">
+        <v>25013.101</v>
+      </c>
+      <c r="H49" t="n">
+        <v>25273.27</v>
+      </c>
+      <c r="I49" t="n">
+        <v>25533.693</v>
+      </c>
+      <c r="J49" t="n">
+        <v>25818.556</v>
+      </c>
+      <c r="K49" t="n">
+        <v>26095.271</v>
+      </c>
+      <c r="L49" t="n">
+        <v>26358.472</v>
+      </c>
+      <c r="M49" t="n">
+        <v>26607.386</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>22987.364</v>
+      </c>
+      <c r="D50" t="n">
+        <v>23037.197</v>
+      </c>
+      <c r="E50" t="n">
+        <v>23136.074</v>
+      </c>
+      <c r="F50" t="n">
+        <v>23299.594</v>
+      </c>
+      <c r="G50" t="n">
+        <v>23417.243</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23442.946</v>
+      </c>
+      <c r="I50" t="n">
+        <v>23485.64</v>
+      </c>
+      <c r="J50" t="n">
+        <v>23524.424</v>
+      </c>
+      <c r="K50" t="n">
+        <v>23521.92</v>
+      </c>
+      <c r="L50" t="n">
+        <v>23506.978</v>
+      </c>
+      <c r="M50" t="n">
+        <v>23482.325</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>29391.61</v>
+      </c>
+      <c r="D51" t="n">
+        <v>29393.679</v>
+      </c>
+      <c r="E51" t="n">
+        <v>29379.159</v>
+      </c>
+      <c r="F51" t="n">
+        <v>29326.484</v>
+      </c>
+      <c r="G51" t="n">
+        <v>29229.606</v>
+      </c>
+      <c r="H51" t="n">
+        <v>29153.42</v>
+      </c>
+      <c r="I51" t="n">
+        <v>29109.539</v>
+      </c>
+      <c r="J51" t="n">
+        <v>29062.453</v>
+      </c>
+      <c r="K51" t="n">
+        <v>29003.794</v>
+      </c>
+      <c r="L51" t="n">
+        <v>28927.469</v>
+      </c>
+      <c r="M51" t="n">
+        <v>28838.797</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>165136.242</v>
+      </c>
+      <c r="D52" t="n">
+        <v>166798.058</v>
+      </c>
+      <c r="E52" t="n">
+        <v>168358.724</v>
+      </c>
+      <c r="F52" t="n">
+        <v>169847.31</v>
+      </c>
+      <c r="G52" t="n">
+        <v>170710.103</v>
+      </c>
+      <c r="H52" t="n">
+        <v>171036.807</v>
+      </c>
+      <c r="I52" t="n">
+        <v>171672.742</v>
+      </c>
+      <c r="J52" t="n">
+        <v>172588.71</v>
+      </c>
+      <c r="K52" t="n">
+        <v>173551.527</v>
+      </c>
+      <c r="L52" t="n">
+        <v>174496.826</v>
+      </c>
+      <c r="M52" t="n">
+        <v>175399.113</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>household_size_and_composition_2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DYB</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DHS</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DYB</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DYB</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>LFS</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>DYB</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LFS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DYB</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,429 +429,657 @@
           <t>geo_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2006</v>
       </c>
       <c r="C3" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D3" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="F3" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="G3" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H3" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="I3" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="J3" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="K3" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L3" t="n">
         <v>2015</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Land area - total</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8028</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8027.7</v>
+      </c>
       <c r="D4" t="n">
-        <v>9814.6</v>
+        <v>8027.7</v>
       </c>
       <c r="E4" t="n">
-        <v>9814.6</v>
+        <v>8027.7</v>
       </c>
       <c r="F4" t="n">
-        <v>9814.6</v>
+        <v>8027.7</v>
       </c>
       <c r="G4" t="n">
-        <v>9814.6</v>
+        <v>8027.7</v>
       </c>
       <c r="H4" t="n">
-        <v>9814.6</v>
+        <v>8027.7</v>
       </c>
       <c r="I4" t="n">
-        <v>9814.6</v>
+        <v>8027.7</v>
       </c>
       <c r="J4" t="n">
-        <v>9814.6</v>
+        <v>8028</v>
       </c>
       <c r="K4" t="n">
-        <v>9811</v>
-      </c>
-      <c r="L4" t="n">
-        <v>9811</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Total area</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>9856</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9856.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9856.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9856.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9856.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9856.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9856.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9856.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>9857</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9857</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Land area - total</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>7961</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7961</v>
-      </c>
-      <c r="F6" t="n">
-        <v>7961</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7961</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7961</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7961</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7961</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7967</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7967</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Total area</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>8028</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8027.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8027.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8027.7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8027.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8027.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8027.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8027.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>8028</v>
-      </c>
-      <c r="L7" t="n">
         <v>8028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Palencia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Land area - total</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
-        <v>8007.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8007.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8007.7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8007.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8007.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8007.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8007.7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8016</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8016</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Palencia</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Total area</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>8052</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>8053</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8053</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>gross_domestic_product_GDP_at_current_market_prices_by_NUTS_3_region</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>geo_name</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>2015</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D10" t="n">
         <v>2016</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E10" t="n">
         <v>2017</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F10" t="n">
         <v>2018</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G10" t="n">
         <v>2019</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H10" t="n">
         <v>2020</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I10" t="n">
         <v>2021</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J10" t="n">
         <v>2022</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K10" t="n">
         <v>2023</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Euro per inhabitant</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>32300</v>
+      </c>
+      <c r="D11" t="n">
+        <v>33300</v>
+      </c>
+      <c r="E11" t="n">
+        <v>34600</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35600</v>
+      </c>
+      <c r="G11" t="n">
+        <v>36600</v>
+      </c>
+      <c r="H11" t="n">
+        <v>32900</v>
+      </c>
+      <c r="I11" t="n">
+        <v>35700</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39200</v>
+      </c>
+      <c r="K11" t="n">
+        <v>42600</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Million euro</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>206231.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>214469.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>224373.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>233735.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>243889.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>221061.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>239837</v>
+      </c>
+      <c r="J12" t="n">
+        <v>267171.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>295939</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>7495.9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>7472.9</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7458.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7769</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7822.9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6945.1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>7637.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8568.299999999999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9406.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>206231.5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>214469.1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>224373.2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>233735.8</v>
-      </c>
-      <c r="F17" t="n">
-        <v>243889.4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>221061.9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>239837</v>
-      </c>
-      <c r="I17" t="n">
-        <v>267171.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>295939</v>
+          <t>population_on_1_january_by_broad_age_group_sex_and_NUTS_3_region</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palencia</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3935.4</v>
+          <t>geo_name</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>4171.9</v>
+        <v>2016</v>
       </c>
       <c r="D18" t="n">
-        <v>4070.3</v>
+        <v>2017</v>
       </c>
       <c r="E18" t="n">
-        <v>4375.1</v>
+        <v>2018</v>
       </c>
       <c r="F18" t="n">
-        <v>4417.9</v>
+        <v>2019</v>
       </c>
       <c r="G18" t="n">
-        <v>4042.4</v>
+        <v>2020</v>
       </c>
       <c r="H18" t="n">
-        <v>4326.9</v>
+        <v>2021</v>
       </c>
       <c r="I18" t="n">
-        <v>4713.3</v>
+        <v>2022</v>
       </c>
       <c r="J18" t="n">
-        <v>5047.5</v>
+        <v>2023</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Females</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3333297</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3359538</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3398209</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3446033</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3500401</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3505239</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3514139</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3583706</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3653105</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3706476</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Males</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3078169</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3099759</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3131714</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3172045</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3219909</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3221401</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3229134</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3288197</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3356163</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3407410</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6411466</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6459297</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6529923</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6618078</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6720310</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6726640</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6743273</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6871903</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7009268</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7113886</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>population_on_1_january_by_broad_age_group_sex_and_NUTS_3_region__by_age_class</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>geo_name</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>65 years or over</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1101434</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1125697</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1152414</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1178613</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1203982</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1210699</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1235279</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1266538</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1304999</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1342648</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>From 15 to 64 years</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4295441</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4315970</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4358532</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4423872</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4506305</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4524261</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4535157</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4638086</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4748699</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4827262</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Less than 15 years</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1014591</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1017630</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1018977</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1015593</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1010023</v>
+      </c>
+      <c r="H30" t="n">
+        <v>991680</v>
+      </c>
+      <c r="I30" t="n">
+        <v>972837</v>
+      </c>
+      <c r="J30" t="n">
+        <v>967279</v>
+      </c>
+      <c r="K30" t="n">
+        <v>955570</v>
+      </c>
+      <c r="L30" t="n">
+        <v>943976</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6411466</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6459297</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6529923</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6618078</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6720310</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6726640</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6743273</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6871903</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7009268</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7113886</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>employment_thousand_persons_by_NUTS_3_region</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>geo_name</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3280.8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3373.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3460.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3557.1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3434.9</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3544.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3716.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3857.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nuts3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="economics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tourism" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="demographics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,400 +415,3753 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:BI77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>area_by_NUTS_3_region</t>
+          <t>consumer_confidence_index</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>geo_name</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2006</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2007</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2008</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2009</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2010</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2011</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2012</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2014</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2015</v>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8028</v>
+        <v>97.70017</v>
       </c>
       <c r="C4" t="n">
-        <v>8027.7</v>
+        <v>98.22165</v>
       </c>
       <c r="D4" t="n">
-        <v>8027.7</v>
+        <v>99.18996</v>
       </c>
       <c r="E4" t="n">
-        <v>8027.7</v>
+        <v>99.98609</v>
       </c>
       <c r="F4" t="n">
-        <v>8027.7</v>
+        <v>100.5841</v>
       </c>
       <c r="G4" t="n">
-        <v>8027.7</v>
+        <v>100.9527</v>
       </c>
       <c r="H4" t="n">
-        <v>8027.7</v>
+        <v>101.1354</v>
       </c>
       <c r="I4" t="n">
-        <v>8027.7</v>
+        <v>101.1922</v>
       </c>
       <c r="J4" t="n">
-        <v>8028</v>
+        <v>101.0743</v>
       </c>
       <c r="K4" t="n">
-        <v>8028</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>gross_domestic_product_GDP_at_current_market_prices_by_NUTS_3_region</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>geo_name</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2015</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2019</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2023</v>
+        <v>100.764</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100.1675</v>
+      </c>
+      <c r="M4" t="n">
+        <v>99.84808</v>
+      </c>
+      <c r="N4" t="n">
+        <v>99.56116</v>
+      </c>
+      <c r="O4" t="n">
+        <v>98.77092</v>
+      </c>
+      <c r="P4" t="n">
+        <v>97.1917</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>96.34094</v>
+      </c>
+      <c r="R4" t="n">
+        <v>95.89206</v>
+      </c>
+      <c r="S4" t="n">
+        <v>95.11839999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>94.38748</v>
+      </c>
+      <c r="U4" t="n">
+        <v>94.29604</v>
+      </c>
+      <c r="V4" t="n">
+        <v>94.5082</v>
+      </c>
+      <c r="W4" t="n">
+        <v>95.00515</v>
+      </c>
+      <c r="X4" t="n">
+        <v>95.73175000000001</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>96.46687</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>97.029</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>97.30398</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>97.41732</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>97.79828999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>98.30374</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>98.96724</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>99.35232000000001</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>99.04723</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>98.43823</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>98.13882</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>98.10148</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>98.22784</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>98.43429</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>98.77981</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>99.14660000000001</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>99.43129</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>99.57366</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>99.63921000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>99.67677</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>99.70948</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>99.92326</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>100.1255</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>100.3225</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>100.4038</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>100.2281</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>99.88108</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>99.51148999999999</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>99.22671</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>99.17956</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>99.14695</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>99.17019000000001</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>99.41817</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>99.74033</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>99.92717</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>99.89664</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>99.76157000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>98.85334</v>
+      </c>
+      <c r="C5" t="n">
+        <v>99.05428000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99.56672</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100.1922</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100.9601</v>
+      </c>
+      <c r="G5" t="n">
+        <v>101.5277</v>
+      </c>
+      <c r="H5" t="n">
+        <v>101.516</v>
+      </c>
+      <c r="I5" t="n">
+        <v>101.277</v>
+      </c>
+      <c r="J5" t="n">
+        <v>101.1606</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100.8813</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100.5841</v>
+      </c>
+      <c r="M5" t="n">
+        <v>100.2511</v>
+      </c>
+      <c r="N5" t="n">
+        <v>99.81926</v>
+      </c>
+      <c r="O5" t="n">
+        <v>99.10256</v>
+      </c>
+      <c r="P5" t="n">
+        <v>97.99290000000001</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>97.40778</v>
+      </c>
+      <c r="R5" t="n">
+        <v>97.14031</v>
+      </c>
+      <c r="S5" t="n">
+        <v>96.95766</v>
+      </c>
+      <c r="T5" t="n">
+        <v>96.91983999999999</v>
+      </c>
+      <c r="U5" t="n">
+        <v>96.99772</v>
+      </c>
+      <c r="V5" t="n">
+        <v>96.95685</v>
+      </c>
+      <c r="W5" t="n">
+        <v>97.04956</v>
+      </c>
+      <c r="X5" t="n">
+        <v>97.1575</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>97.08394</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>96.98483</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>96.95466999999999</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>97.12567</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>97.49252</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>97.94678</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>98.34627</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>98.52292</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>98.47356000000001</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>98.36293000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>98.39339</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>98.6589</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>98.88348000000001</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>98.97713</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>98.83687999999999</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>98.71513</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>98.5899</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>98.59456</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>98.6041</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>98.69248</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>98.9177</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>99.02813</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>98.85326000000001</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>98.52699</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>98.35442</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>98.52218999999999</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>98.62938</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>98.46934</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>98.17923</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>97.93805999999999</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>97.82043</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>97.75543</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>97.66985</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>97.73289</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>98.00545</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>98.17167999999999</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>98.24182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gdp_current_prices</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Euro per inhabitant</t>
-        </is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2017</v>
       </c>
       <c r="C11" t="n">
-        <v>32300</v>
+        <v>2018</v>
       </c>
       <c r="D11" t="n">
-        <v>33300</v>
+        <v>2019</v>
       </c>
       <c r="E11" t="n">
-        <v>34600</v>
+        <v>2020</v>
       </c>
       <c r="F11" t="n">
-        <v>35600</v>
+        <v>2021</v>
       </c>
       <c r="G11" t="n">
-        <v>36600</v>
+        <v>2022</v>
       </c>
       <c r="H11" t="n">
-        <v>32900</v>
+        <v>2023</v>
       </c>
       <c r="I11" t="n">
-        <v>35700</v>
+        <v>2024</v>
       </c>
       <c r="J11" t="n">
-        <v>39200</v>
+        <v>2025</v>
       </c>
       <c r="K11" t="n">
-        <v>42600</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Million euro</t>
-        </is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1321.288</v>
       </c>
       <c r="C12" t="n">
-        <v>206231.5</v>
+        <v>1432.292</v>
       </c>
       <c r="D12" t="n">
-        <v>214469.1</v>
+        <v>1403.651</v>
       </c>
       <c r="E12" t="n">
-        <v>224373.2</v>
+        <v>1288.751</v>
       </c>
       <c r="F12" t="n">
-        <v>233735.8</v>
+        <v>1462.216</v>
       </c>
       <c r="G12" t="n">
-        <v>243889.4</v>
+        <v>1449.99</v>
       </c>
       <c r="H12" t="n">
-        <v>221061.9</v>
+        <v>1619.949</v>
       </c>
       <c r="I12" t="n">
-        <v>239837</v>
+        <v>1725.152</v>
       </c>
       <c r="J12" t="n">
-        <v>267171.6</v>
+        <v>1891.371</v>
       </c>
       <c r="K12" t="n">
-        <v>295939</v>
+        <v>2041.83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2587.955</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2782.838</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2723.094</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2645.806</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2968.405</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2796.987</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3061.093</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3160.902</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3361.557</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3558.562</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gdp_per_capita_current_prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2029</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26725.642</v>
+      </c>
+      <c r="C20" t="n">
+        <v>28326.416</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30526.94</v>
+      </c>
+      <c r="E20" t="n">
+        <v>29664.183</v>
+      </c>
+      <c r="F20" t="n">
+        <v>27188.392</v>
+      </c>
+      <c r="G20" t="n">
+        <v>30792.106</v>
+      </c>
+      <c r="H20" t="n">
+        <v>30154.509</v>
+      </c>
+      <c r="I20" t="n">
+        <v>33312.918</v>
+      </c>
+      <c r="J20" t="n">
+        <v>35151.242</v>
+      </c>
+      <c r="K20" t="n">
+        <v>38039.876</v>
+      </c>
+      <c r="L20" t="n">
+        <v>40581.506</v>
+      </c>
+      <c r="M20" t="n">
+        <v>41888.427</v>
+      </c>
+      <c r="N20" t="n">
+        <v>43059.815</v>
+      </c>
+      <c r="O20" t="n">
+        <v>44363.981</v>
+      </c>
+      <c r="P20" t="n">
+        <v>45765.843</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>37081.496</v>
+      </c>
+      <c r="C21" t="n">
+        <v>38756.651</v>
+      </c>
+      <c r="D21" t="n">
+        <v>41539.756</v>
+      </c>
+      <c r="E21" t="n">
+        <v>40487.302</v>
+      </c>
+      <c r="F21" t="n">
+        <v>39230.928</v>
+      </c>
+      <c r="G21" t="n">
+        <v>43848.345</v>
+      </c>
+      <c r="H21" t="n">
+        <v>41095.77</v>
+      </c>
+      <c r="I21" t="n">
+        <v>44853.761</v>
+      </c>
+      <c r="J21" t="n">
+        <v>46187.295</v>
+      </c>
+      <c r="K21" t="n">
+        <v>48981.965</v>
+      </c>
+      <c r="L21" t="n">
+        <v>51707.603</v>
+      </c>
+      <c r="M21" t="n">
+        <v>53048.574</v>
+      </c>
+      <c r="N21" t="n">
+        <v>54515.019</v>
+      </c>
+      <c r="O21" t="n">
+        <v>56050.844</v>
+      </c>
+      <c r="P21" t="n">
+        <v>57606.464</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>income_share_held_by_highest_10_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>income_share_held_by_lowest_10_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>real_gdp_growth_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>13</v>
+      </c>
+      <c r="C52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C53" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>unemployment_youth_total_15_24_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>44.445</v>
+      </c>
+      <c r="C60" t="n">
+        <v>38.594</v>
+      </c>
+      <c r="D60" t="n">
+        <v>34.362</v>
+      </c>
+      <c r="E60" t="n">
+        <v>32.555</v>
+      </c>
+      <c r="F60" t="n">
+        <v>38.312</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>29.713</v>
+      </c>
+      <c r="I60" t="n">
+        <v>28.747</v>
+      </c>
+      <c r="J60" t="n">
+        <v>26.631</v>
+      </c>
+      <c r="K60" t="n">
+        <v>24.745</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>24.938</v>
+      </c>
+      <c r="C61" t="n">
+        <v>22.572</v>
+      </c>
+      <c r="D61" t="n">
+        <v>20.953</v>
+      </c>
+      <c r="E61" t="n">
+        <v>19.929</v>
+      </c>
+      <c r="F61" t="n">
+        <v>20.398</v>
+      </c>
+      <c r="G61" t="n">
+        <v>19.252</v>
+      </c>
+      <c r="H61" t="n">
+        <v>17.856</v>
+      </c>
+      <c r="I61" t="n">
+        <v>17.419</v>
+      </c>
+      <c r="J61" t="n">
+        <v>18.603</v>
+      </c>
+      <c r="K61" t="n">
+        <v>18.89</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>harmonised_index_of_consumer_prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C69" t="n">
+        <v>7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2028</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="C76" t="n">
+        <v>48.628</v>
+      </c>
+      <c r="D76" t="n">
+        <v>49.078</v>
+      </c>
+      <c r="E76" t="n">
+        <v>49.721</v>
+      </c>
+      <c r="F76" t="n">
+        <v>50.314</v>
+      </c>
+      <c r="G76" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="H76" t="n">
+        <v>51.294</v>
+      </c>
+      <c r="I76" t="n">
+        <v>51.679</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>68.06</v>
+      </c>
+      <c r="C77" t="n">
+        <v>68.246</v>
+      </c>
+      <c r="D77" t="n">
+        <v>68.437</v>
+      </c>
+      <c r="E77" t="n">
+        <v>68.628</v>
+      </c>
+      <c r="F77" t="n">
+        <v>68.821</v>
+      </c>
+      <c r="G77" t="n">
+        <v>69.014</v>
+      </c>
+      <c r="H77" t="n">
+        <v>69.20699999999999</v>
+      </c>
+      <c r="I77" t="n">
+        <v>69.401</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UN_Tourism_8_9_1_TDGDP_04_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.0574</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.50139</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>3.90442</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.83936</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.02301</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UN_Tourism_accommodation_hotels_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.66625227673538</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.84577761675779</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.11392663439669</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.24824041907784</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.27010231370084</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>population_on_1_january_by_broad_age_group_sex_and_NUTS_3_region</t>
+          <t>UN_Tourism_domestic_accommodation_12_2025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>geo_name</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2016</v>
       </c>
       <c r="C18" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D18" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E18" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F18" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G18" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H18" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I18" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K18" t="n">
         <v>2024</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Females</t>
-        </is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>114239</v>
       </c>
       <c r="C19" t="n">
-        <v>3333297</v>
+        <v>115822</v>
       </c>
       <c r="D19" t="n">
-        <v>3359538</v>
+        <v>116500</v>
       </c>
       <c r="E19" t="n">
-        <v>3398209</v>
+        <v>119609</v>
       </c>
       <c r="F19" t="n">
-        <v>3446033</v>
+        <v>51151</v>
       </c>
       <c r="G19" t="n">
-        <v>3500401</v>
+        <v>90700</v>
       </c>
       <c r="H19" t="n">
-        <v>3505239</v>
+        <v>120038</v>
       </c>
       <c r="I19" t="n">
-        <v>3514139</v>
+        <v>157251.063</v>
       </c>
       <c r="J19" t="n">
-        <v>3583706</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3653105</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3706476</v>
+        <v>156540.899</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>132191</v>
+      </c>
+      <c r="C20" t="n">
+        <v>135570</v>
+      </c>
+      <c r="D20" t="n">
+        <v>134674</v>
+      </c>
+      <c r="E20" t="n">
+        <v>138214</v>
+      </c>
+      <c r="F20" t="n">
+        <v>139515</v>
+      </c>
+      <c r="G20" t="n">
+        <v>174647</v>
+      </c>
+      <c r="H20" t="n">
+        <v>142505</v>
+      </c>
+      <c r="I20" t="n">
+        <v>140405</v>
+      </c>
+      <c r="J20" t="n">
+        <v>137433</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UN_Tourism_domestic_trips_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>397134</v>
+      </c>
+      <c r="C27" t="n">
+        <v>448305</v>
+      </c>
+      <c r="D27" t="n">
+        <v>446479</v>
+      </c>
+      <c r="E27" t="n">
+        <v>423572</v>
+      </c>
+      <c r="F27" t="n">
+        <v>250469</v>
+      </c>
+      <c r="G27" t="n">
+        <v>341053</v>
+      </c>
+      <c r="H27" t="n">
+        <v>353920</v>
+      </c>
+      <c r="I27" t="n">
+        <v>370764</v>
+      </c>
+      <c r="J27" t="n">
+        <v>352441</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>255498</v>
+      </c>
+      <c r="C28" t="n">
+        <v>276537</v>
+      </c>
+      <c r="D28" t="n">
+        <v>268152</v>
+      </c>
+      <c r="E28" t="n">
+        <v>260522</v>
+      </c>
+      <c r="F28" t="n">
+        <v>212071</v>
+      </c>
+      <c r="G28" t="n">
+        <v>251666</v>
+      </c>
+      <c r="H28" t="n">
+        <v>274644</v>
+      </c>
+      <c r="I28" t="n">
+        <v>282992</v>
+      </c>
+      <c r="J28" t="n">
+        <v>277344</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_accommodation_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - overnights</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>216930</v>
+      </c>
+      <c r="D35" t="n">
+        <v>224756</v>
+      </c>
+      <c r="E35" t="n">
+        <v>223481</v>
+      </c>
+      <c r="F35" t="n">
+        <v>223386</v>
+      </c>
+      <c r="G35" t="n">
+        <v>41072</v>
+      </c>
+      <c r="H35" t="n">
+        <v>82107</v>
+      </c>
+      <c r="I35" t="n">
+        <v>200329</v>
+      </c>
+      <c r="J35" t="n">
+        <v>280662.496</v>
+      </c>
+      <c r="K35" t="n">
+        <v>299536.376</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>inbound - accommodation - short-term accommodation, hotels and similar (ISIC 5510) - overnights</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>66286</v>
+      </c>
+      <c r="D36" t="n">
+        <v>72738</v>
+      </c>
+      <c r="E36" t="n">
+        <v>78250</v>
+      </c>
+      <c r="F36" t="n">
+        <v>76424</v>
+      </c>
+      <c r="G36" t="n">
+        <v>27459</v>
+      </c>
+      <c r="H36" t="n">
+        <v>34180</v>
+      </c>
+      <c r="I36" t="n">
+        <v>69260</v>
+      </c>
+      <c r="J36" t="n">
+        <v>77025</v>
+      </c>
+      <c r="K36" t="n">
+        <v>77029</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_arrivals_by_purpose_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5703.7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5706.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5636.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6112.7</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1565.465</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2270.304</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4952.511</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4973.06749958168</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5253.19541783694</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>69611.3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>76161.7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>77171.60000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>77396.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>17367.6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>28910.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>66706.8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>80195.98247311771</v>
+      </c>
+      <c r="K44" t="n">
+        <v>88506.1014367087</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>INBD_TRIP_PRPS_BNSS_TOUR</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>11663</v>
+      </c>
+      <c r="D45" t="n">
+        <v>11842</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11064</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11261.2</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>INBD_TRIP_PRPS_PERS_TOUR</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>71020</v>
+      </c>
+      <c r="D46" t="n">
+        <v>74916</v>
+      </c>
+      <c r="E46" t="n">
+        <v>78258</v>
+      </c>
+      <c r="F46" t="n">
+        <v>79652.78</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_arrivals_by_region_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1243</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1314.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1235.9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1340</v>
+      </c>
+      <c r="G53" t="n">
+        <v>262.945</v>
+      </c>
+      <c r="H53" t="n">
+        <v>250.284</v>
+      </c>
+      <c r="I53" t="n">
+        <v>830.221</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1025.13128294283</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1297.90576947888</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4573.9</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5866</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6370.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7092.1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1320.48</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1867.265</v>
+      </c>
+      <c r="I54" t="n">
+        <v>6359.413</v>
+      </c>
+      <c r="J54" t="n">
+        <v>8470.624000010759</v>
+      </c>
+      <c r="K54" t="n">
+        <v>9428.970904708071</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1904.7</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2299</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2560.7</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2977</v>
+      </c>
+      <c r="G55" t="n">
+        <v>562.403</v>
+      </c>
+      <c r="H55" t="n">
+        <v>230.302</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1086.684</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2360.18863897558</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2817.03795662791</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>67047.39999999999</v>
+      </c>
+      <c r="D56" t="n">
+        <v>71695.89999999999</v>
+      </c>
+      <c r="E56" t="n">
+        <v>71903.89999999999</v>
+      </c>
+      <c r="F56" t="n">
+        <v>71377.8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>16676.276</v>
+      </c>
+      <c r="H56" t="n">
+        <v>28505.919</v>
+      </c>
+      <c r="I56" t="n">
+        <v>62765.346</v>
+      </c>
+      <c r="J56" t="n">
+        <v>72386.9099346476</v>
+      </c>
+      <c r="K56" t="n">
+        <v>79114.75530078731</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>424.7</v>
+      </c>
+      <c r="G57" t="n">
+        <v>76.34399999999999</v>
+      </c>
+      <c r="H57" t="n">
+        <v>281.162</v>
+      </c>
+      <c r="I57" t="n">
+        <v>416.759</v>
+      </c>
+      <c r="J57" t="n">
+        <v>617.95432944935</v>
+      </c>
+      <c r="K57" t="n">
+        <v>765.914310277042</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>South Asia (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>159.3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>227</v>
+      </c>
+      <c r="E58" t="n">
+        <v>321</v>
+      </c>
+      <c r="F58" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.655</v>
+      </c>
+      <c r="H58" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="I58" t="n">
+        <v>200.859</v>
+      </c>
+      <c r="J58" t="n">
+        <v>308.24178665693</v>
+      </c>
+      <c r="K58" t="n">
+        <v>334.712612593961</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Africa (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2926.7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2799.2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2919.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3249.1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>649.819</v>
+      </c>
+      <c r="H59" t="n">
+        <v>750</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Americas (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>8131.4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8631.6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>8956</v>
+      </c>
+      <c r="F60" t="n">
+        <v>8269</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1653.79</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>East Asia and the Pacific (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5640.9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5683.2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6041.6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5282.8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1056.565</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1230</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Europe (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>64727.9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>68292.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>69955</v>
+      </c>
+      <c r="F62" t="n">
+        <v>72766.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>38054.506</v>
+      </c>
+      <c r="H62" t="n">
+        <v>44185.21</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Middle East (UNWTO total)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1255.2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1351.3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1449.4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1346.6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>269.32</v>
+      </c>
+      <c r="H63" t="n">
+        <v>310</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_arrivals_by_transport_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>60343.7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>66639.5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>67545.7</v>
+      </c>
+      <c r="F70" t="n">
+        <v>68691.89999999999</v>
+      </c>
+      <c r="G70" t="n">
+        <v>13657.664</v>
+      </c>
+      <c r="H70" t="n">
+        <v>24431.89</v>
+      </c>
+      <c r="I70" t="n">
+        <v>59307.849</v>
+      </c>
+      <c r="J70" t="n">
+        <v>69564.23140752919</v>
+      </c>
+      <c r="K70" t="n">
+        <v>77119.7871470598</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>13335.9</v>
+      </c>
+      <c r="D71" t="n">
+        <v>13263.4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>13250.6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>13096.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5052.128</v>
+      </c>
+      <c r="H71" t="n">
+        <v>6521.955</v>
+      </c>
+      <c r="I71" t="n">
+        <v>11199.208</v>
+      </c>
+      <c r="J71" t="n">
+        <v>13745.4613453271</v>
+      </c>
+      <c r="K71" t="n">
+        <v>14535.4190698515</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1635.4</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1965.7</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2012.1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1720.8</v>
+      </c>
+      <c r="G72" t="n">
+        <v>223.311</v>
+      </c>
+      <c r="H72" t="n">
+        <v>226.957</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1152.225</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1859.35721985221</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2104.09063755124</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - air - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>26350.3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>27508.9</v>
+      </c>
+      <c r="E73" t="n">
+        <v>28880.3</v>
+      </c>
+      <c r="F73" t="n">
+        <v>29395.1</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - by land - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>51237.6</v>
+      </c>
+      <c r="D74" t="n">
+        <v>53434.9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>54667</v>
+      </c>
+      <c r="F74" t="n">
+        <v>55641.4</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>inbound - trips - transport - water - overnight visitors (tourists)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5094.3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5814.4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5774.6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5877.5</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UN_Tourism_inbound_expenditure_12_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>18380.4147013811</v>
+      </c>
+      <c r="H82" t="n">
+        <v>34176.1559870135</v>
+      </c>
+      <c r="I82" t="n">
+        <v>72083.3294863503</v>
+      </c>
+      <c r="J82" t="n">
+        <v>92144.2801105462</v>
+      </c>
+      <c r="K82" t="n">
+        <v>106656.535197297</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>inbound - expenditure - balance of payments - total - visitors</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>63557</v>
+      </c>
+      <c r="D83" t="n">
+        <v>67717</v>
+      </c>
+      <c r="E83" t="n">
+        <v>72518</v>
+      </c>
+      <c r="F83" t="n">
+        <v>70786</v>
+      </c>
+      <c r="G83" t="n">
+        <v>35826.3235656593</v>
+      </c>
+      <c r="H83" t="n">
+        <v>44430.2698336295</v>
+      </c>
+      <c r="I83" t="n">
+        <v>66781.1814155116</v>
+      </c>
+      <c r="J83" t="n">
+        <v>80268.9592165082</v>
+      </c>
+      <c r="K83" t="n">
+        <v>85939.6111204944</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NatChange</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-2.588</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-33.375</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-56.776</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-60.87</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-152.023</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-116.872</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-141.849</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-110.642</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-122.249</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-127.192</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-133.07</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>155.927</v>
+      </c>
+      <c r="D5" t="n">
+        <v>121.383</v>
+      </c>
+      <c r="E5" t="n">
+        <v>112.241</v>
+      </c>
+      <c r="F5" t="n">
+        <v>102.692</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31.378</v>
+      </c>
+      <c r="H5" t="n">
+        <v>48.105</v>
+      </c>
+      <c r="I5" t="n">
+        <v>28.779</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.796</v>
+      </c>
+      <c r="K5" t="n">
+        <v>14.228</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.057</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.865</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NetMigrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>201.135</v>
+      </c>
+      <c r="D12" t="n">
+        <v>337.467</v>
+      </c>
+      <c r="E12" t="n">
+        <v>464.783</v>
+      </c>
+      <c r="F12" t="n">
+        <v>236.854</v>
+      </c>
+      <c r="G12" t="n">
+        <v>144.385</v>
+      </c>
+      <c r="H12" t="n">
+        <v>299.779</v>
+      </c>
+      <c r="I12" t="n">
+        <v>119.099</v>
+      </c>
+      <c r="J12" t="n">
+        <v>111.674</v>
+      </c>
+      <c r="K12" t="n">
+        <v>96.63</v>
+      </c>
+      <c r="L12" t="n">
+        <v>85.30500000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>88.667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>102.984</v>
+      </c>
+      <c r="D13" t="n">
+        <v>132.925</v>
+      </c>
+      <c r="E13" t="n">
+        <v>71.97199999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>145.593</v>
+      </c>
+      <c r="G13" t="n">
+        <v>131.465</v>
+      </c>
+      <c r="H13" t="n">
+        <v>179.377</v>
+      </c>
+      <c r="I13" t="n">
+        <v>91.86199999999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>90.527</v>
+      </c>
+      <c r="K13" t="n">
+        <v>91.73699999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>88.533</v>
+      </c>
+      <c r="M13" t="n">
+        <v>93.271</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TPopulation1Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2029</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2030</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2031</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2032</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2033</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2035</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Males</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3078169</v>
+        <v>46680.827</v>
       </c>
       <c r="D20" t="n">
-        <v>3099759</v>
+        <v>46784.715</v>
       </c>
       <c r="E20" t="n">
-        <v>3131714</v>
+        <v>46952.476</v>
       </c>
       <c r="F20" t="n">
-        <v>3172045</v>
+        <v>47233.166</v>
       </c>
       <c r="G20" t="n">
-        <v>3219909</v>
+        <v>47637.072</v>
       </c>
       <c r="H20" t="n">
-        <v>3221401</v>
+        <v>47721.906</v>
       </c>
       <c r="I20" t="n">
-        <v>3229134</v>
+        <v>47749.421</v>
       </c>
       <c r="J20" t="n">
-        <v>3288197</v>
+        <v>47907.344</v>
       </c>
       <c r="K20" t="n">
-        <v>3356163</v>
+        <v>47915.815</v>
       </c>
       <c r="L20" t="n">
-        <v>3407410</v>
+        <v>47905.238</v>
+      </c>
+      <c r="M20" t="n">
+        <v>47874.678</v>
+      </c>
+      <c r="N20" t="n">
+        <v>47826.907</v>
+      </c>
+      <c r="O20" t="n">
+        <v>47777.635</v>
+      </c>
+      <c r="P20" t="n">
+        <v>47719.497</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>47652.032</v>
+      </c>
+      <c r="R20" t="n">
+        <v>47569.007</v>
+      </c>
+      <c r="S20" t="n">
+        <v>47477.971</v>
+      </c>
+      <c r="T20" t="n">
+        <v>47389.074</v>
+      </c>
+      <c r="U20" t="n">
+        <v>47299.037</v>
+      </c>
+      <c r="V20" t="n">
+        <v>47205.242</v>
+      </c>
+      <c r="W20" t="n">
+        <v>47103.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6411466</v>
+        <v>65001.118</v>
       </c>
       <c r="D21" t="n">
-        <v>6459297</v>
+        <v>65172.593</v>
       </c>
       <c r="E21" t="n">
-        <v>6529923</v>
+        <v>65396.959</v>
       </c>
       <c r="F21" t="n">
-        <v>6618078</v>
+        <v>65642.126</v>
       </c>
       <c r="G21" t="n">
-        <v>6720310</v>
+        <v>65816.792</v>
       </c>
       <c r="H21" t="n">
-        <v>6726640</v>
+        <v>65993.76300000001</v>
       </c>
       <c r="I21" t="n">
-        <v>6743273</v>
+        <v>66173.33199999999</v>
       </c>
       <c r="J21" t="n">
-        <v>6871903</v>
+        <v>66381.485</v>
       </c>
       <c r="K21" t="n">
-        <v>7009268</v>
+        <v>66496.159</v>
       </c>
       <c r="L21" t="n">
-        <v>7113886</v>
+        <v>66600.902</v>
+      </c>
+      <c r="M21" t="n">
+        <v>66700.70699999999</v>
+      </c>
+      <c r="N21" t="n">
+        <v>66792.094</v>
+      </c>
+      <c r="O21" t="n">
+        <v>66884.429</v>
+      </c>
+      <c r="P21" t="n">
+        <v>66972.84299999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>67063.815</v>
+      </c>
+      <c r="R21" t="n">
+        <v>67151.567</v>
+      </c>
+      <c r="S21" t="n">
+        <v>67238.143</v>
+      </c>
+      <c r="T21" t="n">
+        <v>67325.81600000001</v>
+      </c>
+      <c r="U21" t="n">
+        <v>67412.827</v>
+      </c>
+      <c r="V21" t="n">
+        <v>67503.47199999999</v>
+      </c>
+      <c r="W21" t="n">
+        <v>67592.41899999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>population_on_1_january_by_broad_age_group_sex_and_NUTS_3_region__by_age_class</t>
+          <t>TPopulationFemale1July</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>geo_name</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -815,272 +4170,1269 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D27" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E27" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F27" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G27" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H27" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I27" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J27" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L27" t="n">
-        <v>2025</v>
+        <v>2026</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2027</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>65 years or over</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1101434</v>
+        <v>23831.398</v>
       </c>
       <c r="D28" t="n">
-        <v>1125697</v>
+        <v>23956.747</v>
       </c>
       <c r="E28" t="n">
-        <v>1152414</v>
+        <v>24135.524</v>
       </c>
       <c r="F28" t="n">
-        <v>1178613</v>
+        <v>24262.247</v>
       </c>
       <c r="G28" t="n">
-        <v>1203982</v>
+        <v>24292.717</v>
       </c>
       <c r="H28" t="n">
-        <v>1210699</v>
+        <v>24342.743</v>
       </c>
       <c r="I28" t="n">
-        <v>1235279</v>
+        <v>24387.156</v>
       </c>
       <c r="J28" t="n">
-        <v>1266538</v>
+        <v>24388.607</v>
       </c>
       <c r="K28" t="n">
-        <v>1304999</v>
+        <v>24382.98</v>
       </c>
       <c r="L28" t="n">
-        <v>1342648</v>
+        <v>24368.467</v>
+      </c>
+      <c r="M28" t="n">
+        <v>24349.703</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>From 15 to 64 years</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4295441</v>
+        <v>33679.218</v>
       </c>
       <c r="D29" t="n">
-        <v>4315970</v>
+        <v>33798.505</v>
       </c>
       <c r="E29" t="n">
-        <v>4358532</v>
+        <v>33897.082</v>
       </c>
       <c r="F29" t="n">
-        <v>4423872</v>
+        <v>33981.533</v>
       </c>
       <c r="G29" t="n">
-        <v>4506305</v>
+        <v>34067.064</v>
       </c>
       <c r="H29" t="n">
-        <v>4524261</v>
+        <v>34160.426</v>
       </c>
       <c r="I29" t="n">
-        <v>4535157</v>
+        <v>34236.535</v>
       </c>
       <c r="J29" t="n">
-        <v>4638086</v>
+        <v>34286.854</v>
       </c>
       <c r="K29" t="n">
-        <v>4748699</v>
+        <v>34338.168</v>
       </c>
       <c r="L29" t="n">
-        <v>4827262</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Less than 15 years</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1014591</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1017630</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1018977</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1015593</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1010023</v>
-      </c>
-      <c r="H30" t="n">
-        <v>991680</v>
-      </c>
-      <c r="I30" t="n">
-        <v>972837</v>
-      </c>
-      <c r="J30" t="n">
-        <v>967279</v>
-      </c>
-      <c r="K30" t="n">
-        <v>955570</v>
-      </c>
-      <c r="L30" t="n">
-        <v>943976</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>6411466</v>
-      </c>
-      <c r="D31" t="n">
-        <v>6459297</v>
-      </c>
-      <c r="E31" t="n">
-        <v>6529923</v>
-      </c>
-      <c r="F31" t="n">
-        <v>6618078</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6720310</v>
-      </c>
-      <c r="H31" t="n">
-        <v>6726640</v>
-      </c>
-      <c r="I31" t="n">
-        <v>6743273</v>
-      </c>
-      <c r="J31" t="n">
-        <v>6871903</v>
-      </c>
-      <c r="K31" t="n">
-        <v>7009268</v>
-      </c>
-      <c r="L31" t="n">
-        <v>7113886</v>
+        <v>34387.037</v>
+      </c>
+      <c r="M29" t="n">
+        <v>34435.062</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TPopulationMale1July</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>employment_thousand_persons_by_NUTS_3_region</t>
-        </is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>23037.197</v>
+      </c>
+      <c r="D36" t="n">
+        <v>23136.074</v>
+      </c>
+      <c r="E36" t="n">
+        <v>23299.594</v>
+      </c>
+      <c r="F36" t="n">
+        <v>23417.243</v>
+      </c>
+      <c r="G36" t="n">
+        <v>23442.946</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23485.64</v>
+      </c>
+      <c r="I36" t="n">
+        <v>23524.424</v>
+      </c>
+      <c r="J36" t="n">
+        <v>23521.92</v>
+      </c>
+      <c r="K36" t="n">
+        <v>23506.978</v>
+      </c>
+      <c r="L36" t="n">
+        <v>23482.325</v>
+      </c>
+      <c r="M36" t="n">
+        <v>23452.568</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>geo_name</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2016</v>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="C37" t="n">
-        <v>2017</v>
+        <v>31605.558</v>
       </c>
       <c r="D37" t="n">
-        <v>2018</v>
+        <v>31721.037</v>
       </c>
       <c r="E37" t="n">
-        <v>2019</v>
+        <v>31832.377</v>
       </c>
       <c r="F37" t="n">
-        <v>2020</v>
+        <v>31923.744</v>
       </c>
       <c r="G37" t="n">
+        <v>32016.483</v>
+      </c>
+      <c r="H37" t="n">
+        <v>32116.982</v>
+      </c>
+      <c r="I37" t="n">
+        <v>32202.286</v>
+      </c>
+      <c r="J37" t="n">
+        <v>32261.677</v>
+      </c>
+      <c r="K37" t="n">
+        <v>32312.637</v>
+      </c>
+      <c r="L37" t="n">
+        <v>32359.364</v>
+      </c>
+      <c r="M37" t="n">
+        <v>32403.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>population_by_Five_year_Age_Groups_Both_Sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
         <v>2021</v>
       </c>
-      <c r="H37" t="n">
+      <c r="D43" t="n">
         <v>2022</v>
       </c>
-      <c r="I37" t="n">
+      <c r="E43" t="n">
         <v>2023</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3280.8</v>
-      </c>
-      <c r="C38" t="n">
-        <v>3373.2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>3460.2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3557.1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>3434.9</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3544.7</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3716.2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3857.6</v>
-      </c>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1880.1205</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1811.811</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1762.9375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2508.991</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2488.6875</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2440.4135</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>12.181</v>
+      </c>
+      <c r="D46" t="n">
+        <v>13.145</v>
+      </c>
+      <c r="E46" t="n">
+        <v>14.271</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2441.181</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2482.022</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2523.2495</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2414.2975</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2426.8455</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2437.1385</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2568.6625</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2536.98</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2497.2685</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2816.0755</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2789.5235</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2759.065</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3191.626</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3102.8365</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3029.0875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3864.732500000001</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3756.8475</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3633.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3959.072</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4003.9435</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4033.417</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2250.1155</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2202.2055</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2149.078</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3750.603</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3779.729</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3823.3525</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3549.265</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3625.354</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3681.1915</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3082.872</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3166.0035</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3245.963</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2520.3515</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2596.4925</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2689.7955</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2230.308</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2261.6905</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2283.599</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1819.79</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1891.8745</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1960.251</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>80-84</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1295.914</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1284.183</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1333.4525</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>85-89</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1010.5055</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1013.36</v>
+      </c>
+      <c r="E62" t="n">
+        <v>989.9175</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>90-94</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>456.6465</v>
+      </c>
+      <c r="D63" t="n">
+        <v>476.819</v>
+      </c>
+      <c r="E63" t="n">
+        <v>499.2935</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>95-99</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>112.353</v>
+      </c>
+      <c r="D64" t="n">
+        <v>118.029</v>
+      </c>
+      <c r="E64" t="n">
+        <v>124.9375</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3459.9985</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3418.4805</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3396.9025</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>4084.972</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4062.72</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4034.51</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>24.822</v>
+      </c>
+      <c r="D67" t="n">
+        <v>27.626</v>
+      </c>
+      <c r="E67" t="n">
+        <v>29.475</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4053.9875</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4084.77</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4104.08</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3949.6365</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4010.3435</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4023.621</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>3691.3525</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3707.2085</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3774.105500000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3939.8475</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3909.9315</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3856.133</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3999.5245</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3977.662</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3982.1815</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4135.150000000001</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4162.128000000001</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4146.768</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>4292.211</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4203.534500000001</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4127.602</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3851.2735</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3806.7805</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3720.1965</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>4302.087500000001</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4339.6495</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4388.9825</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4305.7735</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4306.1635</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4288.126999999999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4106.648</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4119.6835</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4145.7385</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3845.386</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3859.94</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3878.4595</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3652.5735</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3659.762999999999</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3652.8325</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2349.116</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2589.8755</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2818.432</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>80-84</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1790.376</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1770.1035</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1791.701</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>85-89</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1349.6085</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1344.4475</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1343.811</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>90-94</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>694.876</v>
+      </c>
+      <c r="D84" t="n">
+        <v>708.5505000000001</v>
+      </c>
+      <c r="E84" t="n">
+        <v>722.0875000000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>95-99</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>204.327</v>
+      </c>
+      <c r="D85" t="n">
+        <v>208.047</v>
+      </c>
+      <c r="E85" t="n">
+        <v>213.0755</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>household_size_and_composition_2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>DYB</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LFS</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DYB</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LFS</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -1474,71 +1474,71 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C59" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="D59" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="E59" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="F59" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="G59" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="H59" t="n">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="I59" t="n">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="J59" t="n">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="K59" t="n">
-        <v>2025</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3049974583544135</v>
+        <v>2.1</v>
       </c>
       <c r="C60" t="n">
-        <v>1.162278697649755</v>
+        <v>5.9</v>
       </c>
       <c r="D60" t="n">
-        <v>2.09910812542079</v>
+        <v>5.7</v>
       </c>
       <c r="E60" t="n">
-        <v>1.298241662778914</v>
+        <v>2.3</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5240757210011437</v>
+        <v>1.1</v>
       </c>
       <c r="G60" t="n">
-        <v>2.066416000505547</v>
+        <v>1.5</v>
       </c>
       <c r="H60" t="n">
-        <v>5.905798223075291</v>
+        <v>1.9</v>
       </c>
       <c r="I60" t="n">
-        <v>5.664155272830939</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
-        <v>2.317523548694967</v>
+        <v>1.9</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9273716583866166</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="64">

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI67"/>
+  <dimension ref="A1:BI71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,616 +998,773 @@
         <v>3558.562</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WEOWORLD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>81951.77099999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>87038.871</v>
+      </c>
+      <c r="D12" t="n">
+        <v>88323.317</v>
+      </c>
+      <c r="E12" t="n">
+        <v>86051.31299999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>98225.82000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>102401.753</v>
+      </c>
+      <c r="H12" t="n">
+        <v>106939.787</v>
+      </c>
+      <c r="I12" t="n">
+        <v>111112.86</v>
+      </c>
+      <c r="J12" t="n">
+        <v>117165.394</v>
+      </c>
+      <c r="K12" t="n">
+        <v>123584.494</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>gdp_per_capita_current_prices</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>geo</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2017</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2021</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2022</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2027</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2028</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2029</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2030</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2027</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2028</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2029</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>37081.496</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>38756.651</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>41539.756</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>40487.302</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>39230.928</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>43848.345</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>41095.77</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>44853.761</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>46187.295</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>48981.965</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>51707.603</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>53048.574</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>54515.019</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>56050.844</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>57606.464</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>income_share_held_by_highest_10_percent</t>
-        </is>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WEOWORLD</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10431.887</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10964.629</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11522.387</v>
+      </c>
+      <c r="E20" t="n">
+        <v>11569.296</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11163.104</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12636.815</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13064.779</v>
+      </c>
+      <c r="I20" t="n">
+        <v>13514.172</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13904.733</v>
+      </c>
+      <c r="K20" t="n">
+        <v>14613.202</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15279.622</v>
+      </c>
+      <c r="M20" t="n">
+        <v>15882.97</v>
+      </c>
+      <c r="N20" t="n">
+        <v>16526.382</v>
+      </c>
+      <c r="O20" t="n">
+        <v>17174.161</v>
+      </c>
+      <c r="P20" t="n">
+        <v>17860.167</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>income_share_held_by_highest_10_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B26" t="n">
         <v>2016</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C26" t="n">
         <v>2017</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D26" t="n">
         <v>2018</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>2019</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>2020</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>2021</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>2022</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>2023</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B27" t="n">
         <v>25.9</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C27" t="n">
         <v>25.8</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D27" t="n">
         <v>26.7</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>24.8</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>24.5</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G27" t="n">
         <v>24.9</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>24.6</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>25</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>income_share_held_by_lowest_10_percent</t>
-        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>income_share_held_by_lowest_10_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B33" t="n">
         <v>2016</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C33" t="n">
         <v>2017</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D33" t="n">
         <v>2018</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E33" t="n">
         <v>2019</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F33" t="n">
         <v>2020</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G33" t="n">
         <v>2021</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H33" t="n">
         <v>2022</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I33" t="n">
         <v>2023</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B34" t="n">
         <v>3.2</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C34" t="n">
         <v>3.2</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D34" t="n">
         <v>3.2</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E34" t="n">
         <v>3.1</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F34" t="n">
         <v>3.1</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G34" t="n">
         <v>2.9</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H34" t="n">
         <v>3</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I34" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>real_gdp_growth_percent</t>
-        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>real_gdp_growth_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B40" t="n">
         <v>2021</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C40" t="n">
         <v>2022</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D40" t="n">
         <v>2023</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E40" t="n">
         <v>2024</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F40" t="n">
         <v>2025</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G40" t="n">
         <v>2026</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H40" t="n">
         <v>2027</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I40" t="n">
         <v>2028</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J40" t="n">
         <v>2029</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K40" t="n">
         <v>2030</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B41" t="n">
         <v>6.8</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C41" t="n">
         <v>2.8</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D41" t="n">
         <v>1.6</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E41" t="n">
         <v>1.1</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F41" t="n">
         <v>0.7</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G41" t="n">
         <v>0.9</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H41" t="n">
         <v>1.2</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I41" t="n">
         <v>1.3</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J41" t="n">
         <v>1.2</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K41" t="n">
         <v>1.2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>unemployment_rate</t>
-        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B47" t="n">
         <v>2022</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C47" t="n">
         <v>2023</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D47" t="n">
         <v>2024</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E47" t="n">
         <v>2025</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F47" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B48" t="n">
         <v>7.3</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C48" t="n">
         <v>7.3</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D48" t="n">
         <v>7.4</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E48" t="n">
         <v>7.6</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F48" t="n">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>unemployment_youth_total_15_24_percent</t>
-        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>unemployment_youth_total_15_24_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B54" t="n">
         <v>2016</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C54" t="n">
         <v>2017</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D54" t="n">
         <v>2018</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E54" t="n">
         <v>2019</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F54" t="n">
         <v>2020</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G54" t="n">
         <v>2021</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H54" t="n">
         <v>2022</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I54" t="n">
         <v>2023</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J54" t="n">
         <v>2024</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K54" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B55" t="n">
         <v>24.938</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C55" t="n">
         <v>22.572</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D55" t="n">
         <v>20.953</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>19.929</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F55" t="n">
         <v>20.398</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G55" t="n">
         <v>19.252</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>17.856</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I55" t="n">
         <v>17.419</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J55" t="n">
         <v>18.603</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K55" t="n">
         <v>18.89</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>harmonised_index_of_consumer_prices</t>
-        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>harmonised_index_of_consumer_prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B61" t="n">
         <v>2021</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C61" t="n">
         <v>2022</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D61" t="n">
         <v>2023</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E61" t="n">
         <v>2024</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F61" t="n">
         <v>2025</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G61" t="n">
         <v>2026</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H61" t="n">
         <v>2027</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I61" t="n">
         <v>2028</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J61" t="n">
         <v>2029</v>
       </c>
-      <c r="K59" t="n">
+      <c r="K61" t="n">
         <v>2030</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B62" t="n">
         <v>2.1</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C62" t="n">
         <v>5.9</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D62" t="n">
         <v>5.7</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E62" t="n">
         <v>2.3</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F62" t="n">
         <v>1.1</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G62" t="n">
         <v>1.5</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H62" t="n">
         <v>1.9</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I62" t="n">
         <v>1.9</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J62" t="n">
         <v>1.9</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K62" t="n">
         <v>1.9</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>geo</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C66" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E66" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G66" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2028</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2029</v>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WEOWORLD</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D63" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>population</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2028</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B70" t="n">
         <v>68.06</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C70" t="n">
         <v>68.246</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D70" t="n">
         <v>68.437</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E70" t="n">
         <v>68.628</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F70" t="n">
         <v>68.821</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G70" t="n">
         <v>69.014</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H70" t="n">
         <v>69.20699999999999</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I70" t="n">
         <v>69.401</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WEOWORLD</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>7838.001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>7913.159</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7991.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8017.777</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8088.191</v>
+      </c>
+      <c r="G71" t="n">
+        <v>8160.071</v>
+      </c>
+      <c r="H71" t="n">
+        <v>8231.071</v>
+      </c>
+      <c r="I71" t="n">
+        <v>8301.790999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/world/views_single_sheet.xlsx
+++ b/outputs/world/views_single_sheet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI71"/>
+  <dimension ref="A1:BI79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,806 +964,1120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ADVEC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2587.955</v>
+        <v>49016.624</v>
       </c>
       <c r="C11" t="n">
-        <v>2782.838</v>
+        <v>51868.982</v>
       </c>
       <c r="D11" t="n">
-        <v>2723.094</v>
+        <v>52406.467</v>
       </c>
       <c r="E11" t="n">
-        <v>2645.806</v>
+        <v>51561.468</v>
       </c>
       <c r="F11" t="n">
-        <v>2968.405</v>
+        <v>57609.524</v>
       </c>
       <c r="G11" t="n">
-        <v>2796.987</v>
+        <v>58945.923</v>
       </c>
       <c r="H11" t="n">
-        <v>3061.093</v>
+        <v>62310.258</v>
       </c>
       <c r="I11" t="n">
-        <v>3160.902</v>
+        <v>64901.125</v>
       </c>
       <c r="J11" t="n">
-        <v>3361.557</v>
+        <v>68598.61900000001</v>
       </c>
       <c r="K11" t="n">
-        <v>3558.562</v>
+        <v>72202.717</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>14867.435</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16100.805</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15812.179</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15495.36</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17507.089</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17040.068</v>
+      </c>
+      <c r="H12" t="n">
+        <v>18644.233</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19459.717</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21096.78</v>
+      </c>
+      <c r="K12" t="n">
+        <v>22515.043</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2587.955</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2782.838</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2723.094</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2645.806</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2968.405</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2796.987</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3061.093</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3160.902</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3361.557</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3558.562</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>WEOWORLD</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B14" t="n">
         <v>81951.77099999999</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C14" t="n">
         <v>87038.871</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D14" t="n">
         <v>88323.317</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E14" t="n">
         <v>86051.31299999999</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F14" t="n">
         <v>98225.82000000001</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G14" t="n">
         <v>102401.753</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H14" t="n">
         <v>106939.787</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" t="n">
         <v>111112.86</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J14" t="n">
         <v>117165.394</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K14" t="n">
         <v>123584.494</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>gdp_per_capita_current_prices</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>geo</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2017</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2021</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2022</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2027</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2028</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2029</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>37081.496</v>
-      </c>
-      <c r="C19" t="n">
-        <v>38756.651</v>
-      </c>
-      <c r="D19" t="n">
-        <v>41539.756</v>
-      </c>
-      <c r="E19" t="n">
-        <v>40487.302</v>
-      </c>
-      <c r="F19" t="n">
-        <v>39230.928</v>
-      </c>
-      <c r="G19" t="n">
-        <v>43848.345</v>
-      </c>
-      <c r="H19" t="n">
-        <v>41095.77</v>
-      </c>
-      <c r="I19" t="n">
-        <v>44853.761</v>
-      </c>
-      <c r="J19" t="n">
-        <v>46187.295</v>
-      </c>
-      <c r="K19" t="n">
-        <v>48981.965</v>
-      </c>
-      <c r="L19" t="n">
-        <v>51707.603</v>
-      </c>
-      <c r="M19" t="n">
-        <v>53048.574</v>
-      </c>
-      <c r="N19" t="n">
-        <v>54515.019</v>
-      </c>
-      <c r="O19" t="n">
-        <v>56050.844</v>
-      </c>
-      <c r="P19" t="n">
-        <v>57606.464</v>
+          <t>gdp_per_capita_current_prices</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WEOWORLD</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10431.887</v>
+        <v>2016</v>
       </c>
       <c r="C20" t="n">
-        <v>10964.629</v>
+        <v>2017</v>
       </c>
       <c r="D20" t="n">
-        <v>11522.387</v>
+        <v>2018</v>
       </c>
       <c r="E20" t="n">
-        <v>11569.296</v>
+        <v>2019</v>
       </c>
       <c r="F20" t="n">
-        <v>11163.104</v>
+        <v>2020</v>
       </c>
       <c r="G20" t="n">
-        <v>12636.815</v>
+        <v>2021</v>
       </c>
       <c r="H20" t="n">
-        <v>13064.779</v>
+        <v>2022</v>
       </c>
       <c r="I20" t="n">
-        <v>13514.172</v>
+        <v>2023</v>
       </c>
       <c r="J20" t="n">
-        <v>13904.733</v>
+        <v>2024</v>
       </c>
       <c r="K20" t="n">
-        <v>14613.202</v>
+        <v>2025</v>
       </c>
       <c r="L20" t="n">
-        <v>15279.622</v>
+        <v>2026</v>
       </c>
       <c r="M20" t="n">
-        <v>15882.97</v>
+        <v>2027</v>
       </c>
       <c r="N20" t="n">
-        <v>16526.382</v>
+        <v>2028</v>
       </c>
       <c r="O20" t="n">
-        <v>17174.161</v>
+        <v>2029</v>
       </c>
       <c r="P20" t="n">
-        <v>17860.167</v>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADVEC</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>44090.652</v>
+      </c>
+      <c r="C21" t="n">
+        <v>45842.944</v>
+      </c>
+      <c r="D21" t="n">
+        <v>48316.427</v>
+      </c>
+      <c r="E21" t="n">
+        <v>48628.597</v>
+      </c>
+      <c r="F21" t="n">
+        <v>47672.314</v>
+      </c>
+      <c r="G21" t="n">
+        <v>53226.204</v>
+      </c>
+      <c r="H21" t="n">
+        <v>54189.764</v>
+      </c>
+      <c r="I21" t="n">
+        <v>56864.052</v>
+      </c>
+      <c r="J21" t="n">
+        <v>58846.003</v>
+      </c>
+      <c r="K21" t="n">
+        <v>61967.09</v>
+      </c>
+      <c r="L21" t="n">
+        <v>65067.361</v>
+      </c>
+      <c r="M21" t="n">
+        <v>67360.603</v>
+      </c>
+      <c r="N21" t="n">
+        <v>69747.704</v>
+      </c>
+      <c r="O21" t="n">
+        <v>72116.92600000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>74669.878</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>31488.796</v>
+      </c>
+      <c r="C22" t="n">
+        <v>33433.257</v>
+      </c>
+      <c r="D22" t="n">
+        <v>36149.538</v>
+      </c>
+      <c r="E22" t="n">
+        <v>35438.535</v>
+      </c>
+      <c r="F22" t="n">
+        <v>34705.769</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39322.328</v>
+      </c>
+      <c r="H22" t="n">
+        <v>38176.87</v>
+      </c>
+      <c r="I22" t="n">
+        <v>41565.549</v>
+      </c>
+      <c r="J22" t="n">
+        <v>43263.268</v>
+      </c>
+      <c r="K22" t="n">
+        <v>46804.719</v>
+      </c>
+      <c r="L22" t="n">
+        <v>49878.524</v>
+      </c>
+      <c r="M22" t="n">
+        <v>51516.589</v>
+      </c>
+      <c r="N22" t="n">
+        <v>53226.339</v>
+      </c>
+      <c r="O22" t="n">
+        <v>55025.27</v>
+      </c>
+      <c r="P22" t="n">
+        <v>56866.121</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>37081.496</v>
+      </c>
+      <c r="C23" t="n">
+        <v>38756.651</v>
+      </c>
+      <c r="D23" t="n">
+        <v>41539.756</v>
+      </c>
+      <c r="E23" t="n">
+        <v>40487.302</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39230.928</v>
+      </c>
+      <c r="G23" t="n">
+        <v>43848.345</v>
+      </c>
+      <c r="H23" t="n">
+        <v>41095.77</v>
+      </c>
+      <c r="I23" t="n">
+        <v>44853.761</v>
+      </c>
+      <c r="J23" t="n">
+        <v>46187.295</v>
+      </c>
+      <c r="K23" t="n">
+        <v>48981.965</v>
+      </c>
+      <c r="L23" t="n">
+        <v>51707.603</v>
+      </c>
+      <c r="M23" t="n">
+        <v>53048.574</v>
+      </c>
+      <c r="N23" t="n">
+        <v>54515.019</v>
+      </c>
+      <c r="O23" t="n">
+        <v>56050.844</v>
+      </c>
+      <c r="P23" t="n">
+        <v>57606.464</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>WEOWORLD</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10431.887</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10964.629</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11522.387</v>
+      </c>
+      <c r="E24" t="n">
+        <v>11569.296</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11163.104</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12636.815</v>
+      </c>
+      <c r="H24" t="n">
+        <v>13064.779</v>
+      </c>
+      <c r="I24" t="n">
+        <v>13514.172</v>
+      </c>
+      <c r="J24" t="n">
+        <v>13904.733</v>
+      </c>
+      <c r="K24" t="n">
+        <v>14613.202</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15279.622</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15882.97</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16526.382</v>
+      </c>
+      <c r="O24" t="n">
+        <v>17174.161</v>
+      </c>
+      <c r="P24" t="n">
+        <v>17860.167</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>income_share_held_by_highest_10_percent</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B30" t="n">
         <v>2016</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C30" t="n">
         <v>2017</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D30" t="n">
         <v>2018</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E30" t="n">
         <v>2019</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F30" t="n">
         <v>2020</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G30" t="n">
         <v>2021</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H30" t="n">
         <v>2022</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I30" t="n">
         <v>2023</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="C27" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="F27" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I27" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>income_share_held_by_lowest_10_percent</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B37" t="n">
         <v>2016</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C37" t="n">
         <v>2017</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D37" t="n">
         <v>2018</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E37" t="n">
         <v>2019</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F37" t="n">
         <v>2020</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G37" t="n">
         <v>2021</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H37" t="n">
         <v>2022</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I37" t="n">
         <v>2023</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I34" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>real_gdp_growth_percent</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B44" t="n">
         <v>2021</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C44" t="n">
         <v>2022</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D44" t="n">
         <v>2023</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E44" t="n">
         <v>2024</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F44" t="n">
         <v>2025</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G44" t="n">
         <v>2026</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H44" t="n">
         <v>2027</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I44" t="n">
         <v>2028</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J44" t="n">
         <v>2029</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K44" t="n">
         <v>2030</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>unemployment_rate</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B51" t="n">
         <v>2022</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C51" t="n">
         <v>2023</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D51" t="n">
         <v>2024</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E51" t="n">
         <v>2025</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F51" t="n">
         <v>2026</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="C48" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="D48" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="E48" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F48" t="n">
-        <v>7.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>unemployment_youth_total_15_24_percent</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B58" t="n">
         <v>2016</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C58" t="n">
         <v>2017</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D58" t="n">
         <v>2018</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E58" t="n">
         <v>2019</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F58" t="n">
         <v>2020</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G58" t="n">
         <v>2021</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H58" t="n">
         <v>2022</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I58" t="n">
         <v>2023</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J58" t="n">
         <v>2024</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K58" t="n">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>24.938</v>
-      </c>
-      <c r="C55" t="n">
-        <v>22.572</v>
-      </c>
-      <c r="D55" t="n">
-        <v>20.953</v>
-      </c>
-      <c r="E55" t="n">
-        <v>19.929</v>
-      </c>
-      <c r="F55" t="n">
-        <v>20.398</v>
-      </c>
-      <c r="G55" t="n">
-        <v>19.252</v>
-      </c>
-      <c r="H55" t="n">
-        <v>17.856</v>
-      </c>
-      <c r="I55" t="n">
-        <v>17.419</v>
-      </c>
-      <c r="J55" t="n">
-        <v>18.603</v>
-      </c>
-      <c r="K55" t="n">
-        <v>18.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>harmonised_index_of_consumer_prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>geo</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C61" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G61" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2027</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2028</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2029</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C62" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="D62" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1.9</v>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>24.938</v>
+      </c>
+      <c r="C59" t="n">
+        <v>22.572</v>
+      </c>
+      <c r="D59" t="n">
+        <v>20.953</v>
+      </c>
+      <c r="E59" t="n">
+        <v>19.929</v>
+      </c>
+      <c r="F59" t="n">
+        <v>20.398</v>
+      </c>
+      <c r="G59" t="n">
+        <v>19.252</v>
+      </c>
+      <c r="H59" t="n">
+        <v>17.856</v>
+      </c>
+      <c r="I59" t="n">
+        <v>17.419</v>
+      </c>
+      <c r="J59" t="n">
+        <v>18.603</v>
+      </c>
+      <c r="K59" t="n">
+        <v>18.89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WEOWORLD</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="C63" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D63" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E63" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F63" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H63" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I63" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J63" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K63" t="n">
-        <v>3.2</v>
+          <t>harmonised_index_of_consumer_prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ADVEC</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>population</t>
-        </is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C67" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>WEOWORLD</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C69" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D69" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>geo</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B75" t="n">
         <v>2022</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C75" t="n">
         <v>2023</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D75" t="n">
         <v>2024</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E75" t="n">
         <v>2025</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F75" t="n">
         <v>2026</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G75" t="n">
         <v>2027</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H75" t="n">
         <v>2028</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I75" t="n">
         <v>2029</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ADVEC</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1087.769</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1095.776</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1102.898</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1107.017</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1109.661</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1112.642</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1115.603</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1118.605</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>446.345</v>
+      </c>
+      <c r="C77" t="n">
+        <v>448.55</v>
+      </c>
+      <c r="D77" t="n">
+        <v>449.798</v>
+      </c>
+      <c r="E77" t="n">
+        <v>450.74</v>
+      </c>
+      <c r="F77" t="n">
+        <v>451.398</v>
+      </c>
+      <c r="G77" t="n">
+        <v>452.081</v>
+      </c>
+      <c r="H77" t="n">
+        <v>452.622</v>
+      </c>
+      <c r="I77" t="n">
+        <v>453.043</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B78" t="n">
         <v>68.06</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C78" t="n">
         <v>68.246</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D78" t="n">
         <v>68.437</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E78" t="n">
         <v>68.628</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F78" t="n">
         <v>68.821</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G78" t="n">
         <v>69.014</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H78" t="n">
         <v>69.20699999999999</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I78" t="n">
         <v>69.401</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>WEOWORLD</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B79" t="n">
         <v>7838.001</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C79" t="n">
         <v>7913.159</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D79" t="n">
         <v>7991.01</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E79" t="n">
         <v>8017.777</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F79" t="n">
         <v>8088.191</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G79" t="n">
         <v>8160.071</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H79" t="n">
         <v>8231.071</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I79" t="n">
         <v>8301.790999999999</v>
       </c>
     </row>
